--- a/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085079A6-AEFD-49A3-934D-A2F72A82791D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C203A05-E931-40D4-91C0-3C570BAE7722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2001" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2001" uniqueCount="588">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -1888,6 +1888,9 @@
   </si>
   <si>
     <t>\I: gas</t>
+  </si>
+  <si>
+    <t>TRAELC</t>
   </si>
 </sst>
 </file>
@@ -2778,6 +2781,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2796,7 +2800,6 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="20% - Accent3 3 2" xfId="4" xr:uid="{ABC4988B-8BA7-47D0-A9D6-448C999748B6}"/>
@@ -3480,7 +3483,7 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="K9" s="1"/>
-      <c r="L9" s="154" t="s">
+      <c r="L9" s="148" t="s">
         <v>586</v>
       </c>
       <c r="M9" s="1"/>
@@ -5184,7 +5187,7 @@
         <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>587</v>
       </c>
       <c r="F5" t="s">
         <v>25</v>
@@ -5283,7 +5286,7 @@
       <c r="E8" s="26"/>
       <c r="F8" t="str">
         <f>C5</f>
-        <v>ELC</v>
+        <v>TRAELC</v>
       </c>
       <c r="G8" t="str">
         <f>E7</f>
@@ -5350,25 +5353,25 @@
       <c r="A1" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="148" t="s">
+      <c r="C1" s="149" t="s">
         <v>107</v>
       </c>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="149" t="s">
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="150" t="s">
         <v>108</v>
       </c>
-      <c r="G1" s="148"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="148" t="s">
+      <c r="G1" s="149"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="149" t="s">
         <v>109</v>
       </c>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
-      <c r="L1" s="148"/>
-      <c r="M1" s="148"/>
-      <c r="N1" s="148"/>
-      <c r="O1" s="151" t="s">
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="152" t="s">
         <v>110</v>
       </c>
       <c r="P1" s="27"/>
@@ -5414,7 +5417,7 @@
       <c r="N2" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="O2" s="152"/>
+      <c r="O2" s="153"/>
       <c r="P2" s="27"/>
       <c r="Q2" s="27"/>
       <c r="R2" s="27"/>
@@ -5459,7 +5462,7 @@
       <c r="N3" s="28">
         <v>2050</v>
       </c>
-      <c r="O3" s="152"/>
+      <c r="O3" s="153"/>
       <c r="P3" s="27"/>
       <c r="Q3" s="27"/>
       <c r="R3" s="27"/>
@@ -5501,7 +5504,7 @@
       <c r="N4" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="O4" s="153"/>
+      <c r="O4" s="154"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="27"/>
       <c r="R4" s="27"/>

--- a/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C203A05-E931-40D4-91C0-3C570BAE7722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4691D356-DC38-4D49-859B-C5A9BE6ABE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -409,9 +409,6 @@
     <t>STG</t>
   </si>
   <si>
-    <t>EXP</t>
-  </si>
-  <si>
     <t>Trd_electricity import</t>
   </si>
   <si>
@@ -576,9 +573,6 @@
     <t>windoff</t>
   </si>
   <si>
-    <t>fossil_supply</t>
-  </si>
-  <si>
     <t>hydro and geothermal</t>
   </si>
   <si>
@@ -1891,6 +1885,12 @@
   </si>
   <si>
     <t>TRAELC</t>
+  </si>
+  <si>
+    <t>\I: bioenergy</t>
+  </si>
+  <si>
+    <t>\I: fossil_supply</t>
   </si>
 </sst>
 </file>
@@ -3195,7 +3195,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{034C1C47-C7B1-48B4-9602-2B825216B37E}">
-  <dimension ref="B2:V19"/>
+  <dimension ref="B2:V21"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="10.1328125" bestFit="1" customWidth="1"/>
@@ -3219,7 +3219,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -3270,10 +3270,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="2:22">
@@ -3346,13 +3346,13 @@
     </row>
     <row r="6" spans="2:22">
       <c r="B6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C6" s="147" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>20</v>
@@ -3383,18 +3383,18 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="V6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="2:22">
       <c r="B7" t="s">
+        <v>581</v>
+      </c>
+      <c r="C7" s="147" t="s">
         <v>583</v>
       </c>
-      <c r="C7" s="147" t="s">
-        <v>585</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>20</v>
@@ -3413,7 +3413,7 @@
         <v>34</v>
       </c>
       <c r="L7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M7" s="1">
         <v>1</v>
@@ -3427,10 +3427,10 @@
     </row>
     <row r="8" spans="2:22">
       <c r="B8" t="s">
-        <v>28</v>
+        <v>581</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
@@ -3446,7 +3446,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="str">
         <f>C10</f>
-        <v>fossil_supply</v>
+        <v>\I: fossil_supply</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1" t="s">
@@ -3465,10 +3465,10 @@
     </row>
     <row r="9" spans="2:22">
       <c r="B9" t="s">
-        <v>96</v>
+        <v>581</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
@@ -3484,7 +3484,7 @@
       <c r="I9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="148" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -3499,13 +3499,13 @@
     </row>
     <row r="10" spans="2:22">
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>581</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>149</v>
+        <v>587</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>20</v>
@@ -3536,10 +3536,10 @@
         <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>20</v>
@@ -3574,10 +3574,10 @@
         <v>28</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>20</v>
@@ -3608,10 +3608,10 @@
         <v>28</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>20</v>
@@ -3623,7 +3623,7 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="L13" s="1" t="s">
-        <v>30</v>
+        <v>586</v>
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -3641,10 +3641,10 @@
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>20</v>
@@ -3679,10 +3679,10 @@
         <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D15" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>20</v>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -3768,45 +3768,45 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" spans="2:22">
-      <c r="J18" t="str">
+    <row r="20" spans="2:22">
+      <c r="J20" t="str">
         <f>C8</f>
         <v>Trd_electricity import</v>
       </c>
-      <c r="L18" t="s">
+      <c r="L20" t="s">
         <v>19</v>
       </c>
-      <c r="P18">
+      <c r="P20">
         <v>0</v>
       </c>
-      <c r="Q18">
+      <c r="Q20">
         <v>3</v>
       </c>
-      <c r="R18">
+      <c r="R20">
         <v>1000</v>
       </c>
-      <c r="S18">
+      <c r="S20">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="2:22">
-      <c r="J19" t="str">
+    <row r="21" spans="2:22">
+      <c r="J21" t="str">
         <f>C9</f>
         <v>Trd_electricity export</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K21" t="s">
         <v>19</v>
       </c>
-      <c r="P19">
+      <c r="P21">
         <v>0</v>
       </c>
-      <c r="Q19">
+      <c r="Q21">
         <v>3</v>
       </c>
-      <c r="R19">
+      <c r="R21">
         <v>1000</v>
       </c>
-      <c r="S19">
+      <c r="S21">
         <v>50</v>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
         <v>57</v>
       </c>
       <c r="N4" s="23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O4" s="23" t="s">
         <v>89</v>
@@ -5184,10 +5184,10 @@
     </row>
     <row r="5" spans="2:25">
       <c r="B5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="F5" t="s">
         <v>25</v>
@@ -5351,20 +5351,20 @@
   <sheetData>
     <row r="1" spans="1:18" ht="33.75" customHeight="1">
       <c r="A1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="149" t="s">
         <v>106</v>
-      </c>
-      <c r="C1" s="149" t="s">
-        <v>107</v>
       </c>
       <c r="D1" s="149"/>
       <c r="E1" s="149"/>
       <c r="F1" s="150" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G1" s="149"/>
       <c r="H1" s="151"/>
       <c r="I1" s="149" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J1" s="149"/>
       <c r="K1" s="149"/>
@@ -5372,7 +5372,7 @@
       <c r="M1" s="149"/>
       <c r="N1" s="149"/>
       <c r="O1" s="152" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P1" s="27"/>
       <c r="Q1" s="27"/>
@@ -5380,42 +5380,42 @@
     </row>
     <row r="2" spans="1:18">
       <c r="C2" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F2" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="H2" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="I2" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="G2" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="H2" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="I2" s="28" t="s">
-        <v>112</v>
-      </c>
       <c r="J2" s="28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K2" s="28" t="str">
         <f>I2</f>
         <v>input~GASNGA</v>
       </c>
       <c r="L2" s="28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M2" s="28" t="str">
         <f>K2</f>
         <v>input~GASNGA</v>
       </c>
       <c r="N2" s="28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O2" s="153"/>
       <c r="P2" s="27"/>
@@ -5475,7 +5475,7 @@
         <v>2030</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F4" s="30">
         <v>2015</v>
@@ -5484,25 +5484,25 @@
         <v>2030</v>
       </c>
       <c r="H4" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="I4" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="J4" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="K4" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="K4" s="32" t="s">
+      <c r="L4" s="33" t="s">
         <v>116</v>
       </c>
-      <c r="L4" s="33" t="s">
+      <c r="M4" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="M4" s="29" t="s">
+      <c r="N4" s="29" t="s">
         <v>118</v>
-      </c>
-      <c r="N4" s="29" t="s">
-        <v>119</v>
       </c>
       <c r="O4" s="154"/>
       <c r="P4" s="27"/>
@@ -5547,7 +5547,7 @@
         <v>9.4E-2</v>
       </c>
       <c r="O5" s="41" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P5" s="42"/>
       <c r="Q5" s="42"/>
@@ -5591,7 +5591,7 @@
         <v>1.0940000000000001</v>
       </c>
       <c r="O6" s="50" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P6" s="51"/>
       <c r="Q6" s="51"/>
@@ -5635,7 +5635,7 @@
         <v>9.4E-2</v>
       </c>
       <c r="O7" s="41" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P7" s="42"/>
       <c r="Q7" s="42"/>
@@ -5679,7 +5679,7 @@
         <v>1.17</v>
       </c>
       <c r="O8" s="50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P8" s="51"/>
       <c r="Q8" s="51"/>
@@ -5723,7 +5723,7 @@
         <v>1.19</v>
       </c>
       <c r="O9" s="41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P9" s="42"/>
       <c r="Q9" s="42"/>
@@ -5767,7 +5767,7 @@
         <v>1.18</v>
       </c>
       <c r="O10" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P10" s="51"/>
       <c r="Q10" s="51"/>
@@ -5811,7 +5811,7 @@
         <v>1.2</v>
       </c>
       <c r="O11" s="41" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P11" s="42"/>
       <c r="Q11" s="42"/>
@@ -5855,7 +5855,7 @@
         <v>0.70799999999999996</v>
       </c>
       <c r="O12" s="50" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P12" s="51"/>
       <c r="Q12" s="51"/>
@@ -5899,7 +5899,7 @@
         <v>0.72</v>
       </c>
       <c r="O13" s="41" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P13" s="42"/>
       <c r="Q13" s="42"/>
@@ -5943,7 +5943,7 @@
         <v>0.01</v>
       </c>
       <c r="O14" s="62" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P14" s="63"/>
       <c r="Q14" s="63"/>
@@ -5987,7 +5987,7 @@
         <v>0.06</v>
       </c>
       <c r="O15" s="72" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P15" s="73"/>
       <c r="Q15" s="73"/>
@@ -6031,7 +6031,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="O16" s="82" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P16" s="83"/>
       <c r="Q16" s="83"/>
@@ -6075,7 +6075,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="72" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P17" s="73"/>
       <c r="Q17" s="73"/>
@@ -6119,7 +6119,7 @@
         <v>3.056E-2</v>
       </c>
       <c r="O18" s="92" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P18" s="93"/>
       <c r="Q18" s="93"/>
@@ -6163,7 +6163,7 @@
         <v>0.02</v>
       </c>
       <c r="O19" s="103" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P19" s="104"/>
       <c r="Q19" s="104"/>
@@ -6207,7 +6207,7 @@
         <v>1.5694083453910281</v>
       </c>
       <c r="O20" s="113" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P20" s="93"/>
       <c r="Q20" s="93"/>
@@ -6251,7 +6251,7 @@
         <v>0.3</v>
       </c>
       <c r="O21" s="122" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P21" s="123"/>
       <c r="Q21" s="123"/>
@@ -6295,7 +6295,7 @@
         <v>0.3</v>
       </c>
       <c r="O22" s="132" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P22" s="133"/>
       <c r="Q22" s="133"/>
@@ -6339,7 +6339,7 @@
         <v>0.20588235294117646</v>
       </c>
       <c r="O23" s="142" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P23" s="123"/>
       <c r="Q23" s="123"/>
@@ -6347,7 +6347,7 @@
     </row>
     <row r="26" spans="1:26" ht="17.25" thickBot="1">
       <c r="C26" s="143" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T26" s="143" t="s">
         <v>0</v>
@@ -6389,7 +6389,7 @@
         <v>input~GASNGA~2015</v>
       </c>
       <c r="J27" s="144" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K27" s="144" t="str">
         <f t="shared" si="1"/>
@@ -6414,7 +6414,7 @@
         <v>57</v>
       </c>
       <c r="Q27" s="144" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="T27" s="144" t="s">
         <v>6</v>
@@ -6484,7 +6484,7 @@
         <v>0.85470085470085477</v>
       </c>
       <c r="O28" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P28">
         <v>25</v>
@@ -6514,7 +6514,7 @@
         <v>14</v>
       </c>
       <c r="Z28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:26">
@@ -6563,7 +6563,7 @@
         <v>0.84745762711864414</v>
       </c>
       <c r="O29" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P29">
         <v>25</v>
@@ -6593,7 +6593,7 @@
         <v>14</v>
       </c>
       <c r="Z29" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -6615,203 +6615,203 @@
   <sheetData>
     <row r="9" spans="2:56">
       <c r="B9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="X9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AD9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AL9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AR9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AZ9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="2:56">
       <c r="B10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D10" t="s">
         <v>161</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10" t="s">
         <v>162</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>163</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>164</v>
       </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
         <v>165</v>
       </c>
-      <c r="G10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H10" t="s">
-        <v>167</v>
-      </c>
       <c r="J10" t="s">
+        <v>160</v>
+      </c>
+      <c r="K10" t="s">
+        <v>202</v>
+      </c>
+      <c r="L10" t="s">
+        <v>203</v>
+      </c>
+      <c r="M10" t="s">
+        <v>204</v>
+      </c>
+      <c r="O10" t="s">
+        <v>159</v>
+      </c>
+      <c r="P10" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>161</v>
+      </c>
+      <c r="R10" t="s">
         <v>162</v>
       </c>
-      <c r="K10" t="s">
-        <v>204</v>
-      </c>
-      <c r="L10" t="s">
-        <v>205</v>
-      </c>
-      <c r="M10" t="s">
-        <v>206</v>
-      </c>
-      <c r="O10" t="s">
+      <c r="S10" t="s">
+        <v>163</v>
+      </c>
+      <c r="T10" t="s">
+        <v>221</v>
+      </c>
+      <c r="U10" t="s">
+        <v>164</v>
+      </c>
+      <c r="V10" t="s">
+        <v>165</v>
+      </c>
+      <c r="X10" t="s">
+        <v>160</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>202</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>143</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>258</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>159</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>160</v>
+      </c>
+      <c r="AF10" t="s">
         <v>161</v>
       </c>
-      <c r="P10" t="s">
+      <c r="AG10" t="s">
         <v>162</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="AH10" t="s">
         <v>163</v>
       </c>
-      <c r="R10" t="s">
+      <c r="AI10" t="s">
         <v>164</v>
       </c>
-      <c r="S10" t="s">
+      <c r="AJ10" t="s">
         <v>165</v>
       </c>
-      <c r="T10" t="s">
-        <v>223</v>
-      </c>
-      <c r="U10" t="s">
-        <v>166</v>
-      </c>
-      <c r="V10" t="s">
-        <v>167</v>
-      </c>
-      <c r="X10" t="s">
+      <c r="AL10" t="s">
+        <v>160</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>257</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>202</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>143</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>258</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>159</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>160</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>161</v>
+      </c>
+      <c r="AU10" t="s">
         <v>162</v>
       </c>
-      <c r="Y10" t="s">
-        <v>259</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>204</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>144</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>260</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>161</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>162</v>
-      </c>
-      <c r="AF10" t="s">
+      <c r="AV10" t="s">
         <v>163</v>
       </c>
-      <c r="AG10" t="s">
+      <c r="AW10" t="s">
         <v>164</v>
       </c>
-      <c r="AH10" t="s">
+      <c r="AX10" t="s">
         <v>165</v>
       </c>
-      <c r="AI10" t="s">
-        <v>166</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>167</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>162</v>
-      </c>
-      <c r="AM10" t="s">
-        <v>259</v>
-      </c>
-      <c r="AN10" t="s">
-        <v>204</v>
-      </c>
-      <c r="AO10" t="s">
-        <v>144</v>
-      </c>
-      <c r="AP10" t="s">
-        <v>260</v>
-      </c>
-      <c r="AR10" t="s">
-        <v>161</v>
-      </c>
-      <c r="AS10" t="s">
-        <v>162</v>
-      </c>
-      <c r="AT10" t="s">
-        <v>163</v>
-      </c>
-      <c r="AU10" t="s">
-        <v>164</v>
-      </c>
-      <c r="AV10" t="s">
-        <v>165</v>
-      </c>
-      <c r="AW10" t="s">
-        <v>166</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>167</v>
-      </c>
       <c r="AZ10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="BA10" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="BB10" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="BC10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="BD10" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" spans="2:56">
       <c r="B11" t="s">
+        <v>166</v>
+      </c>
+      <c r="C11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D11" t="s">
         <v>168</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" t="s">
         <v>169</v>
       </c>
-      <c r="D11" t="s">
+      <c r="H11" t="s">
         <v>170</v>
       </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" t="s">
-        <v>171</v>
-      </c>
-      <c r="H11" t="s">
-        <v>172</v>
-      </c>
       <c r="J11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="K11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="L11">
         <v>14.703515544593534</v>
@@ -6820,37 +6820,37 @@
         <v>0.18394567124097769</v>
       </c>
       <c r="O11" t="s">
+        <v>222</v>
+      </c>
+      <c r="P11" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q11" t="s">
         <v>224</v>
       </c>
-      <c r="P11" t="s">
+      <c r="R11" t="s">
+        <v>10</v>
+      </c>
+      <c r="S11" t="s">
+        <v>20</v>
+      </c>
+      <c r="T11" t="s">
         <v>225</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="U11" t="s">
         <v>226</v>
       </c>
-      <c r="R11" t="s">
-        <v>10</v>
-      </c>
-      <c r="S11" t="s">
-        <v>20</v>
-      </c>
-      <c r="T11" t="s">
-        <v>227</v>
-      </c>
-      <c r="U11" t="s">
-        <v>228</v>
-      </c>
       <c r="V11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="X11" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Y11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="Z11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AA11">
         <v>0.99781284363204548</v>
@@ -6859,13 +6859,13 @@
         <v>40.097866745833329</v>
       </c>
       <c r="AD11" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AE11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AF11" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AG11" t="s">
         <v>10</v>
@@ -6874,19 +6874,19 @@
         <v>20</v>
       </c>
       <c r="AI11" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AJ11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AL11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AM11" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AN11" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AO11">
         <v>0.99692224665834439</v>
@@ -6895,13 +6895,13 @@
         <v>56.425477930352955</v>
       </c>
       <c r="AR11" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS11" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AT11" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AU11" t="s">
         <v>10</v>
@@ -6910,19 +6910,19 @@
         <v>20</v>
       </c>
       <c r="AW11" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ11" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="BA11" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="BB11" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="BC11">
         <v>0.9878288138539939</v>
@@ -6933,13 +6933,13 @@
     </row>
     <row r="12" spans="2:56">
       <c r="B12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -6948,16 +6948,16 @@
         <v>20</v>
       </c>
       <c r="G12" t="s">
+        <v>169</v>
+      </c>
+      <c r="H12" t="s">
+        <v>170</v>
+      </c>
+      <c r="J12" t="s">
         <v>171</v>
       </c>
-      <c r="H12" t="s">
-        <v>172</v>
-      </c>
-      <c r="J12" t="s">
-        <v>173</v>
-      </c>
       <c r="K12" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="L12">
         <v>7.0247960503319238</v>
@@ -6966,13 +6966,13 @@
         <v>0.1895344528514209</v>
       </c>
       <c r="O12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="Q12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="R12" t="s">
         <v>10</v>
@@ -6981,22 +6981,22 @@
         <v>20</v>
       </c>
       <c r="T12" t="s">
+        <v>225</v>
+      </c>
+      <c r="U12" t="s">
+        <v>226</v>
+      </c>
+      <c r="V12" t="s">
+        <v>170</v>
+      </c>
+      <c r="X12" t="s">
         <v>227</v>
       </c>
-      <c r="U12" t="s">
-        <v>228</v>
-      </c>
-      <c r="V12" t="s">
-        <v>172</v>
-      </c>
-      <c r="X12" t="s">
-        <v>229</v>
-      </c>
       <c r="Y12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Z12" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AA12">
         <v>0.99164479201276912</v>
@@ -7005,13 +7005,13 @@
         <v>153.17881309923388</v>
       </c>
       <c r="AD12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AE12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AF12" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AG12" t="s">
         <v>10</v>
@@ -7020,19 +7020,19 @@
         <v>20</v>
       </c>
       <c r="AI12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AJ12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AL12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AM12" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AN12" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AO12">
         <v>0.99590345602074126</v>
@@ -7041,13 +7041,13 @@
         <v>75.103306286410302</v>
       </c>
       <c r="AR12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AT12" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AU12" t="s">
         <v>10</v>
@@ -7056,19 +7056,19 @@
         <v>20</v>
       </c>
       <c r="AW12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="BA12" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="BB12" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="BC12">
         <v>0.98395883577792953</v>
@@ -7079,13 +7079,13 @@
     </row>
     <row r="13" spans="2:56">
       <c r="B13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C13" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D13" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -7094,16 +7094,16 @@
         <v>20</v>
       </c>
       <c r="G13" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J13" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="K13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L13">
         <v>12.174517979652411</v>
@@ -7112,13 +7112,13 @@
         <v>0.18533082336913481</v>
       </c>
       <c r="O13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Q13" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="R13" t="s">
         <v>10</v>
@@ -7127,22 +7127,22 @@
         <v>20</v>
       </c>
       <c r="T13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="U13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="V13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="X13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Y13" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="Z13" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA13">
         <v>0.99568371668484024</v>
@@ -7151,13 +7151,13 @@
         <v>79.131860777928608</v>
       </c>
       <c r="AD13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AE13" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AF13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AG13" t="s">
         <v>10</v>
@@ -7166,19 +7166,19 @@
         <v>20</v>
       </c>
       <c r="AI13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AJ13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AL13" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AM13" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AN13" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AO13">
         <v>0.9975157188831717</v>
@@ -7187,13 +7187,13 @@
         <v>45.545153808519316</v>
       </c>
       <c r="AR13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS13" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AT13" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AU13" t="s">
         <v>10</v>
@@ -7202,19 +7202,19 @@
         <v>20</v>
       </c>
       <c r="AW13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ13" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="BA13" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="BB13" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="BC13">
         <v>0.94957327345368925</v>
@@ -7225,13 +7225,13 @@
     </row>
     <row r="14" spans="2:56">
       <c r="B14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C14" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -7240,16 +7240,16 @@
         <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J14" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K14" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L14">
         <v>8.646134759765264</v>
@@ -7258,13 +7258,13 @@
         <v>0.18564315469610329</v>
       </c>
       <c r="O14" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Q14" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="R14" t="s">
         <v>10</v>
@@ -7273,22 +7273,22 @@
         <v>20</v>
       </c>
       <c r="T14" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="U14" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="V14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="X14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Y14" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="Z14" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AA14">
         <v>0.99673728461460676</v>
@@ -7297,13 +7297,13 @@
         <v>59.816448732209111</v>
       </c>
       <c r="AD14" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AE14" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AF14" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AG14" t="s">
         <v>10</v>
@@ -7312,19 +7312,19 @@
         <v>20</v>
       </c>
       <c r="AI14" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AJ14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AL14" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AM14" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AN14" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AO14">
         <v>0.99725701149052537</v>
@@ -7333,13 +7333,13 @@
         <v>50.288122673700855</v>
       </c>
       <c r="AR14" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS14" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AT14" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AU14" t="s">
         <v>10</v>
@@ -7348,19 +7348,19 @@
         <v>20</v>
       </c>
       <c r="AW14" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ14" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="BA14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="BB14" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="BC14">
         <v>0.98560960960201449</v>
@@ -7371,13 +7371,13 @@
     </row>
     <row r="15" spans="2:56">
       <c r="B15" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C15" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D15" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -7386,16 +7386,16 @@
         <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J15" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="K15" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="L15">
         <v>10.978710703279315</v>
@@ -7404,13 +7404,13 @@
         <v>0.1751830539964257</v>
       </c>
       <c r="O15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P15" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="Q15" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="R15" t="s">
         <v>10</v>
@@ -7419,22 +7419,22 @@
         <v>20</v>
       </c>
       <c r="T15" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="U15" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="V15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="X15" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="Y15" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Z15" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AA15">
         <v>0.99709164861435029</v>
@@ -7443,13 +7443,13 @@
         <v>53.319775403577559</v>
       </c>
       <c r="AD15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AE15" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AF15" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AG15" t="s">
         <v>10</v>
@@ -7458,19 +7458,19 @@
         <v>20</v>
       </c>
       <c r="AI15" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AJ15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AL15" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AM15" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AN15" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AO15">
         <v>0.99595483459575906</v>
@@ -7479,13 +7479,13 @@
         <v>74.161365744417125</v>
       </c>
       <c r="AR15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS15" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AT15" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AU15" t="s">
         <v>10</v>
@@ -7494,19 +7494,19 @@
         <v>20</v>
       </c>
       <c r="AW15" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ15" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="BA15" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="BB15" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="BC15">
         <v>0.99053075643264799</v>
@@ -7517,13 +7517,13 @@
     </row>
     <row r="16" spans="2:56">
       <c r="B16" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C16" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D16" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -7532,16 +7532,16 @@
         <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J16" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="K16" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L16">
         <v>13.930117028134356</v>
@@ -7550,13 +7550,13 @@
         <v>0.18239756272718469</v>
       </c>
       <c r="O16" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P16" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="Q16" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="R16" t="s">
         <v>10</v>
@@ -7565,22 +7565,22 @@
         <v>20</v>
       </c>
       <c r="T16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="U16" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="V16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="X16" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="Y16" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="Z16" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AA16">
         <v>0.99552574319771747</v>
@@ -7589,13 +7589,13 @@
         <v>82.028041375179441</v>
       </c>
       <c r="AD16" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AE16" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AF16" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AG16" t="s">
         <v>10</v>
@@ -7604,19 +7604,19 @@
         <v>20</v>
       </c>
       <c r="AI16" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AJ16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AL16" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AM16" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AN16" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AO16">
         <v>0.99761292756299069</v>
@@ -7625,13 +7625,13 @@
         <v>43.762994678503716</v>
       </c>
       <c r="AR16" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS16" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AT16" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AU16" t="s">
         <v>10</v>
@@ -7640,19 +7640,19 @@
         <v>20</v>
       </c>
       <c r="AW16" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ16" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="BA16" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="BB16" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="BC16">
         <v>0.98974923036021278</v>
@@ -7663,13 +7663,13 @@
     </row>
     <row r="17" spans="2:56">
       <c r="B17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C17" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D17" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -7678,16 +7678,16 @@
         <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J17" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K17" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L17">
         <v>7.7139766429685555</v>
@@ -7696,13 +7696,13 @@
         <v>0.16714441187363149</v>
       </c>
       <c r="O17" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P17" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q17" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="R17" t="s">
         <v>10</v>
@@ -7711,22 +7711,22 @@
         <v>20</v>
       </c>
       <c r="T17" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="U17" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="V17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="X17" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Y17" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="Z17" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AA17">
         <v>0.99856414548474748</v>
@@ -7735,13 +7735,13 @@
         <v>26.323999446296273</v>
       </c>
       <c r="AD17" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AE17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AF17" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AG17" t="s">
         <v>10</v>
@@ -7750,19 +7750,19 @@
         <v>20</v>
       </c>
       <c r="AI17" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AJ17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AL17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AM17" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AN17" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AO17">
         <v>0.99446613913875159</v>
@@ -7771,13 +7771,13 @@
         <v>101.45411578955439</v>
       </c>
       <c r="AR17" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS17" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AT17" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AU17" t="s">
         <v>10</v>
@@ -7786,19 +7786,19 @@
         <v>20</v>
       </c>
       <c r="AW17" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ17" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="BA17" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="BB17" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="BC17">
         <v>0.99439449087123744</v>
@@ -7809,13 +7809,13 @@
     </row>
     <row r="18" spans="2:56">
       <c r="B18" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C18" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D18" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -7824,16 +7824,16 @@
         <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J18" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K18" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L18">
         <v>13.532966068581743</v>
@@ -7842,13 +7842,13 @@
         <v>0.15443081133819789</v>
       </c>
       <c r="O18" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P18" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="Q18" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="R18" t="s">
         <v>10</v>
@@ -7857,22 +7857,22 @@
         <v>20</v>
       </c>
       <c r="T18" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="U18" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="V18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="X18" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="Y18" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="Z18" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AA18">
         <v>0.99837169372341228</v>
@@ -7881,13 +7881,13 @@
         <v>29.852281737441412</v>
       </c>
       <c r="AD18" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AE18" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AF18" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AG18" t="s">
         <v>10</v>
@@ -7896,19 +7896,19 @@
         <v>20</v>
       </c>
       <c r="AI18" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AJ18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AL18" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AM18" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AN18" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AO18">
         <v>0.99821201020674788</v>
@@ -7917,13 +7917,13 @@
         <v>32.77981287628851</v>
       </c>
       <c r="AR18" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS18" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AT18" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AU18" t="s">
         <v>10</v>
@@ -7932,19 +7932,19 @@
         <v>20</v>
       </c>
       <c r="AW18" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ18" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="BA18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="BB18" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="BC18">
         <v>0.9960370911532308</v>
@@ -7955,13 +7955,13 @@
     </row>
     <row r="19" spans="2:56">
       <c r="B19" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C19" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D19" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -7970,16 +7970,16 @@
         <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J19" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K19" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="L19">
         <v>0.30791874242419603</v>
@@ -7988,13 +7988,13 @@
         <v>0.15242372922965119</v>
       </c>
       <c r="O19" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P19" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="Q19" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="R19" t="s">
         <v>10</v>
@@ -8003,22 +8003,22 @@
         <v>20</v>
       </c>
       <c r="T19" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="U19" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="V19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="X19" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="Y19" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Z19" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AA19">
         <v>0.99541580702824473</v>
@@ -8027,13 +8027,13 @@
         <v>84.0435378155141</v>
       </c>
       <c r="AD19" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AE19" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AF19" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AG19" t="s">
         <v>10</v>
@@ -8042,19 +8042,19 @@
         <v>20</v>
       </c>
       <c r="AI19" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AJ19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AL19" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AM19" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AN19" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AO19">
         <v>0.99562511313409086</v>
@@ -8063,13 +8063,13 @@
         <v>80.206259208334231</v>
       </c>
       <c r="AR19" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS19" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AT19" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AU19" t="s">
         <v>10</v>
@@ -8078,19 +8078,19 @@
         <v>20</v>
       </c>
       <c r="AW19" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ19" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="BA19" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="BB19" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="BC19">
         <v>0.98596601099553871</v>
@@ -8101,13 +8101,13 @@
     </row>
     <row r="20" spans="2:56">
       <c r="B20" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C20" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D20" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -8116,16 +8116,16 @@
         <v>20</v>
       </c>
       <c r="G20" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J20" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K20" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L20">
         <v>3.0931829905152187E-2</v>
@@ -8134,13 +8134,13 @@
         <v>0.13596321535260519</v>
       </c>
       <c r="O20" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P20" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q20" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="R20" t="s">
         <v>10</v>
@@ -8149,22 +8149,22 @@
         <v>20</v>
       </c>
       <c r="T20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="U20" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="V20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="X20" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Y20" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="Z20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AA20">
         <v>0.9981722170039925</v>
@@ -8173,13 +8173,13 @@
         <v>33.509354926805031</v>
       </c>
       <c r="AD20" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AE20" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AF20" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AG20" t="s">
         <v>10</v>
@@ -8188,19 +8188,19 @@
         <v>20</v>
       </c>
       <c r="AI20" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AJ20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AL20" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AM20" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AN20" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AO20">
         <v>0.99857516825685033</v>
@@ -8209,13 +8209,13 @@
         <v>26.121915291078167</v>
       </c>
       <c r="AR20" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS20" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AT20" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AU20" t="s">
         <v>10</v>
@@ -8224,19 +8224,19 @@
         <v>20</v>
       </c>
       <c r="AW20" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ20" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="BA20" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="BB20" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="BC20">
         <v>0.96328479701100822</v>
@@ -8247,13 +8247,13 @@
     </row>
     <row r="21" spans="2:56">
       <c r="B21" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -8262,16 +8262,16 @@
         <v>20</v>
       </c>
       <c r="G21" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K21" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="L21">
         <v>7.2737697525181089</v>
@@ -8280,13 +8280,13 @@
         <v>0.1484590937756623</v>
       </c>
       <c r="O21" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P21" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="Q21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="R21" t="s">
         <v>10</v>
@@ -8295,22 +8295,22 @@
         <v>20</v>
       </c>
       <c r="T21" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="U21" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="V21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="X21" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="Y21" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="Z21" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AA21">
         <v>0.99757939258365447</v>
@@ -8319,13 +8319,13 @@
         <v>44.377802633000776</v>
       </c>
       <c r="AD21" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AE21" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AF21" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AG21" t="s">
         <v>10</v>
@@ -8334,19 +8334,19 @@
         <v>20</v>
       </c>
       <c r="AI21" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AJ21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AL21" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AM21" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AN21" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="AO21">
         <v>0.99624198670989172</v>
@@ -8355,13 +8355,13 @@
         <v>68.896910318651507</v>
       </c>
       <c r="AR21" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS21" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AT21" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AU21" t="s">
         <v>10</v>
@@ -8370,19 +8370,19 @@
         <v>20</v>
       </c>
       <c r="AW21" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ21" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="BA21" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="BB21" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="BC21">
         <v>0.98248517632197996</v>
@@ -8393,13 +8393,13 @@
     </row>
     <row r="22" spans="2:56">
       <c r="B22" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C22" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D22" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -8408,16 +8408,16 @@
         <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H22" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J22" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K22" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L22">
         <v>7.307015755869652</v>
@@ -8426,13 +8426,13 @@
         <v>0.17768231485175401</v>
       </c>
       <c r="O22" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P22" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Q22" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="R22" t="s">
         <v>10</v>
@@ -8441,22 +8441,22 @@
         <v>20</v>
       </c>
       <c r="T22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="U22" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="V22" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="X22" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Y22" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Z22" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AA22">
         <v>0.9982917156958806</v>
@@ -8465,13 +8465,13 @@
         <v>31.318545575522229</v>
       </c>
       <c r="AD22" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AE22" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AF22" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AG22" t="s">
         <v>10</v>
@@ -8480,19 +8480,19 @@
         <v>20</v>
       </c>
       <c r="AI22" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AJ22" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AL22" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AM22" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AN22" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AO22">
         <v>0.99239099026325794</v>
@@ -8501,13 +8501,13 @@
         <v>139.49851184027145</v>
       </c>
       <c r="AR22" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS22" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AT22" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AU22" t="s">
         <v>10</v>
@@ -8516,19 +8516,19 @@
         <v>20</v>
       </c>
       <c r="AW22" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX22" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ22" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="BA22" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="BB22" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="BC22">
         <v>0.992142345264865</v>
@@ -8539,13 +8539,13 @@
     </row>
     <row r="23" spans="2:56">
       <c r="B23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -8554,16 +8554,16 @@
         <v>20</v>
       </c>
       <c r="G23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K23" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L23">
         <v>13.939949671576917</v>
@@ -8572,13 +8572,13 @@
         <v>0.1699372145053003</v>
       </c>
       <c r="O23" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P23" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="Q23" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="R23" t="s">
         <v>10</v>
@@ -8587,22 +8587,22 @@
         <v>20</v>
       </c>
       <c r="T23" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="U23" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="V23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="X23" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="Y23" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="Z23" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AA23">
         <v>0.99649838493007836</v>
@@ -8611,13 +8611,13 @@
         <v>64.196276281897482</v>
       </c>
       <c r="AD23" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AE23" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AF23" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AG23" t="s">
         <v>10</v>
@@ -8626,19 +8626,19 @@
         <v>20</v>
       </c>
       <c r="AI23" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AJ23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AL23" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AM23" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AN23" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AO23">
         <v>0.99807547980555666</v>
@@ -8647,13 +8647,13 @@
         <v>35.282870231460656</v>
       </c>
       <c r="AR23" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS23" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AT23" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AU23" t="s">
         <v>10</v>
@@ -8662,19 +8662,19 @@
         <v>20</v>
       </c>
       <c r="AW23" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ23" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="BA23" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="BB23" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="BC23">
         <v>0.99241288386292881</v>
@@ -8685,13 +8685,13 @@
     </row>
     <row r="24" spans="2:56">
       <c r="B24" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D24" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -8700,16 +8700,16 @@
         <v>20</v>
       </c>
       <c r="G24" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K24" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L24">
         <v>1.6370832793384471</v>
@@ -8718,13 +8718,13 @@
         <v>0.1729078211793279</v>
       </c>
       <c r="O24" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P24" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Q24" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="R24" t="s">
         <v>10</v>
@@ -8733,22 +8733,22 @@
         <v>20</v>
       </c>
       <c r="T24" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="U24" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="V24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="X24" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Y24" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Z24" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AA24">
         <v>0.9958319028842455</v>
@@ -8757,13 +8757,13 @@
         <v>76.415113788833068</v>
       </c>
       <c r="AD24" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AE24" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AF24" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AG24" t="s">
         <v>10</v>
@@ -8772,19 +8772,19 @@
         <v>20</v>
       </c>
       <c r="AI24" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AJ24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AL24" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AM24" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AN24" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AO24">
         <v>0.99665105279570931</v>
@@ -8793,13 +8793,13 @@
         <v>61.397365411996212</v>
       </c>
       <c r="AR24" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS24" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AT24" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AU24" t="s">
         <v>10</v>
@@ -8808,19 +8808,19 @@
         <v>20</v>
       </c>
       <c r="AW24" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ24" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="BA24" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="BB24" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="BC24">
         <v>0.99503867375582744</v>
@@ -8831,13 +8831,13 @@
     </row>
     <row r="25" spans="2:56">
       <c r="B25" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C25" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D25" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -8846,16 +8846,16 @@
         <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J25" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K25" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L25">
         <v>0.73381363970591551</v>
@@ -8864,13 +8864,13 @@
         <v>0.16678541694650079</v>
       </c>
       <c r="O25" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P25" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Q25" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="R25" t="s">
         <v>10</v>
@@ -8879,22 +8879,22 @@
         <v>20</v>
       </c>
       <c r="T25" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="U25" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="V25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="X25" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Y25" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Z25" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AA25">
         <v>0.9986195737404916</v>
@@ -8903,13 +8903,13 @@
         <v>25.307814757654675</v>
       </c>
       <c r="AD25" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AE25" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AF25" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AG25" t="s">
         <v>10</v>
@@ -8918,19 +8918,19 @@
         <v>20</v>
       </c>
       <c r="AI25" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AJ25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AL25" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AM25" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AN25" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="AO25">
         <v>0.99826030196534266</v>
@@ -8939,13 +8939,13 @@
         <v>31.894463968718917</v>
       </c>
       <c r="AR25" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS25" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AT25" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AU25" t="s">
         <v>10</v>
@@ -8954,19 +8954,19 @@
         <v>20</v>
       </c>
       <c r="AW25" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ25" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="BA25" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="BB25" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="BC25">
         <v>0.99162758874212198</v>
@@ -8977,13 +8977,13 @@
     </row>
     <row r="26" spans="2:56">
       <c r="B26" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D26" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -8992,16 +8992,16 @@
         <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="K26" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="L26">
         <v>1.8144550028683772</v>
@@ -9010,13 +9010,13 @@
         <v>0.1577067378709853</v>
       </c>
       <c r="O26" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P26" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="Q26" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="R26" t="s">
         <v>10</v>
@@ -9025,22 +9025,22 @@
         <v>20</v>
       </c>
       <c r="T26" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="U26" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="V26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="X26" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="Y26" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="Z26" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AA26">
         <v>0.99656426482871763</v>
@@ -9049,13 +9049,13 @@
         <v>62.988478140176163</v>
       </c>
       <c r="AR26" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS26" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AT26" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AU26" t="s">
         <v>10</v>
@@ -9064,19 +9064,19 @@
         <v>20</v>
       </c>
       <c r="AW26" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ26" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="BA26" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="BB26" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="BC26">
         <v>0.99508487560623826</v>
@@ -9087,13 +9087,13 @@
     </row>
     <row r="27" spans="2:56">
       <c r="AR27" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS27" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AT27" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AU27" t="s">
         <v>10</v>
@@ -9102,19 +9102,19 @@
         <v>20</v>
       </c>
       <c r="AW27" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ27" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="BA27" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="BB27" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="BC27">
         <v>0.97496359905143026</v>
@@ -9125,13 +9125,13 @@
     </row>
     <row r="28" spans="2:56">
       <c r="AR28" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS28" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AT28" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AU28" t="s">
         <v>10</v>
@@ -9140,19 +9140,19 @@
         <v>20</v>
       </c>
       <c r="AW28" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX28" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ28" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="BA28" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="BB28" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="BC28">
         <v>0.99514843803074871</v>
@@ -9163,13 +9163,13 @@
     </row>
     <row r="29" spans="2:56">
       <c r="AR29" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS29" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AT29" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AU29" t="s">
         <v>10</v>
@@ -9178,19 +9178,19 @@
         <v>20</v>
       </c>
       <c r="AW29" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ29" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="BA29" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="BB29" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="BC29">
         <v>0.98039565814133589</v>
@@ -9201,13 +9201,13 @@
     </row>
     <row r="30" spans="2:56">
       <c r="AR30" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS30" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AT30" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AU30" t="s">
         <v>10</v>
@@ -9216,19 +9216,19 @@
         <v>20</v>
       </c>
       <c r="AW30" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ30" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="BA30" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="BB30" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="BC30">
         <v>0.99199988291996133</v>
@@ -9239,13 +9239,13 @@
     </row>
     <row r="31" spans="2:56">
       <c r="AR31" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS31" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AT31" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AU31" t="s">
         <v>10</v>
@@ -9254,19 +9254,19 @@
         <v>20</v>
       </c>
       <c r="AW31" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX31" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ31" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="BA31" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="BB31" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="BC31">
         <v>0.96374055461874508</v>
@@ -9277,13 +9277,13 @@
     </row>
     <row r="32" spans="2:56">
       <c r="AR32" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS32" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AT32" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AU32" t="s">
         <v>10</v>
@@ -9292,19 +9292,19 @@
         <v>20</v>
       </c>
       <c r="AW32" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX32" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ32" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="BA32" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="BB32" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="BC32">
         <v>0.99048115912556611</v>
@@ -9315,13 +9315,13 @@
     </row>
     <row r="33" spans="44:56">
       <c r="AR33" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS33" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AT33" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AU33" t="s">
         <v>10</v>
@@ -9330,19 +9330,19 @@
         <v>20</v>
       </c>
       <c r="AW33" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX33" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ33" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="BA33" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="BB33" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="BC33">
         <v>0.99441710380733805</v>
@@ -9353,13 +9353,13 @@
     </row>
     <row r="34" spans="44:56">
       <c r="AR34" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS34" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AT34" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AU34" t="s">
         <v>10</v>
@@ -9368,19 +9368,19 @@
         <v>20</v>
       </c>
       <c r="AW34" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX34" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ34" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA34" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="BB34" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="BC34">
         <v>0.9871879084242271</v>
@@ -9391,13 +9391,13 @@
     </row>
     <row r="35" spans="44:56">
       <c r="AR35" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS35" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AT35" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AU35" t="s">
         <v>10</v>
@@ -9406,19 +9406,19 @@
         <v>20</v>
       </c>
       <c r="AW35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX35" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ35" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="BA35" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="BB35" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="BC35">
         <v>0.99511226039729839</v>
@@ -9429,13 +9429,13 @@
     </row>
     <row r="36" spans="44:56">
       <c r="AR36" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS36" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AT36" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AU36" t="s">
         <v>10</v>
@@ -9444,19 +9444,19 @@
         <v>20</v>
       </c>
       <c r="AW36" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ36" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="BA36" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="BB36" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="BC36">
         <v>0.99402092584318991</v>
@@ -9467,13 +9467,13 @@
     </row>
     <row r="37" spans="44:56">
       <c r="AR37" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS37" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AT37" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AU37" t="s">
         <v>10</v>
@@ -9482,19 +9482,19 @@
         <v>20</v>
       </c>
       <c r="AW37" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX37" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ37" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="BA37" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="BB37" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="BC37">
         <v>0.99402264995370893</v>
@@ -9505,13 +9505,13 @@
     </row>
     <row r="38" spans="44:56">
       <c r="AR38" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS38" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AT38" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AU38" t="s">
         <v>10</v>
@@ -9520,19 +9520,19 @@
         <v>20</v>
       </c>
       <c r="AW38" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX38" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ38" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="BA38" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="BB38" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="BC38">
         <v>0.99490522012066784</v>
@@ -9543,13 +9543,13 @@
     </row>
     <row r="39" spans="44:56">
       <c r="AR39" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS39" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="AT39" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AU39" t="s">
         <v>10</v>
@@ -9558,19 +9558,19 @@
         <v>20</v>
       </c>
       <c r="AW39" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX39" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ39" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="BA39" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="BB39" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="BC39">
         <v>0.99728827252195684</v>
@@ -9581,13 +9581,13 @@
     </row>
     <row r="40" spans="44:56">
       <c r="AR40" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS40" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AT40" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AU40" t="s">
         <v>10</v>
@@ -9596,19 +9596,19 @@
         <v>20</v>
       </c>
       <c r="AW40" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX40" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ40" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="BA40" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="BB40" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="BC40">
         <v>0.95113733831453195</v>
@@ -9619,13 +9619,13 @@
     </row>
     <row r="41" spans="44:56">
       <c r="AR41" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS41" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AT41" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AU41" t="s">
         <v>10</v>
@@ -9634,19 +9634,19 @@
         <v>20</v>
       </c>
       <c r="AW41" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX41" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ41" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="BA41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="BB41" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="BC41">
         <v>0.9955021345306051</v>
@@ -9657,13 +9657,13 @@
     </row>
     <row r="42" spans="44:56">
       <c r="AR42" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS42" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AT42" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AU42" t="s">
         <v>10</v>
@@ -9672,19 +9672,19 @@
         <v>20</v>
       </c>
       <c r="AW42" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX42" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ42" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="BA42" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="BB42" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="BC42">
         <v>0.99579892549254256</v>
@@ -9695,13 +9695,13 @@
     </row>
     <row r="43" spans="44:56">
       <c r="AR43" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AS43" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AT43" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AU43" t="s">
         <v>10</v>
@@ -9710,19 +9710,19 @@
         <v>20</v>
       </c>
       <c r="AW43" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AX43" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AZ43" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="BA43" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="BB43" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="BC43">
         <v>0.9877150845460122</v>
@@ -9743,95 +9743,95 @@
   <sheetData>
     <row r="9" spans="2:26">
       <c r="B9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="W9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="2:26">
       <c r="B10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D10" t="s">
         <v>161</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10" t="s">
         <v>162</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>163</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>164</v>
       </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
         <v>165</v>
       </c>
-      <c r="G10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H10" t="s">
-        <v>167</v>
-      </c>
       <c r="J10" t="s">
+        <v>160</v>
+      </c>
+      <c r="K10" t="s">
+        <v>202</v>
+      </c>
+      <c r="L10" t="s">
+        <v>203</v>
+      </c>
+      <c r="M10" t="s">
+        <v>204</v>
+      </c>
+      <c r="O10" t="s">
+        <v>159</v>
+      </c>
+      <c r="P10" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>161</v>
+      </c>
+      <c r="R10" t="s">
         <v>162</v>
       </c>
-      <c r="K10" t="s">
+      <c r="S10" t="s">
+        <v>163</v>
+      </c>
+      <c r="T10" t="s">
+        <v>164</v>
+      </c>
+      <c r="U10" t="s">
+        <v>165</v>
+      </c>
+      <c r="W10" t="s">
+        <v>160</v>
+      </c>
+      <c r="X10" t="s">
+        <v>202</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>203</v>
+      </c>
+      <c r="Z10" t="s">
         <v>204</v>
-      </c>
-      <c r="L10" t="s">
-        <v>205</v>
-      </c>
-      <c r="M10" t="s">
-        <v>206</v>
-      </c>
-      <c r="O10" t="s">
-        <v>161</v>
-      </c>
-      <c r="P10" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>163</v>
-      </c>
-      <c r="R10" t="s">
-        <v>164</v>
-      </c>
-      <c r="S10" t="s">
-        <v>165</v>
-      </c>
-      <c r="T10" t="s">
-        <v>166</v>
-      </c>
-      <c r="U10" t="s">
-        <v>167</v>
-      </c>
-      <c r="W10" t="s">
-        <v>162</v>
-      </c>
-      <c r="X10" t="s">
-        <v>204</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>205</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="11" spans="2:26">
       <c r="B11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C11" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D11" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -9840,16 +9840,16 @@
         <v>20</v>
       </c>
       <c r="G11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J11" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="K11" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="L11">
         <v>8.3728062197205944</v>
@@ -9858,13 +9858,13 @@
         <v>0.4071105959727585</v>
       </c>
       <c r="O11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P11" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="Q11" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="R11" t="s">
         <v>10</v>
@@ -9873,16 +9873,16 @@
         <v>20</v>
       </c>
       <c r="T11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W11" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="X11" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="Y11">
         <v>2.177</v>
@@ -9893,13 +9893,13 @@
     </row>
     <row r="12" spans="2:26">
       <c r="B12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C12" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D12" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -9908,16 +9908,16 @@
         <v>20</v>
       </c>
       <c r="G12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J12" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K12" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="L12">
         <v>42.531235680568031</v>
@@ -9926,13 +9926,13 @@
         <v>0.36457772816942419</v>
       </c>
       <c r="O12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P12" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Q12" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="R12" t="s">
         <v>10</v>
@@ -9941,16 +9941,16 @@
         <v>20</v>
       </c>
       <c r="T12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W12" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="X12" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="Y12">
         <v>47.905999999999999</v>
@@ -9961,13 +9961,13 @@
     </row>
     <row r="13" spans="2:26">
       <c r="B13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C13" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D13" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -9976,16 +9976,16 @@
         <v>20</v>
       </c>
       <c r="G13" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J13" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K13" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="L13">
         <v>30.271312154499352</v>
@@ -9994,13 +9994,13 @@
         <v>0.34977720239710119</v>
       </c>
       <c r="O13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P13" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="Q13" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="R13" t="s">
         <v>10</v>
@@ -10009,16 +10009,16 @@
         <v>20</v>
       </c>
       <c r="T13" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W13" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="X13" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="Y13">
         <v>91.13</v>
@@ -10029,13 +10029,13 @@
     </row>
     <row r="14" spans="2:26">
       <c r="B14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C14" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D14" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -10044,16 +10044,16 @@
         <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J14" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K14" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="L14">
         <v>22.688073076145226</v>
@@ -10062,13 +10062,13 @@
         <v>0.2378222396486388</v>
       </c>
       <c r="O14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P14" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="Q14" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="R14" t="s">
         <v>10</v>
@@ -10077,16 +10077,16 @@
         <v>20</v>
       </c>
       <c r="T14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W14" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="X14" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="Y14">
         <v>30.484999999999999</v>
@@ -10097,13 +10097,13 @@
     </row>
     <row r="15" spans="2:26">
       <c r="B15" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C15" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D15" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -10112,16 +10112,16 @@
         <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J15" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K15" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="L15">
         <v>29.120153762247021</v>
@@ -10130,13 +10130,13 @@
         <v>0.2926790130249729</v>
       </c>
       <c r="O15" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P15" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="Q15" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="R15" t="s">
         <v>10</v>
@@ -10145,16 +10145,16 @@
         <v>20</v>
       </c>
       <c r="T15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W15" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="X15" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="Y15">
         <v>6.726</v>
@@ -10165,13 +10165,13 @@
     </row>
     <row r="16" spans="2:26">
       <c r="B16" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C16" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D16" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -10180,16 +10180,16 @@
         <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J16" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K16" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="L16">
         <v>10.867385180190169</v>
@@ -10198,13 +10198,13 @@
         <v>0.1103684814428935</v>
       </c>
       <c r="O16" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P16" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="Q16" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="R16" t="s">
         <v>10</v>
@@ -10213,16 +10213,16 @@
         <v>20</v>
       </c>
       <c r="T16" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W16" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="X16" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="Y16">
         <v>33.183</v>
@@ -10233,13 +10233,13 @@
     </row>
     <row r="17" spans="2:26">
       <c r="B17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C17" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D17" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -10248,16 +10248,16 @@
         <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J17" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K17" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="L17">
         <v>32.115075062865692</v>
@@ -10266,13 +10266,13 @@
         <v>0.2243348627558987</v>
       </c>
       <c r="O17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P17" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="Q17" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="R17" t="s">
         <v>10</v>
@@ -10281,16 +10281,16 @@
         <v>20</v>
       </c>
       <c r="T17" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W17" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="X17" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="Y17">
         <v>40.698999999999998</v>
@@ -10301,13 +10301,13 @@
     </row>
     <row r="18" spans="2:26">
       <c r="B18" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C18" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D18" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -10316,16 +10316,16 @@
         <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J18" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="K18" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="L18">
         <v>9.0868240253443027</v>
@@ -10334,13 +10334,13 @@
         <v>0.17692716652199311</v>
       </c>
       <c r="O18" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P18" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="Q18" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R18" t="s">
         <v>10</v>
@@ -10349,16 +10349,16 @@
         <v>20</v>
       </c>
       <c r="T18" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W18" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="X18" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="Y18">
         <v>43.79</v>
@@ -10369,13 +10369,13 @@
     </row>
     <row r="19" spans="2:26">
       <c r="B19" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C19" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D19" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -10384,16 +10384,16 @@
         <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J19" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="K19" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="L19">
         <v>18.016423245563796</v>
@@ -10402,13 +10402,13 @@
         <v>0.37709145338738631</v>
       </c>
       <c r="O19" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P19" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="Q19" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="R19" t="s">
         <v>10</v>
@@ -10417,16 +10417,16 @@
         <v>20</v>
       </c>
       <c r="T19" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W19" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="X19" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="Y19">
         <v>3.617</v>
@@ -10437,13 +10437,13 @@
     </row>
     <row r="20" spans="2:26">
       <c r="B20" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C20" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D20" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -10452,16 +10452,16 @@
         <v>20</v>
       </c>
       <c r="G20" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J20" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="K20" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="L20">
         <v>0.75250112047637663</v>
@@ -10470,13 +10470,13 @@
         <v>0.20583489876164651</v>
       </c>
       <c r="O20" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P20" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="Q20" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="R20" t="s">
         <v>10</v>
@@ -10485,16 +10485,16 @@
         <v>20</v>
       </c>
       <c r="T20" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W20" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="X20" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="Y20">
         <v>45.468000000000004</v>
@@ -10505,13 +10505,13 @@
     </row>
     <row r="21" spans="2:26">
       <c r="B21" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C21" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D21" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -10520,16 +10520,16 @@
         <v>20</v>
       </c>
       <c r="G21" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J21" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="K21" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="L21">
         <v>18.381813037942475</v>
@@ -10538,13 +10538,13 @@
         <v>0.21707807750595889</v>
       </c>
       <c r="O21" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P21" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="Q21" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R21" t="s">
         <v>10</v>
@@ -10553,16 +10553,16 @@
         <v>20</v>
       </c>
       <c r="T21" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W21" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="X21" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="Y21">
         <v>33.305</v>
@@ -10573,13 +10573,13 @@
     </row>
     <row r="22" spans="2:26">
       <c r="B22" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C22" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D22" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -10588,16 +10588,16 @@
         <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H22" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J22" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="K22" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="L22">
         <v>4.5221914845937041</v>
@@ -10606,13 +10606,13 @@
         <v>0.11806257993100711</v>
       </c>
       <c r="O22" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P22" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="Q22" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="R22" t="s">
         <v>10</v>
@@ -10621,16 +10621,16 @@
         <v>20</v>
       </c>
       <c r="T22" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U22" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W22" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="X22" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="Y22">
         <v>32.006</v>
@@ -10641,13 +10641,13 @@
     </row>
     <row r="23" spans="2:26">
       <c r="B23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C23" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D23" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -10656,16 +10656,16 @@
         <v>20</v>
       </c>
       <c r="G23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J23" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K23" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="L23">
         <v>8.2953562793919264</v>
@@ -10674,13 +10674,13 @@
         <v>0.1425131297827614</v>
       </c>
       <c r="O23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P23" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="Q23" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="R23" t="s">
         <v>10</v>
@@ -10689,16 +10689,16 @@
         <v>20</v>
       </c>
       <c r="T23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W23" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="X23" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Y23">
         <v>92.117999999999995</v>
@@ -10709,13 +10709,13 @@
     </row>
     <row r="24" spans="2:26">
       <c r="B24" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C24" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D24" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -10724,16 +10724,16 @@
         <v>20</v>
       </c>
       <c r="G24" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J24" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="K24" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="L24">
         <v>1.2792726734837132</v>
@@ -10742,13 +10742,13 @@
         <v>0.120834301617764</v>
       </c>
       <c r="O24" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P24" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="Q24" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="R24" t="s">
         <v>10</v>
@@ -10757,16 +10757,16 @@
         <v>20</v>
       </c>
       <c r="T24" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W24" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="X24" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="Y24">
         <v>55.912999999999997</v>
@@ -10777,13 +10777,13 @@
     </row>
     <row r="25" spans="2:26">
       <c r="B25" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C25" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D25" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -10792,16 +10792,16 @@
         <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J25" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="K25" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="L25">
         <v>1.6182682752282065</v>
@@ -10810,13 +10810,13 @@
         <v>0.1260421379882968</v>
       </c>
       <c r="O25" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P25" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="Q25" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="R25" t="s">
         <v>10</v>
@@ -10825,16 +10825,16 @@
         <v>20</v>
       </c>
       <c r="T25" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W25" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="X25" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="Y25">
         <v>164.86799999999999</v>
@@ -10845,13 +10845,13 @@
     </row>
     <row r="26" spans="2:26">
       <c r="O26" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P26" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="Q26" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="R26" t="s">
         <v>10</v>
@@ -10860,16 +10860,16 @@
         <v>20</v>
       </c>
       <c r="T26" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W26" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="X26" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="Y26">
         <v>177.54</v>
@@ -10880,13 +10880,13 @@
     </row>
     <row r="27" spans="2:26">
       <c r="O27" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P27" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="Q27" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="R27" t="s">
         <v>10</v>
@@ -10895,16 +10895,16 @@
         <v>20</v>
       </c>
       <c r="T27" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W27" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="X27" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="Y27">
         <v>234.209</v>
@@ -10915,13 +10915,13 @@
     </row>
     <row r="28" spans="2:26">
       <c r="O28" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P28" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="Q28" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="R28" t="s">
         <v>10</v>
@@ -10930,16 +10930,16 @@
         <v>20</v>
       </c>
       <c r="T28" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U28" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W28" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="X28" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="Y28">
         <v>244.34299999999999</v>
@@ -10950,13 +10950,13 @@
     </row>
     <row r="29" spans="2:26">
       <c r="O29" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P29" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="Q29" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="R29" t="s">
         <v>10</v>
@@ -10965,16 +10965,16 @@
         <v>20</v>
       </c>
       <c r="T29" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W29" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="X29" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="Y29">
         <v>96.406999999999996</v>
@@ -10985,13 +10985,13 @@
     </row>
     <row r="30" spans="2:26">
       <c r="O30" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P30" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="Q30" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="R30" t="s">
         <v>10</v>
@@ -11000,16 +11000,16 @@
         <v>20</v>
       </c>
       <c r="T30" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W30" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="X30" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="Y30">
         <v>60.06</v>
@@ -11020,13 +11020,13 @@
     </row>
     <row r="31" spans="2:26">
       <c r="O31" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P31" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="Q31" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="R31" t="s">
         <v>10</v>
@@ -11035,16 +11035,16 @@
         <v>20</v>
       </c>
       <c r="T31" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U31" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W31" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="X31" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="Y31">
         <v>142.483</v>
@@ -11055,13 +11055,13 @@
     </row>
     <row r="32" spans="2:26">
       <c r="O32" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P32" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="Q32" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="R32" t="s">
         <v>10</v>
@@ -11070,16 +11070,16 @@
         <v>20</v>
       </c>
       <c r="T32" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U32" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W32" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="X32" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="Y32">
         <v>72.956000000000003</v>
@@ -11090,13 +11090,13 @@
     </row>
     <row r="33" spans="15:26">
       <c r="O33" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P33" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="Q33" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="R33" t="s">
         <v>10</v>
@@ -11105,16 +11105,16 @@
         <v>20</v>
       </c>
       <c r="T33" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U33" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W33" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="X33" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="Y33">
         <v>19.841000000000001</v>
@@ -11125,13 +11125,13 @@
     </row>
     <row r="34" spans="15:26">
       <c r="O34" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P34" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="Q34" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="R34" t="s">
         <v>10</v>
@@ -11140,16 +11140,16 @@
         <v>20</v>
       </c>
       <c r="T34" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U34" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W34" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="X34" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="Y34">
         <v>138.42500000000001</v>
@@ -11160,13 +11160,13 @@
     </row>
     <row r="35" spans="15:26">
       <c r="O35" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P35" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="Q35" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="R35" t="s">
         <v>10</v>
@@ -11175,16 +11175,16 @@
         <v>20</v>
       </c>
       <c r="T35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U35" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W35" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="X35" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="Y35">
         <v>69.513999999999996</v>
@@ -11195,13 +11195,13 @@
     </row>
     <row r="36" spans="15:26">
       <c r="O36" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P36" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="Q36" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="R36" t="s">
         <v>10</v>
@@ -11210,16 +11210,16 @@
         <v>20</v>
       </c>
       <c r="T36" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W36" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="X36" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="Y36">
         <v>60.743000000000002</v>
@@ -11230,13 +11230,13 @@
     </row>
     <row r="37" spans="15:26">
       <c r="O37" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P37" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="Q37" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="R37" t="s">
         <v>10</v>
@@ -11245,16 +11245,16 @@
         <v>20</v>
       </c>
       <c r="T37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U37" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W37" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="X37" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="Y37">
         <v>6.194</v>
@@ -11265,13 +11265,13 @@
     </row>
     <row r="38" spans="15:26">
       <c r="O38" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P38" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="Q38" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="R38" t="s">
         <v>10</v>
@@ -11280,16 +11280,16 @@
         <v>20</v>
       </c>
       <c r="T38" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U38" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W38" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="X38" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="Y38">
         <v>44.996000000000002</v>
@@ -11300,13 +11300,13 @@
     </row>
     <row r="39" spans="15:26">
       <c r="O39" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P39" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="Q39" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="R39" t="s">
         <v>10</v>
@@ -11315,16 +11315,16 @@
         <v>20</v>
       </c>
       <c r="T39" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U39" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W39" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="X39" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="Y39">
         <v>45.517000000000003</v>
@@ -11335,13 +11335,13 @@
     </row>
     <row r="40" spans="15:26">
       <c r="O40" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P40" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="Q40" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="R40" t="s">
         <v>10</v>
@@ -11350,16 +11350,16 @@
         <v>20</v>
       </c>
       <c r="T40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U40" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W40" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="X40" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="Y40">
         <v>76.210999999999999</v>
@@ -11370,13 +11370,13 @@
     </row>
     <row r="41" spans="15:26">
       <c r="O41" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P41" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="Q41" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="R41" t="s">
         <v>10</v>
@@ -11385,16 +11385,16 @@
         <v>20</v>
       </c>
       <c r="T41" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U41" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W41" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="X41" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="Y41">
         <v>20.327999999999999</v>
@@ -11405,13 +11405,13 @@
     </row>
     <row r="42" spans="15:26">
       <c r="O42" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P42" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="Q42" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="R42" t="s">
         <v>10</v>
@@ -11420,16 +11420,16 @@
         <v>20</v>
       </c>
       <c r="T42" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U42" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W42" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="X42" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Y42">
         <v>65.320999999999998</v>
@@ -11440,13 +11440,13 @@
     </row>
     <row r="43" spans="15:26">
       <c r="O43" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P43" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Q43" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="R43" t="s">
         <v>10</v>
@@ -11455,16 +11455,16 @@
         <v>20</v>
       </c>
       <c r="T43" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="U43" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W43" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="X43" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="Y43">
         <v>32.902000000000001</v>
@@ -11485,21 +11485,21 @@
   <sheetData>
     <row r="9" spans="2:16">
       <c r="B9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="2:16">
       <c r="B10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C10" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D10" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E10">
         <v>2023</v>
@@ -11514,30 +11514,30 @@
         <v>53</v>
       </c>
       <c r="J10" t="s">
+        <v>159</v>
+      </c>
+      <c r="K10" t="s">
+        <v>160</v>
+      </c>
+      <c r="L10" t="s">
         <v>161</v>
       </c>
-      <c r="K10" t="s">
+      <c r="M10" t="s">
         <v>162</v>
       </c>
-      <c r="L10" t="s">
+      <c r="N10" t="s">
         <v>163</v>
       </c>
-      <c r="M10" t="s">
+      <c r="O10" t="s">
         <v>164</v>
       </c>
-      <c r="N10" t="s">
+      <c r="P10" t="s">
         <v>165</v>
-      </c>
-      <c r="O10" t="s">
-        <v>166</v>
-      </c>
-      <c r="P10" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="11" spans="2:16">
       <c r="B11" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C11" t="s">
         <v>30</v>
@@ -11555,13 +11555,13 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="H11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K11" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="M11" t="s">
         <v>10</v>
@@ -11570,15 +11570,15 @@
         <v>20</v>
       </c>
       <c r="O11" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P11" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C12" t="s">
         <v>30</v>
@@ -11596,13 +11596,13 @@
         <v>0.5</v>
       </c>
       <c r="H12" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="J12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K12" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="M12" t="s">
         <v>10</v>
@@ -11611,15 +11611,15 @@
         <v>20</v>
       </c>
       <c r="O12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P12" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C13" t="s">
         <v>30</v>
@@ -11637,13 +11637,13 @@
         <v>5150</v>
       </c>
       <c r="H13" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="J13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K13" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="M13" t="s">
         <v>10</v>
@@ -11652,15 +11652,15 @@
         <v>20</v>
       </c>
       <c r="O13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P13" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="B14" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C14" t="s">
         <v>30</v>
@@ -11678,13 +11678,13 @@
         <v>180</v>
       </c>
       <c r="H14" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="J14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K14" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="M14" t="s">
         <v>10</v>
@@ -11693,15 +11693,15 @@
         <v>20</v>
       </c>
       <c r="O14" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P14" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="B15" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C15" t="s">
         <v>30</v>
@@ -11719,13 +11719,13 @@
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="J15" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K15" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="M15" t="s">
         <v>10</v>
@@ -11734,15 +11734,15 @@
         <v>20</v>
       </c>
       <c r="O15" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P15" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="16" spans="2:16">
       <c r="B16" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C16" t="s">
         <v>30</v>
@@ -11760,13 +11760,13 @@
         <v>0.35000000000000003</v>
       </c>
       <c r="H16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J16" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K16" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="M16" t="s">
         <v>10</v>
@@ -11775,15 +11775,15 @@
         <v>20</v>
       </c>
       <c r="O16" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P16" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="17" spans="2:16">
       <c r="B17" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C17" t="s">
         <v>30</v>
@@ -11801,13 +11801,13 @@
         <v>0.5</v>
       </c>
       <c r="H17" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="J17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K17" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="M17" t="s">
         <v>10</v>
@@ -11816,15 +11816,15 @@
         <v>20</v>
       </c>
       <c r="O17" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P17" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="18" spans="2:16">
       <c r="B18" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C18" t="s">
         <v>30</v>
@@ -11842,13 +11842,13 @@
         <v>2400</v>
       </c>
       <c r="H18" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="J18" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K18" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="M18" t="s">
         <v>10</v>
@@ -11857,15 +11857,15 @@
         <v>20</v>
       </c>
       <c r="O18" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P18" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C19" t="s">
         <v>30</v>
@@ -11883,13 +11883,13 @@
         <v>85</v>
       </c>
       <c r="H19" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="J19" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K19" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="M19" t="s">
         <v>10</v>
@@ -11898,15 +11898,15 @@
         <v>20</v>
       </c>
       <c r="O19" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P19" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C20" t="s">
         <v>30</v>
@@ -11924,13 +11924,13 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="J20" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K20" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="M20" t="s">
         <v>10</v>
@@ -11939,15 +11939,15 @@
         <v>20</v>
       </c>
       <c r="O20" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P20" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C21" t="s">
         <v>32</v>
@@ -11965,13 +11965,13 @@
         <v>0.61</v>
       </c>
       <c r="H21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J21" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K21" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="M21" t="s">
         <v>10</v>
@@ -11980,15 +11980,15 @@
         <v>20</v>
       </c>
       <c r="O21" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P21" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="22" spans="2:16">
       <c r="B22" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C22" t="s">
         <v>32</v>
@@ -12006,13 +12006,13 @@
         <v>1000</v>
       </c>
       <c r="H22" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="J22" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K22" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="M22" t="s">
         <v>10</v>
@@ -12021,15 +12021,15 @@
         <v>20</v>
       </c>
       <c r="O22" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P22" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C23" t="s">
         <v>32</v>
@@ -12047,13 +12047,13 @@
         <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="J23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K23" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="M23" t="s">
         <v>10</v>
@@ -12062,15 +12062,15 @@
         <v>20</v>
       </c>
       <c r="O23" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P23" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="24" spans="2:16">
       <c r="B24" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C24" t="s">
         <v>32</v>
@@ -12088,13 +12088,13 @@
         <v>0.54</v>
       </c>
       <c r="H24" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J24" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K24" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="M24" t="s">
         <v>10</v>
@@ -12103,15 +12103,15 @@
         <v>20</v>
       </c>
       <c r="O24" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P24" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="25" spans="2:16">
       <c r="B25" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C25" t="s">
         <v>32</v>
@@ -12129,13 +12129,13 @@
         <v>2350</v>
       </c>
       <c r="H25" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="J25" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K25" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="M25" t="s">
         <v>10</v>
@@ -12144,15 +12144,15 @@
         <v>20</v>
       </c>
       <c r="O25" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P25" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="26" spans="2:16">
       <c r="B26" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C26" t="s">
         <v>32</v>
@@ -12170,13 +12170,13 @@
         <v>60</v>
       </c>
       <c r="H26" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="J26" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K26" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="M26" t="s">
         <v>10</v>
@@ -12185,15 +12185,15 @@
         <v>20</v>
       </c>
       <c r="O26" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P26" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C27" t="s">
         <v>31</v>
@@ -12211,13 +12211,13 @@
         <v>0.4</v>
       </c>
       <c r="H27" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J27" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K27" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="M27" t="s">
         <v>10</v>
@@ -12226,15 +12226,15 @@
         <v>20</v>
       </c>
       <c r="O27" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P27" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C28" t="s">
         <v>31</v>
@@ -12252,12 +12252,12 @@
         <v>4300</v>
       </c>
       <c r="H28" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C29" t="s">
         <v>31</v>
@@ -12275,12 +12275,12 @@
         <v>130</v>
       </c>
       <c r="H29" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -12298,12 +12298,12 @@
         <v>0.42</v>
       </c>
       <c r="H30" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31" spans="2:16">
       <c r="B31" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C31" t="s">
         <v>32</v>
@@ -12321,12 +12321,12 @@
         <v>500</v>
       </c>
       <c r="H31" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="32" spans="2:16">
       <c r="B32" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C32" t="s">
         <v>32</v>
@@ -12344,12 +12344,12 @@
         <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C33" t="s">
         <v>27</v>
@@ -12367,12 +12367,12 @@
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34" spans="2:8">
       <c r="B34" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C34" t="s">
         <v>27</v>
@@ -12390,12 +12390,12 @@
         <v>0.4</v>
       </c>
       <c r="H34" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="B35" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C35" t="s">
         <v>27</v>
@@ -12413,12 +12413,12 @@
         <v>2700</v>
       </c>
       <c r="H35" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C36" t="s">
         <v>27</v>
@@ -12436,12 +12436,12 @@
         <v>65</v>
       </c>
       <c r="H36" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C37" t="s">
         <v>27</v>
@@ -12459,12 +12459,12 @@
         <v>4</v>
       </c>
       <c r="H37" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C38" t="s">
         <v>32</v>
@@ -12482,12 +12482,12 @@
         <v>0.5</v>
       </c>
       <c r="H38" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C39" t="s">
         <v>32</v>
@@ -12505,12 +12505,12 @@
         <v>2400</v>
       </c>
       <c r="H39" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C40" t="s">
         <v>32</v>
@@ -12528,12 +12528,12 @@
         <v>85</v>
       </c>
       <c r="H40" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C41" t="s">
         <v>31</v>
@@ -12551,12 +12551,12 @@
         <v>0.43</v>
       </c>
       <c r="H41" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="42" spans="2:8">
       <c r="B42" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C42" t="s">
         <v>31</v>
@@ -12574,12 +12574,12 @@
         <v>5100</v>
       </c>
       <c r="H42" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C43" t="s">
         <v>31</v>
@@ -12597,12 +12597,12 @@
         <v>180</v>
       </c>
       <c r="H43" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C44" t="s">
         <v>35</v>
@@ -12620,12 +12620,12 @@
         <v>0.33</v>
       </c>
       <c r="H44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="45" spans="2:8">
       <c r="B45" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C45" t="s">
         <v>35</v>
@@ -12643,12 +12643,12 @@
         <v>4500</v>
       </c>
       <c r="H45" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C46" t="s">
         <v>35</v>
@@ -12666,12 +12666,12 @@
         <v>175</v>
       </c>
       <c r="H46" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="B47" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C47" t="s">
         <v>31</v>
@@ -12689,12 +12689,12 @@
         <v>0.4</v>
       </c>
       <c r="H47" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="2:8">
       <c r="B48" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C48" t="s">
         <v>31</v>
@@ -12712,12 +12712,12 @@
         <v>5150</v>
       </c>
       <c r="H48" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C49" t="s">
         <v>31</v>
@@ -12735,12 +12735,12 @@
         <v>155</v>
       </c>
       <c r="H49" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="50" spans="2:8">
       <c r="B50" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C50" t="s">
         <v>26</v>
@@ -12758,12 +12758,12 @@
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="51" spans="2:8">
       <c r="B51" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C51" t="s">
         <v>26</v>
@@ -12781,12 +12781,12 @@
         <v>0.23</v>
       </c>
       <c r="H51" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C52" t="s">
         <v>26</v>
@@ -12804,12 +12804,12 @@
         <v>480</v>
       </c>
       <c r="H52" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C53" t="s">
         <v>26</v>
@@ -12827,12 +12827,12 @@
         <v>16</v>
       </c>
       <c r="H53" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="54" spans="2:8">
       <c r="B54" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C54" t="s">
         <v>26</v>
@@ -12850,12 +12850,12 @@
         <v>1.5</v>
       </c>
       <c r="H54" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C55" t="s">
         <v>31</v>
@@ -12873,12 +12873,12 @@
         <v>0.39</v>
       </c>
       <c r="H55" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="56" spans="2:8">
       <c r="B56" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C56" t="s">
         <v>31</v>
@@ -12896,12 +12896,12 @@
         <v>1800</v>
       </c>
       <c r="H56" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="B57" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C57" t="s">
         <v>31</v>
@@ -12919,12 +12919,12 @@
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="B58" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C58" t="s">
         <v>31</v>
@@ -12942,12 +12942,12 @@
         <v>0.43</v>
       </c>
       <c r="H58" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="59" spans="2:8">
       <c r="B59" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C59" t="s">
         <v>31</v>
@@ -12965,12 +12965,12 @@
         <v>2100</v>
       </c>
       <c r="H59" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="60" spans="2:8">
       <c r="B60" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C60" t="s">
         <v>31</v>
@@ -12988,12 +12988,12 @@
         <v>65</v>
       </c>
       <c r="H60" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="B61" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C61" t="s">
         <v>31</v>
@@ -13011,12 +13011,12 @@
         <v>0.48</v>
       </c>
       <c r="H61" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="62" spans="2:8">
       <c r="B62" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C62" t="s">
         <v>31</v>
@@ -13034,12 +13034,12 @@
         <v>2300</v>
       </c>
       <c r="H62" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="B63" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C63" t="s">
         <v>31</v>
@@ -13057,15 +13057,15 @@
         <v>70</v>
       </c>
       <c r="H63" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="64" spans="2:8">
       <c r="B64" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C64" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
@@ -13080,15 +13080,15 @@
         <v>1</v>
       </c>
       <c r="H64" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="65" spans="2:8">
       <c r="B65" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C65" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D65" t="s">
         <v>19</v>
@@ -13103,15 +13103,15 @@
         <v>0.49</v>
       </c>
       <c r="H65" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="66" spans="2:8">
       <c r="B66" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C66" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
@@ -13126,15 +13126,15 @@
         <v>1980</v>
       </c>
       <c r="H66" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="67" spans="2:8">
       <c r="B67" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C67" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
@@ -13149,15 +13149,15 @@
         <v>70</v>
       </c>
       <c r="H67" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="68" spans="2:8">
       <c r="B68" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C68" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
@@ -13172,15 +13172,15 @@
         <v>3</v>
       </c>
       <c r="H68" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="69" spans="2:8">
       <c r="B69" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C69" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
@@ -13195,15 +13195,15 @@
         <v>1</v>
       </c>
       <c r="H69" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70" spans="2:8">
       <c r="B70" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C70" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D70" t="s">
         <v>19</v>
@@ -13218,15 +13218,15 @@
         <v>0.44</v>
       </c>
       <c r="H70" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C71" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D71" t="s">
         <v>19</v>
@@ -13241,15 +13241,15 @@
         <v>1370</v>
       </c>
       <c r="H71" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="72" spans="2:8">
       <c r="B72" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C72" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D72" t="s">
         <v>19</v>
@@ -13264,15 +13264,15 @@
         <v>36</v>
       </c>
       <c r="H72" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="73" spans="2:8">
       <c r="B73" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C73" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D73" t="s">
         <v>19</v>
@@ -13287,7 +13287,7 @@
         <v>1.5</v>
       </c>
       <c r="H73" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
   </sheetData>

--- a/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4691D356-DC38-4D49-859B-C5A9BE6ABE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B51EFDC-50DF-4216-AB1A-12C32B1053F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2001" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2001" uniqueCount="589">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -373,9 +373,6 @@
     </r>
   </si>
   <si>
-    <t>~FI_T: FX</t>
-  </si>
-  <si>
     <t>commodity</t>
   </si>
   <si>
@@ -1891,6 +1888,12 @@
   </si>
   <si>
     <t>\I: fossil_supply</t>
+  </si>
+  <si>
+    <t>~FI_T: FX~USD21</t>
+  </si>
+  <si>
+    <t>~fi_t: USD21</t>
   </si>
 </sst>
 </file>
@@ -3219,7 +3222,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -3270,10 +3273,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="S3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="2:22">
@@ -3346,13 +3349,13 @@
     </row>
     <row r="6" spans="2:22">
       <c r="B6" t="s">
+        <v>580</v>
+      </c>
+      <c r="C6" s="147" t="s">
         <v>581</v>
       </c>
-      <c r="C6" s="147" t="s">
-        <v>582</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>20</v>
@@ -3383,18 +3386,18 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="V6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="2:22">
       <c r="B7" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C7" s="147" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>20</v>
@@ -3413,7 +3416,7 @@
         <v>34</v>
       </c>
       <c r="L7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M7" s="1">
         <v>1</v>
@@ -3427,10 +3430,10 @@
     </row>
     <row r="8" spans="2:22">
       <c r="B8" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
@@ -3465,10 +3468,10 @@
     </row>
     <row r="9" spans="2:22">
       <c r="B9" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
@@ -3484,7 +3487,7 @@
       <c r="I9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="148" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -3499,13 +3502,13 @@
     </row>
     <row r="10" spans="2:22">
       <c r="B10" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>20</v>
@@ -3536,10 +3539,10 @@
         <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>20</v>
@@ -3574,10 +3577,10 @@
         <v>28</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>20</v>
@@ -3608,10 +3611,10 @@
         <v>28</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>20</v>
@@ -3623,7 +3626,7 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="L13" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -3641,10 +3644,10 @@
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>20</v>
@@ -3679,10 +3682,10 @@
         <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>20</v>
@@ -3727,7 +3730,7 @@
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -3755,7 +3758,7 @@
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -5088,7 +5091,7 @@
       <c r="F3" s="23"/>
       <c r="G3" s="23"/>
       <c r="H3" s="23" t="s">
-        <v>84</v>
+        <v>587</v>
       </c>
       <c r="I3" s="23"/>
       <c r="J3" s="23"/>
@@ -5127,10 +5130,10 @@
         <v>54</v>
       </c>
       <c r="G4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H4" t="s">
         <v>85</v>
-      </c>
-      <c r="H4" t="s">
-        <v>86</v>
       </c>
       <c r="I4">
         <v>2030</v>
@@ -5139,22 +5142,22 @@
         <v>0</v>
       </c>
       <c r="K4" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="L4" s="23" t="s">
         <v>87</v>
-      </c>
-      <c r="L4" s="23" t="s">
-        <v>88</v>
       </c>
       <c r="M4" s="23" t="s">
         <v>57</v>
       </c>
       <c r="N4" s="23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O4" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="P4" s="23" t="s">
         <v>89</v>
-      </c>
-      <c r="P4" s="23" t="s">
-        <v>90</v>
       </c>
       <c r="Q4" s="23"/>
       <c r="R4" s="23" t="s">
@@ -5176,18 +5179,18 @@
         <v>11</v>
       </c>
       <c r="X4" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y4" s="23" t="s">
         <v>91</v>
-      </c>
-      <c r="Y4" s="23" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="5" spans="2:25">
       <c r="B5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F5" t="s">
         <v>25</v>
@@ -5213,14 +5216,14 @@
       </c>
       <c r="Q5" s="23"/>
       <c r="R5" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S5" s="23" t="str">
         <f>B5</f>
         <v>ev_battery</v>
       </c>
       <c r="T5" s="23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U5" s="23" t="s">
         <v>20</v>
@@ -5260,7 +5263,7 @@
     <row r="7" spans="2:25">
       <c r="B7" s="23"/>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
         <v>45</v>
@@ -5351,20 +5354,20 @@
   <sheetData>
     <row r="1" spans="1:18" ht="33.75" customHeight="1">
       <c r="A1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="149" t="s">
         <v>105</v>
-      </c>
-      <c r="C1" s="149" t="s">
-        <v>106</v>
       </c>
       <c r="D1" s="149"/>
       <c r="E1" s="149"/>
       <c r="F1" s="150" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G1" s="149"/>
       <c r="H1" s="151"/>
       <c r="I1" s="149" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J1" s="149"/>
       <c r="K1" s="149"/>
@@ -5372,7 +5375,7 @@
       <c r="M1" s="149"/>
       <c r="N1" s="149"/>
       <c r="O1" s="152" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P1" s="27"/>
       <c r="Q1" s="27"/>
@@ -5380,42 +5383,42 @@
     </row>
     <row r="2" spans="1:18">
       <c r="C2" s="28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F2" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="H2" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="I2" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="H2" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="I2" s="28" t="s">
-        <v>111</v>
-      </c>
       <c r="J2" s="28" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K2" s="28" t="str">
         <f>I2</f>
         <v>input~GASNGA</v>
       </c>
       <c r="L2" s="28" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="M2" s="28" t="str">
         <f>K2</f>
         <v>input~GASNGA</v>
       </c>
       <c r="N2" s="28" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O2" s="153"/>
       <c r="P2" s="27"/>
@@ -5475,7 +5478,7 @@
         <v>2030</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F4" s="30">
         <v>2015</v>
@@ -5484,25 +5487,25 @@
         <v>2030</v>
       </c>
       <c r="H4" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="I4" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="J4" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="K4" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="K4" s="32" t="s">
+      <c r="L4" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="L4" s="33" t="s">
+      <c r="M4" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="M4" s="29" t="s">
+      <c r="N4" s="29" t="s">
         <v>117</v>
-      </c>
-      <c r="N4" s="29" t="s">
-        <v>118</v>
       </c>
       <c r="O4" s="154"/>
       <c r="P4" s="27"/>
@@ -5547,7 +5550,7 @@
         <v>9.4E-2</v>
       </c>
       <c r="O5" s="41" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P5" s="42"/>
       <c r="Q5" s="42"/>
@@ -5591,7 +5594,7 @@
         <v>1.0940000000000001</v>
       </c>
       <c r="O6" s="50" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P6" s="51"/>
       <c r="Q6" s="51"/>
@@ -5635,7 +5638,7 @@
         <v>9.4E-2</v>
       </c>
       <c r="O7" s="41" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P7" s="42"/>
       <c r="Q7" s="42"/>
@@ -5679,7 +5682,7 @@
         <v>1.17</v>
       </c>
       <c r="O8" s="50" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P8" s="51"/>
       <c r="Q8" s="51"/>
@@ -5723,7 +5726,7 @@
         <v>1.19</v>
       </c>
       <c r="O9" s="41" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P9" s="42"/>
       <c r="Q9" s="42"/>
@@ -5767,7 +5770,7 @@
         <v>1.18</v>
       </c>
       <c r="O10" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P10" s="51"/>
       <c r="Q10" s="51"/>
@@ -5811,7 +5814,7 @@
         <v>1.2</v>
       </c>
       <c r="O11" s="41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P11" s="42"/>
       <c r="Q11" s="42"/>
@@ -5855,7 +5858,7 @@
         <v>0.70799999999999996</v>
       </c>
       <c r="O12" s="50" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P12" s="51"/>
       <c r="Q12" s="51"/>
@@ -5899,7 +5902,7 @@
         <v>0.72</v>
       </c>
       <c r="O13" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P13" s="42"/>
       <c r="Q13" s="42"/>
@@ -5943,7 +5946,7 @@
         <v>0.01</v>
       </c>
       <c r="O14" s="62" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P14" s="63"/>
       <c r="Q14" s="63"/>
@@ -5987,7 +5990,7 @@
         <v>0.06</v>
       </c>
       <c r="O15" s="72" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P15" s="73"/>
       <c r="Q15" s="73"/>
@@ -6031,7 +6034,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="O16" s="82" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P16" s="83"/>
       <c r="Q16" s="83"/>
@@ -6075,7 +6078,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="72" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P17" s="73"/>
       <c r="Q17" s="73"/>
@@ -6119,7 +6122,7 @@
         <v>3.056E-2</v>
       </c>
       <c r="O18" s="92" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P18" s="93"/>
       <c r="Q18" s="93"/>
@@ -6163,7 +6166,7 @@
         <v>0.02</v>
       </c>
       <c r="O19" s="103" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P19" s="104"/>
       <c r="Q19" s="104"/>
@@ -6207,7 +6210,7 @@
         <v>1.5694083453910281</v>
       </c>
       <c r="O20" s="113" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P20" s="93"/>
       <c r="Q20" s="93"/>
@@ -6251,7 +6254,7 @@
         <v>0.3</v>
       </c>
       <c r="O21" s="122" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P21" s="123"/>
       <c r="Q21" s="123"/>
@@ -6295,7 +6298,7 @@
         <v>0.3</v>
       </c>
       <c r="O22" s="132" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P22" s="133"/>
       <c r="Q22" s="133"/>
@@ -6339,7 +6342,7 @@
         <v>0.20588235294117646</v>
       </c>
       <c r="O23" s="142" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P23" s="123"/>
       <c r="Q23" s="123"/>
@@ -6347,7 +6350,7 @@
     </row>
     <row r="26" spans="1:26" ht="17.25" thickBot="1">
       <c r="C26" s="143" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="T26" s="143" t="s">
         <v>0</v>
@@ -6389,7 +6392,7 @@
         <v>input~GASNGA~2015</v>
       </c>
       <c r="J27" s="144" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K27" s="144" t="str">
         <f t="shared" si="1"/>
@@ -6414,7 +6417,7 @@
         <v>57</v>
       </c>
       <c r="Q27" s="144" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T27" s="144" t="s">
         <v>6</v>
@@ -6435,7 +6438,7 @@
         <v>11</v>
       </c>
       <c r="Z27" s="144" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:26">
@@ -6484,7 +6487,7 @@
         <v>0.85470085470085477</v>
       </c>
       <c r="O28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P28">
         <v>25</v>
@@ -6514,7 +6517,7 @@
         <v>14</v>
       </c>
       <c r="Z28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:26">
@@ -6563,7 +6566,7 @@
         <v>0.84745762711864414</v>
       </c>
       <c r="O29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P29">
         <v>25</v>
@@ -6593,7 +6596,7 @@
         <v>14</v>
       </c>
       <c r="Z29" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -6615,203 +6618,203 @@
   <sheetData>
     <row r="9" spans="2:56">
       <c r="B9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="X9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AD9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AL9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AR9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AZ9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="2:56">
       <c r="B10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C10" t="s">
         <v>159</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>160</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>161</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>162</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>163</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>164</v>
       </c>
-      <c r="H10" t="s">
-        <v>165</v>
-      </c>
       <c r="J10" t="s">
+        <v>159</v>
+      </c>
+      <c r="K10" t="s">
+        <v>201</v>
+      </c>
+      <c r="L10" t="s">
+        <v>202</v>
+      </c>
+      <c r="M10" t="s">
+        <v>203</v>
+      </c>
+      <c r="O10" t="s">
+        <v>158</v>
+      </c>
+      <c r="P10" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q10" t="s">
         <v>160</v>
       </c>
-      <c r="K10" t="s">
-        <v>202</v>
-      </c>
-      <c r="L10" t="s">
-        <v>203</v>
-      </c>
-      <c r="M10" t="s">
-        <v>204</v>
-      </c>
-      <c r="O10" t="s">
+      <c r="R10" t="s">
+        <v>161</v>
+      </c>
+      <c r="S10" t="s">
+        <v>162</v>
+      </c>
+      <c r="T10" t="s">
+        <v>220</v>
+      </c>
+      <c r="U10" t="s">
+        <v>163</v>
+      </c>
+      <c r="V10" t="s">
+        <v>164</v>
+      </c>
+      <c r="X10" t="s">
         <v>159</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Y10" t="s">
+        <v>256</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>201</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>142</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>257</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>159</v>
+      </c>
+      <c r="AF10" t="s">
         <v>160</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="AG10" t="s">
         <v>161</v>
       </c>
-      <c r="R10" t="s">
+      <c r="AH10" t="s">
         <v>162</v>
       </c>
-      <c r="S10" t="s">
+      <c r="AI10" t="s">
         <v>163</v>
       </c>
-      <c r="T10" t="s">
-        <v>221</v>
-      </c>
-      <c r="U10" t="s">
+      <c r="AJ10" t="s">
         <v>164</v>
       </c>
-      <c r="V10" t="s">
-        <v>165</v>
-      </c>
-      <c r="X10" t="s">
+      <c r="AL10" t="s">
+        <v>159</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>256</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>201</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>142</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>257</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>158</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>159</v>
+      </c>
+      <c r="AT10" t="s">
         <v>160</v>
       </c>
-      <c r="Y10" t="s">
+      <c r="AU10" t="s">
+        <v>161</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>162</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>163</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>164</v>
+      </c>
+      <c r="AZ10" t="s">
+        <v>159</v>
+      </c>
+      <c r="BA10" t="s">
+        <v>256</v>
+      </c>
+      <c r="BB10" t="s">
+        <v>201</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>142</v>
+      </c>
+      <c r="BD10" t="s">
         <v>257</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>202</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>143</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>258</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>159</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>160</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>161</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>162</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>163</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>164</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>165</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>160</v>
-      </c>
-      <c r="AM10" t="s">
-        <v>257</v>
-      </c>
-      <c r="AN10" t="s">
-        <v>202</v>
-      </c>
-      <c r="AO10" t="s">
-        <v>143</v>
-      </c>
-      <c r="AP10" t="s">
-        <v>258</v>
-      </c>
-      <c r="AR10" t="s">
-        <v>159</v>
-      </c>
-      <c r="AS10" t="s">
-        <v>160</v>
-      </c>
-      <c r="AT10" t="s">
-        <v>161</v>
-      </c>
-      <c r="AU10" t="s">
-        <v>162</v>
-      </c>
-      <c r="AV10" t="s">
-        <v>163</v>
-      </c>
-      <c r="AW10" t="s">
-        <v>164</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>165</v>
-      </c>
-      <c r="AZ10" t="s">
-        <v>160</v>
-      </c>
-      <c r="BA10" t="s">
-        <v>257</v>
-      </c>
-      <c r="BB10" t="s">
-        <v>202</v>
-      </c>
-      <c r="BC10" t="s">
-        <v>143</v>
-      </c>
-      <c r="BD10" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="11" spans="2:56">
       <c r="B11" t="s">
+        <v>165</v>
+      </c>
+      <c r="C11" t="s">
         <v>166</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>167</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" t="s">
         <v>168</v>
       </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>169</v>
       </c>
-      <c r="H11" t="s">
-        <v>170</v>
-      </c>
       <c r="J11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L11">
         <v>14.703515544593534</v>
@@ -6820,37 +6823,37 @@
         <v>0.18394567124097769</v>
       </c>
       <c r="O11" t="s">
+        <v>221</v>
+      </c>
+      <c r="P11" t="s">
         <v>222</v>
       </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
         <v>223</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="R11" t="s">
+        <v>10</v>
+      </c>
+      <c r="S11" t="s">
+        <v>20</v>
+      </c>
+      <c r="T11" t="s">
         <v>224</v>
       </c>
-      <c r="R11" t="s">
-        <v>10</v>
-      </c>
-      <c r="S11" t="s">
-        <v>20</v>
-      </c>
-      <c r="T11" t="s">
+      <c r="U11" t="s">
         <v>225</v>
       </c>
-      <c r="U11" t="s">
-        <v>226</v>
-      </c>
       <c r="V11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="X11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Z11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AA11">
         <v>0.99781284363204548</v>
@@ -6859,14 +6862,14 @@
         <v>40.097866745833329</v>
       </c>
       <c r="AD11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AE11" t="s">
+        <v>274</v>
+      </c>
+      <c r="AF11" t="s">
         <v>275</v>
       </c>
-      <c r="AF11" t="s">
-        <v>276</v>
-      </c>
       <c r="AG11" t="s">
         <v>10</v>
       </c>
@@ -6874,19 +6877,19 @@
         <v>20</v>
       </c>
       <c r="AI11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AJ11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AL11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AM11" t="s">
+        <v>304</v>
+      </c>
+      <c r="AN11" t="s">
         <v>305</v>
-      </c>
-      <c r="AN11" t="s">
-        <v>306</v>
       </c>
       <c r="AO11">
         <v>0.99692224665834439</v>
@@ -6895,14 +6898,14 @@
         <v>56.425477930352955</v>
       </c>
       <c r="AR11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS11" t="s">
+        <v>333</v>
+      </c>
+      <c r="AT11" t="s">
         <v>334</v>
       </c>
-      <c r="AT11" t="s">
-        <v>335</v>
-      </c>
       <c r="AU11" t="s">
         <v>10</v>
       </c>
@@ -6910,19 +6913,19 @@
         <v>20</v>
       </c>
       <c r="AW11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ11" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="BA11" t="s">
+        <v>399</v>
+      </c>
+      <c r="BB11" t="s">
         <v>400</v>
-      </c>
-      <c r="BB11" t="s">
-        <v>401</v>
       </c>
       <c r="BC11">
         <v>0.9878288138539939</v>
@@ -6933,14 +6936,14 @@
     </row>
     <row r="12" spans="2:56">
       <c r="B12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" t="s">
         <v>171</v>
       </c>
-      <c r="D12" t="s">
-        <v>172</v>
-      </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
@@ -6948,16 +6951,16 @@
         <v>20</v>
       </c>
       <c r="G12" t="s">
+        <v>168</v>
+      </c>
+      <c r="H12" t="s">
         <v>169</v>
       </c>
-      <c r="H12" t="s">
+      <c r="J12" t="s">
         <v>170</v>
       </c>
-      <c r="J12" t="s">
-        <v>171</v>
-      </c>
       <c r="K12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L12">
         <v>7.0247960503319238</v>
@@ -6966,14 +6969,14 @@
         <v>0.1895344528514209</v>
       </c>
       <c r="O12" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P12" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q12" t="s">
         <v>227</v>
       </c>
-      <c r="Q12" t="s">
-        <v>228</v>
-      </c>
       <c r="R12" t="s">
         <v>10</v>
       </c>
@@ -6981,22 +6984,22 @@
         <v>20</v>
       </c>
       <c r="T12" t="s">
+        <v>224</v>
+      </c>
+      <c r="U12" t="s">
         <v>225</v>
       </c>
-      <c r="U12" t="s">
+      <c r="V12" t="s">
+        <v>169</v>
+      </c>
+      <c r="X12" t="s">
         <v>226</v>
       </c>
-      <c r="V12" t="s">
-        <v>170</v>
-      </c>
-      <c r="X12" t="s">
-        <v>227</v>
-      </c>
       <c r="Y12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Z12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AA12">
         <v>0.99164479201276912</v>
@@ -7005,14 +7008,14 @@
         <v>153.17881309923388</v>
       </c>
       <c r="AD12" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AE12" t="s">
+        <v>276</v>
+      </c>
+      <c r="AF12" t="s">
         <v>277</v>
       </c>
-      <c r="AF12" t="s">
-        <v>278</v>
-      </c>
       <c r="AG12" t="s">
         <v>10</v>
       </c>
@@ -7020,19 +7023,19 @@
         <v>20</v>
       </c>
       <c r="AI12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AJ12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AL12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AM12" t="s">
+        <v>306</v>
+      </c>
+      <c r="AN12" t="s">
         <v>307</v>
-      </c>
-      <c r="AN12" t="s">
-        <v>308</v>
       </c>
       <c r="AO12">
         <v>0.99590345602074126</v>
@@ -7041,14 +7044,14 @@
         <v>75.103306286410302</v>
       </c>
       <c r="AR12" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS12" t="s">
+        <v>335</v>
+      </c>
+      <c r="AT12" t="s">
         <v>336</v>
       </c>
-      <c r="AT12" t="s">
-        <v>337</v>
-      </c>
       <c r="AU12" t="s">
         <v>10</v>
       </c>
@@ -7056,19 +7059,19 @@
         <v>20</v>
       </c>
       <c r="AW12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="BA12" t="s">
+        <v>401</v>
+      </c>
+      <c r="BB12" t="s">
         <v>402</v>
-      </c>
-      <c r="BB12" t="s">
-        <v>403</v>
       </c>
       <c r="BC12">
         <v>0.98395883577792953</v>
@@ -7079,14 +7082,14 @@
     </row>
     <row r="13" spans="2:56">
       <c r="B13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C13" t="s">
+        <v>172</v>
+      </c>
+      <c r="D13" t="s">
         <v>173</v>
       </c>
-      <c r="D13" t="s">
-        <v>174</v>
-      </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
@@ -7094,16 +7097,16 @@
         <v>20</v>
       </c>
       <c r="G13" t="s">
+        <v>168</v>
+      </c>
+      <c r="H13" t="s">
         <v>169</v>
       </c>
-      <c r="H13" t="s">
-        <v>170</v>
-      </c>
       <c r="J13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L13">
         <v>12.174517979652411</v>
@@ -7112,14 +7115,14 @@
         <v>0.18533082336913481</v>
       </c>
       <c r="O13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P13" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q13" t="s">
         <v>229</v>
       </c>
-      <c r="Q13" t="s">
-        <v>230</v>
-      </c>
       <c r="R13" t="s">
         <v>10</v>
       </c>
@@ -7127,22 +7130,22 @@
         <v>20</v>
       </c>
       <c r="T13" t="s">
+        <v>224</v>
+      </c>
+      <c r="U13" t="s">
         <v>225</v>
       </c>
-      <c r="U13" t="s">
-        <v>226</v>
-      </c>
       <c r="V13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="X13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Y13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Z13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AA13">
         <v>0.99568371668484024</v>
@@ -7151,14 +7154,14 @@
         <v>79.131860777928608</v>
       </c>
       <c r="AD13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AE13" t="s">
+        <v>278</v>
+      </c>
+      <c r="AF13" t="s">
         <v>279</v>
       </c>
-      <c r="AF13" t="s">
-        <v>280</v>
-      </c>
       <c r="AG13" t="s">
         <v>10</v>
       </c>
@@ -7166,19 +7169,19 @@
         <v>20</v>
       </c>
       <c r="AI13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AJ13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AL13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AM13" t="s">
+        <v>308</v>
+      </c>
+      <c r="AN13" t="s">
         <v>309</v>
-      </c>
-      <c r="AN13" t="s">
-        <v>310</v>
       </c>
       <c r="AO13">
         <v>0.9975157188831717</v>
@@ -7187,14 +7190,14 @@
         <v>45.545153808519316</v>
       </c>
       <c r="AR13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS13" t="s">
+        <v>337</v>
+      </c>
+      <c r="AT13" t="s">
         <v>338</v>
       </c>
-      <c r="AT13" t="s">
-        <v>339</v>
-      </c>
       <c r="AU13" t="s">
         <v>10</v>
       </c>
@@ -7202,19 +7205,19 @@
         <v>20</v>
       </c>
       <c r="AW13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ13" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="BA13" t="s">
+        <v>403</v>
+      </c>
+      <c r="BB13" t="s">
         <v>404</v>
-      </c>
-      <c r="BB13" t="s">
-        <v>405</v>
       </c>
       <c r="BC13">
         <v>0.94957327345368925</v>
@@ -7225,14 +7228,14 @@
     </row>
     <row r="14" spans="2:56">
       <c r="B14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C14" t="s">
+        <v>174</v>
+      </c>
+      <c r="D14" t="s">
         <v>175</v>
       </c>
-      <c r="D14" t="s">
-        <v>176</v>
-      </c>
       <c r="E14" t="s">
         <v>10</v>
       </c>
@@ -7240,16 +7243,16 @@
         <v>20</v>
       </c>
       <c r="G14" t="s">
+        <v>168</v>
+      </c>
+      <c r="H14" t="s">
         <v>169</v>
       </c>
-      <c r="H14" t="s">
-        <v>170</v>
-      </c>
       <c r="J14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L14">
         <v>8.646134759765264</v>
@@ -7258,14 +7261,14 @@
         <v>0.18564315469610329</v>
       </c>
       <c r="O14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P14" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q14" t="s">
         <v>231</v>
       </c>
-      <c r="Q14" t="s">
-        <v>232</v>
-      </c>
       <c r="R14" t="s">
         <v>10</v>
       </c>
@@ -7273,22 +7276,22 @@
         <v>20</v>
       </c>
       <c r="T14" t="s">
+        <v>224</v>
+      </c>
+      <c r="U14" t="s">
         <v>225</v>
       </c>
-      <c r="U14" t="s">
-        <v>226</v>
-      </c>
       <c r="V14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="X14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Y14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Z14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AA14">
         <v>0.99673728461460676</v>
@@ -7297,14 +7300,14 @@
         <v>59.816448732209111</v>
       </c>
       <c r="AD14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AE14" t="s">
+        <v>280</v>
+      </c>
+      <c r="AF14" t="s">
         <v>281</v>
       </c>
-      <c r="AF14" t="s">
-        <v>282</v>
-      </c>
       <c r="AG14" t="s">
         <v>10</v>
       </c>
@@ -7312,19 +7315,19 @@
         <v>20</v>
       </c>
       <c r="AI14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AJ14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AL14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AM14" t="s">
+        <v>310</v>
+      </c>
+      <c r="AN14" t="s">
         <v>311</v>
-      </c>
-      <c r="AN14" t="s">
-        <v>312</v>
       </c>
       <c r="AO14">
         <v>0.99725701149052537</v>
@@ -7333,14 +7336,14 @@
         <v>50.288122673700855</v>
       </c>
       <c r="AR14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS14" t="s">
+        <v>339</v>
+      </c>
+      <c r="AT14" t="s">
         <v>340</v>
       </c>
-      <c r="AT14" t="s">
-        <v>341</v>
-      </c>
       <c r="AU14" t="s">
         <v>10</v>
       </c>
@@ -7348,19 +7351,19 @@
         <v>20</v>
       </c>
       <c r="AW14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ14" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="BA14" t="s">
+        <v>405</v>
+      </c>
+      <c r="BB14" t="s">
         <v>406</v>
-      </c>
-      <c r="BB14" t="s">
-        <v>407</v>
       </c>
       <c r="BC14">
         <v>0.98560960960201449</v>
@@ -7371,14 +7374,14 @@
     </row>
     <row r="15" spans="2:56">
       <c r="B15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C15" t="s">
+        <v>176</v>
+      </c>
+      <c r="D15" t="s">
         <v>177</v>
       </c>
-      <c r="D15" t="s">
-        <v>178</v>
-      </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
@@ -7386,16 +7389,16 @@
         <v>20</v>
       </c>
       <c r="G15" t="s">
+        <v>168</v>
+      </c>
+      <c r="H15" t="s">
         <v>169</v>
       </c>
-      <c r="H15" t="s">
-        <v>170</v>
-      </c>
       <c r="J15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L15">
         <v>10.978710703279315</v>
@@ -7404,14 +7407,14 @@
         <v>0.1751830539964257</v>
       </c>
       <c r="O15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P15" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q15" t="s">
         <v>233</v>
       </c>
-      <c r="Q15" t="s">
-        <v>234</v>
-      </c>
       <c r="R15" t="s">
         <v>10</v>
       </c>
@@ -7419,22 +7422,22 @@
         <v>20</v>
       </c>
       <c r="T15" t="s">
+        <v>224</v>
+      </c>
+      <c r="U15" t="s">
         <v>225</v>
       </c>
-      <c r="U15" t="s">
-        <v>226</v>
-      </c>
       <c r="V15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="X15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Y15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Z15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AA15">
         <v>0.99709164861435029</v>
@@ -7443,14 +7446,14 @@
         <v>53.319775403577559</v>
       </c>
       <c r="AD15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AE15" t="s">
+        <v>282</v>
+      </c>
+      <c r="AF15" t="s">
         <v>283</v>
       </c>
-      <c r="AF15" t="s">
-        <v>284</v>
-      </c>
       <c r="AG15" t="s">
         <v>10</v>
       </c>
@@ -7458,19 +7461,19 @@
         <v>20</v>
       </c>
       <c r="AI15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AJ15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AL15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AM15" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AN15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AO15">
         <v>0.99595483459575906</v>
@@ -7479,14 +7482,14 @@
         <v>74.161365744417125</v>
       </c>
       <c r="AR15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS15" t="s">
+        <v>341</v>
+      </c>
+      <c r="AT15" t="s">
         <v>342</v>
       </c>
-      <c r="AT15" t="s">
-        <v>343</v>
-      </c>
       <c r="AU15" t="s">
         <v>10</v>
       </c>
@@ -7494,19 +7497,19 @@
         <v>20</v>
       </c>
       <c r="AW15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ15" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="BA15" t="s">
+        <v>407</v>
+      </c>
+      <c r="BB15" t="s">
         <v>408</v>
-      </c>
-      <c r="BB15" t="s">
-        <v>409</v>
       </c>
       <c r="BC15">
         <v>0.99053075643264799</v>
@@ -7517,14 +7520,14 @@
     </row>
     <row r="16" spans="2:56">
       <c r="B16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C16" t="s">
+        <v>178</v>
+      </c>
+      <c r="D16" t="s">
         <v>179</v>
       </c>
-      <c r="D16" t="s">
-        <v>180</v>
-      </c>
       <c r="E16" t="s">
         <v>10</v>
       </c>
@@ -7532,16 +7535,16 @@
         <v>20</v>
       </c>
       <c r="G16" t="s">
+        <v>168</v>
+      </c>
+      <c r="H16" t="s">
         <v>169</v>
       </c>
-      <c r="H16" t="s">
-        <v>170</v>
-      </c>
       <c r="J16" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L16">
         <v>13.930117028134356</v>
@@ -7550,14 +7553,14 @@
         <v>0.18239756272718469</v>
       </c>
       <c r="O16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P16" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q16" t="s">
         <v>235</v>
       </c>
-      <c r="Q16" t="s">
-        <v>236</v>
-      </c>
       <c r="R16" t="s">
         <v>10</v>
       </c>
@@ -7565,22 +7568,22 @@
         <v>20</v>
       </c>
       <c r="T16" t="s">
+        <v>224</v>
+      </c>
+      <c r="U16" t="s">
         <v>225</v>
       </c>
-      <c r="U16" t="s">
-        <v>226</v>
-      </c>
       <c r="V16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="X16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Y16" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Z16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AA16">
         <v>0.99552574319771747</v>
@@ -7589,14 +7592,14 @@
         <v>82.028041375179441</v>
       </c>
       <c r="AD16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AE16" t="s">
+        <v>284</v>
+      </c>
+      <c r="AF16" t="s">
         <v>285</v>
       </c>
-      <c r="AF16" t="s">
-        <v>286</v>
-      </c>
       <c r="AG16" t="s">
         <v>10</v>
       </c>
@@ -7604,19 +7607,19 @@
         <v>20</v>
       </c>
       <c r="AI16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AJ16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AL16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AM16" t="s">
+        <v>313</v>
+      </c>
+      <c r="AN16" t="s">
         <v>314</v>
-      </c>
-      <c r="AN16" t="s">
-        <v>315</v>
       </c>
       <c r="AO16">
         <v>0.99761292756299069</v>
@@ -7625,14 +7628,14 @@
         <v>43.762994678503716</v>
       </c>
       <c r="AR16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS16" t="s">
+        <v>343</v>
+      </c>
+      <c r="AT16" t="s">
         <v>344</v>
       </c>
-      <c r="AT16" t="s">
-        <v>345</v>
-      </c>
       <c r="AU16" t="s">
         <v>10</v>
       </c>
@@ -7640,19 +7643,19 @@
         <v>20</v>
       </c>
       <c r="AW16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ16" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="BA16" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="BB16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="BC16">
         <v>0.98974923036021278</v>
@@ -7663,14 +7666,14 @@
     </row>
     <row r="17" spans="2:56">
       <c r="B17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C17" t="s">
+        <v>180</v>
+      </c>
+      <c r="D17" t="s">
         <v>181</v>
       </c>
-      <c r="D17" t="s">
-        <v>182</v>
-      </c>
       <c r="E17" t="s">
         <v>10</v>
       </c>
@@ -7678,16 +7681,16 @@
         <v>20</v>
       </c>
       <c r="G17" t="s">
+        <v>168</v>
+      </c>
+      <c r="H17" t="s">
         <v>169</v>
       </c>
-      <c r="H17" t="s">
-        <v>170</v>
-      </c>
       <c r="J17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L17">
         <v>7.7139766429685555</v>
@@ -7696,14 +7699,14 @@
         <v>0.16714441187363149</v>
       </c>
       <c r="O17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P17" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q17" t="s">
         <v>237</v>
       </c>
-      <c r="Q17" t="s">
-        <v>238</v>
-      </c>
       <c r="R17" t="s">
         <v>10</v>
       </c>
@@ -7711,22 +7714,22 @@
         <v>20</v>
       </c>
       <c r="T17" t="s">
+        <v>224</v>
+      </c>
+      <c r="U17" t="s">
         <v>225</v>
       </c>
-      <c r="U17" t="s">
-        <v>226</v>
-      </c>
       <c r="V17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="X17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Y17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Z17" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AA17">
         <v>0.99856414548474748</v>
@@ -7735,14 +7738,14 @@
         <v>26.323999446296273</v>
       </c>
       <c r="AD17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AE17" t="s">
+        <v>286</v>
+      </c>
+      <c r="AF17" t="s">
         <v>287</v>
       </c>
-      <c r="AF17" t="s">
-        <v>288</v>
-      </c>
       <c r="AG17" t="s">
         <v>10</v>
       </c>
@@ -7750,19 +7753,19 @@
         <v>20</v>
       </c>
       <c r="AI17" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AJ17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AL17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AM17" t="s">
+        <v>315</v>
+      </c>
+      <c r="AN17" t="s">
         <v>316</v>
-      </c>
-      <c r="AN17" t="s">
-        <v>317</v>
       </c>
       <c r="AO17">
         <v>0.99446613913875159</v>
@@ -7771,14 +7774,14 @@
         <v>101.45411578955439</v>
       </c>
       <c r="AR17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS17" t="s">
+        <v>345</v>
+      </c>
+      <c r="AT17" t="s">
         <v>346</v>
       </c>
-      <c r="AT17" t="s">
-        <v>347</v>
-      </c>
       <c r="AU17" t="s">
         <v>10</v>
       </c>
@@ -7786,19 +7789,19 @@
         <v>20</v>
       </c>
       <c r="AW17" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ17" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="BA17" t="s">
+        <v>410</v>
+      </c>
+      <c r="BB17" t="s">
         <v>411</v>
-      </c>
-      <c r="BB17" t="s">
-        <v>412</v>
       </c>
       <c r="BC17">
         <v>0.99439449087123744</v>
@@ -7809,14 +7812,14 @@
     </row>
     <row r="18" spans="2:56">
       <c r="B18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C18" t="s">
+        <v>182</v>
+      </c>
+      <c r="D18" t="s">
         <v>183</v>
       </c>
-      <c r="D18" t="s">
-        <v>184</v>
-      </c>
       <c r="E18" t="s">
         <v>10</v>
       </c>
@@ -7824,16 +7827,16 @@
         <v>20</v>
       </c>
       <c r="G18" t="s">
+        <v>168</v>
+      </c>
+      <c r="H18" t="s">
         <v>169</v>
       </c>
-      <c r="H18" t="s">
-        <v>170</v>
-      </c>
       <c r="J18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K18" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L18">
         <v>13.532966068581743</v>
@@ -7842,14 +7845,14 @@
         <v>0.15443081133819789</v>
       </c>
       <c r="O18" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P18" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q18" t="s">
         <v>239</v>
       </c>
-      <c r="Q18" t="s">
-        <v>240</v>
-      </c>
       <c r="R18" t="s">
         <v>10</v>
       </c>
@@ -7857,22 +7860,22 @@
         <v>20</v>
       </c>
       <c r="T18" t="s">
+        <v>224</v>
+      </c>
+      <c r="U18" t="s">
         <v>225</v>
       </c>
-      <c r="U18" t="s">
-        <v>226</v>
-      </c>
       <c r="V18" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="X18" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Y18" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Z18" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AA18">
         <v>0.99837169372341228</v>
@@ -7881,14 +7884,14 @@
         <v>29.852281737441412</v>
       </c>
       <c r="AD18" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AE18" t="s">
+        <v>288</v>
+      </c>
+      <c r="AF18" t="s">
         <v>289</v>
       </c>
-      <c r="AF18" t="s">
-        <v>290</v>
-      </c>
       <c r="AG18" t="s">
         <v>10</v>
       </c>
@@ -7896,19 +7899,19 @@
         <v>20</v>
       </c>
       <c r="AI18" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AJ18" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AL18" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AM18" t="s">
+        <v>317</v>
+      </c>
+      <c r="AN18" t="s">
         <v>318</v>
-      </c>
-      <c r="AN18" t="s">
-        <v>319</v>
       </c>
       <c r="AO18">
         <v>0.99821201020674788</v>
@@ -7917,14 +7920,14 @@
         <v>32.77981287628851</v>
       </c>
       <c r="AR18" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS18" t="s">
+        <v>347</v>
+      </c>
+      <c r="AT18" t="s">
         <v>348</v>
       </c>
-      <c r="AT18" t="s">
-        <v>349</v>
-      </c>
       <c r="AU18" t="s">
         <v>10</v>
       </c>
@@ -7932,19 +7935,19 @@
         <v>20</v>
       </c>
       <c r="AW18" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX18" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ18" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BA18" t="s">
+        <v>412</v>
+      </c>
+      <c r="BB18" t="s">
         <v>413</v>
-      </c>
-      <c r="BB18" t="s">
-        <v>414</v>
       </c>
       <c r="BC18">
         <v>0.9960370911532308</v>
@@ -7955,14 +7958,14 @@
     </row>
     <row r="19" spans="2:56">
       <c r="B19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C19" t="s">
+        <v>184</v>
+      </c>
+      <c r="D19" t="s">
         <v>185</v>
       </c>
-      <c r="D19" t="s">
-        <v>186</v>
-      </c>
       <c r="E19" t="s">
         <v>10</v>
       </c>
@@ -7970,16 +7973,16 @@
         <v>20</v>
       </c>
       <c r="G19" t="s">
+        <v>168</v>
+      </c>
+      <c r="H19" t="s">
         <v>169</v>
       </c>
-      <c r="H19" t="s">
-        <v>170</v>
-      </c>
       <c r="J19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L19">
         <v>0.30791874242419603</v>
@@ -7988,14 +7991,14 @@
         <v>0.15242372922965119</v>
       </c>
       <c r="O19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P19" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q19" t="s">
         <v>241</v>
       </c>
-      <c r="Q19" t="s">
-        <v>242</v>
-      </c>
       <c r="R19" t="s">
         <v>10</v>
       </c>
@@ -8003,22 +8006,22 @@
         <v>20</v>
       </c>
       <c r="T19" t="s">
+        <v>224</v>
+      </c>
+      <c r="U19" t="s">
         <v>225</v>
       </c>
-      <c r="U19" t="s">
-        <v>226</v>
-      </c>
       <c r="V19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="X19" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Y19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Z19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AA19">
         <v>0.99541580702824473</v>
@@ -8027,14 +8030,14 @@
         <v>84.0435378155141</v>
       </c>
       <c r="AD19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AE19" t="s">
+        <v>290</v>
+      </c>
+      <c r="AF19" t="s">
         <v>291</v>
       </c>
-      <c r="AF19" t="s">
-        <v>292</v>
-      </c>
       <c r="AG19" t="s">
         <v>10</v>
       </c>
@@ -8042,19 +8045,19 @@
         <v>20</v>
       </c>
       <c r="AI19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AJ19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AL19" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AM19" t="s">
+        <v>319</v>
+      </c>
+      <c r="AN19" t="s">
         <v>320</v>
-      </c>
-      <c r="AN19" t="s">
-        <v>321</v>
       </c>
       <c r="AO19">
         <v>0.99562511313409086</v>
@@ -8063,14 +8066,14 @@
         <v>80.206259208334231</v>
       </c>
       <c r="AR19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS19" t="s">
+        <v>349</v>
+      </c>
+      <c r="AT19" t="s">
         <v>350</v>
       </c>
-      <c r="AT19" t="s">
-        <v>351</v>
-      </c>
       <c r="AU19" t="s">
         <v>10</v>
       </c>
@@ -8078,19 +8081,19 @@
         <v>20</v>
       </c>
       <c r="AW19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ19" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="BA19" t="s">
+        <v>414</v>
+      </c>
+      <c r="BB19" t="s">
         <v>415</v>
-      </c>
-      <c r="BB19" t="s">
-        <v>416</v>
       </c>
       <c r="BC19">
         <v>0.98596601099553871</v>
@@ -8101,14 +8104,14 @@
     </row>
     <row r="20" spans="2:56">
       <c r="B20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C20" t="s">
+        <v>186</v>
+      </c>
+      <c r="D20" t="s">
         <v>187</v>
       </c>
-      <c r="D20" t="s">
-        <v>188</v>
-      </c>
       <c r="E20" t="s">
         <v>10</v>
       </c>
@@ -8116,16 +8119,16 @@
         <v>20</v>
       </c>
       <c r="G20" t="s">
+        <v>168</v>
+      </c>
+      <c r="H20" t="s">
         <v>169</v>
       </c>
-      <c r="H20" t="s">
-        <v>170</v>
-      </c>
       <c r="J20" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K20" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L20">
         <v>3.0931829905152187E-2</v>
@@ -8134,14 +8137,14 @@
         <v>0.13596321535260519</v>
       </c>
       <c r="O20" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P20" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q20" t="s">
         <v>243</v>
       </c>
-      <c r="Q20" t="s">
-        <v>244</v>
-      </c>
       <c r="R20" t="s">
         <v>10</v>
       </c>
@@ -8149,22 +8152,22 @@
         <v>20</v>
       </c>
       <c r="T20" t="s">
+        <v>224</v>
+      </c>
+      <c r="U20" t="s">
         <v>225</v>
       </c>
-      <c r="U20" t="s">
-        <v>226</v>
-      </c>
       <c r="V20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="X20" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Y20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Z20" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AA20">
         <v>0.9981722170039925</v>
@@ -8173,14 +8176,14 @@
         <v>33.509354926805031</v>
       </c>
       <c r="AD20" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AE20" t="s">
+        <v>292</v>
+      </c>
+      <c r="AF20" t="s">
         <v>293</v>
       </c>
-      <c r="AF20" t="s">
-        <v>294</v>
-      </c>
       <c r="AG20" t="s">
         <v>10</v>
       </c>
@@ -8188,19 +8191,19 @@
         <v>20</v>
       </c>
       <c r="AI20" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AJ20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AL20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AM20" t="s">
+        <v>321</v>
+      </c>
+      <c r="AN20" t="s">
         <v>322</v>
-      </c>
-      <c r="AN20" t="s">
-        <v>323</v>
       </c>
       <c r="AO20">
         <v>0.99857516825685033</v>
@@ -8209,14 +8212,14 @@
         <v>26.121915291078167</v>
       </c>
       <c r="AR20" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS20" t="s">
+        <v>351</v>
+      </c>
+      <c r="AT20" t="s">
         <v>352</v>
       </c>
-      <c r="AT20" t="s">
-        <v>353</v>
-      </c>
       <c r="AU20" t="s">
         <v>10</v>
       </c>
@@ -8224,19 +8227,19 @@
         <v>20</v>
       </c>
       <c r="AW20" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="BA20" t="s">
+        <v>416</v>
+      </c>
+      <c r="BB20" t="s">
         <v>417</v>
-      </c>
-      <c r="BB20" t="s">
-        <v>418</v>
       </c>
       <c r="BC20">
         <v>0.96328479701100822</v>
@@ -8247,14 +8250,14 @@
     </row>
     <row r="21" spans="2:56">
       <c r="B21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C21" t="s">
+        <v>188</v>
+      </c>
+      <c r="D21" t="s">
         <v>189</v>
       </c>
-      <c r="D21" t="s">
-        <v>190</v>
-      </c>
       <c r="E21" t="s">
         <v>10</v>
       </c>
@@ -8262,16 +8265,16 @@
         <v>20</v>
       </c>
       <c r="G21" t="s">
+        <v>168</v>
+      </c>
+      <c r="H21" t="s">
         <v>169</v>
       </c>
-      <c r="H21" t="s">
-        <v>170</v>
-      </c>
       <c r="J21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L21">
         <v>7.2737697525181089</v>
@@ -8280,14 +8283,14 @@
         <v>0.1484590937756623</v>
       </c>
       <c r="O21" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P21" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q21" t="s">
         <v>245</v>
       </c>
-      <c r="Q21" t="s">
-        <v>246</v>
-      </c>
       <c r="R21" t="s">
         <v>10</v>
       </c>
@@ -8295,22 +8298,22 @@
         <v>20</v>
       </c>
       <c r="T21" t="s">
+        <v>224</v>
+      </c>
+      <c r="U21" t="s">
         <v>225</v>
       </c>
-      <c r="U21" t="s">
-        <v>226</v>
-      </c>
       <c r="V21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="X21" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Y21" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Z21" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AA21">
         <v>0.99757939258365447</v>
@@ -8319,14 +8322,14 @@
         <v>44.377802633000776</v>
       </c>
       <c r="AD21" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AE21" t="s">
+        <v>294</v>
+      </c>
+      <c r="AF21" t="s">
         <v>295</v>
       </c>
-      <c r="AF21" t="s">
-        <v>296</v>
-      </c>
       <c r="AG21" t="s">
         <v>10</v>
       </c>
@@ -8334,19 +8337,19 @@
         <v>20</v>
       </c>
       <c r="AI21" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AJ21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AL21" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AM21" t="s">
+        <v>323</v>
+      </c>
+      <c r="AN21" t="s">
         <v>324</v>
-      </c>
-      <c r="AN21" t="s">
-        <v>325</v>
       </c>
       <c r="AO21">
         <v>0.99624198670989172</v>
@@ -8355,14 +8358,14 @@
         <v>68.896910318651507</v>
       </c>
       <c r="AR21" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS21" t="s">
+        <v>353</v>
+      </c>
+      <c r="AT21" t="s">
         <v>354</v>
       </c>
-      <c r="AT21" t="s">
-        <v>355</v>
-      </c>
       <c r="AU21" t="s">
         <v>10</v>
       </c>
@@ -8370,19 +8373,19 @@
         <v>20</v>
       </c>
       <c r="AW21" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ21" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="BA21" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="BB21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="BC21">
         <v>0.98248517632197996</v>
@@ -8393,14 +8396,14 @@
     </row>
     <row r="22" spans="2:56">
       <c r="B22" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C22" t="s">
+        <v>190</v>
+      </c>
+      <c r="D22" t="s">
         <v>191</v>
       </c>
-      <c r="D22" t="s">
-        <v>192</v>
-      </c>
       <c r="E22" t="s">
         <v>10</v>
       </c>
@@ -8408,16 +8411,16 @@
         <v>20</v>
       </c>
       <c r="G22" t="s">
+        <v>168</v>
+      </c>
+      <c r="H22" t="s">
         <v>169</v>
       </c>
-      <c r="H22" t="s">
-        <v>170</v>
-      </c>
       <c r="J22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K22" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L22">
         <v>7.307015755869652</v>
@@ -8426,14 +8429,14 @@
         <v>0.17768231485175401</v>
       </c>
       <c r="O22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P22" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q22" t="s">
         <v>247</v>
       </c>
-      <c r="Q22" t="s">
-        <v>248</v>
-      </c>
       <c r="R22" t="s">
         <v>10</v>
       </c>
@@ -8441,22 +8444,22 @@
         <v>20</v>
       </c>
       <c r="T22" t="s">
+        <v>224</v>
+      </c>
+      <c r="U22" t="s">
         <v>225</v>
       </c>
-      <c r="U22" t="s">
-        <v>226</v>
-      </c>
       <c r="V22" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="X22" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Y22" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Z22" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AA22">
         <v>0.9982917156958806</v>
@@ -8465,14 +8468,14 @@
         <v>31.318545575522229</v>
       </c>
       <c r="AD22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AE22" t="s">
+        <v>296</v>
+      </c>
+      <c r="AF22" t="s">
         <v>297</v>
       </c>
-      <c r="AF22" t="s">
-        <v>298</v>
-      </c>
       <c r="AG22" t="s">
         <v>10</v>
       </c>
@@ -8480,19 +8483,19 @@
         <v>20</v>
       </c>
       <c r="AI22" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AJ22" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AL22" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AM22" t="s">
+        <v>325</v>
+      </c>
+      <c r="AN22" t="s">
         <v>326</v>
-      </c>
-      <c r="AN22" t="s">
-        <v>327</v>
       </c>
       <c r="AO22">
         <v>0.99239099026325794</v>
@@ -8501,14 +8504,14 @@
         <v>139.49851184027145</v>
       </c>
       <c r="AR22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS22" t="s">
+        <v>355</v>
+      </c>
+      <c r="AT22" t="s">
         <v>356</v>
       </c>
-      <c r="AT22" t="s">
-        <v>357</v>
-      </c>
       <c r="AU22" t="s">
         <v>10</v>
       </c>
@@ -8516,19 +8519,19 @@
         <v>20</v>
       </c>
       <c r="AW22" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX22" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ22" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="BA22" t="s">
+        <v>419</v>
+      </c>
+      <c r="BB22" t="s">
         <v>420</v>
-      </c>
-      <c r="BB22" t="s">
-        <v>421</v>
       </c>
       <c r="BC22">
         <v>0.992142345264865</v>
@@ -8539,14 +8542,14 @@
     </row>
     <row r="23" spans="2:56">
       <c r="B23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D23" t="s">
         <v>193</v>
       </c>
-      <c r="D23" t="s">
-        <v>194</v>
-      </c>
       <c r="E23" t="s">
         <v>10</v>
       </c>
@@ -8554,16 +8557,16 @@
         <v>20</v>
       </c>
       <c r="G23" t="s">
+        <v>168</v>
+      </c>
+      <c r="H23" t="s">
         <v>169</v>
       </c>
-      <c r="H23" t="s">
-        <v>170</v>
-      </c>
       <c r="J23" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K23" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L23">
         <v>13.939949671576917</v>
@@ -8572,14 +8575,14 @@
         <v>0.1699372145053003</v>
       </c>
       <c r="O23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P23" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q23" t="s">
         <v>249</v>
       </c>
-      <c r="Q23" t="s">
-        <v>250</v>
-      </c>
       <c r="R23" t="s">
         <v>10</v>
       </c>
@@ -8587,22 +8590,22 @@
         <v>20</v>
       </c>
       <c r="T23" t="s">
+        <v>224</v>
+      </c>
+      <c r="U23" t="s">
         <v>225</v>
       </c>
-      <c r="U23" t="s">
-        <v>226</v>
-      </c>
       <c r="V23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="X23" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="Y23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Z23" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AA23">
         <v>0.99649838493007836</v>
@@ -8611,14 +8614,14 @@
         <v>64.196276281897482</v>
       </c>
       <c r="AD23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AE23" t="s">
+        <v>298</v>
+      </c>
+      <c r="AF23" t="s">
         <v>299</v>
       </c>
-      <c r="AF23" t="s">
-        <v>300</v>
-      </c>
       <c r="AG23" t="s">
         <v>10</v>
       </c>
@@ -8626,19 +8629,19 @@
         <v>20</v>
       </c>
       <c r="AI23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AJ23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AL23" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AM23" t="s">
+        <v>327</v>
+      </c>
+      <c r="AN23" t="s">
         <v>328</v>
-      </c>
-      <c r="AN23" t="s">
-        <v>329</v>
       </c>
       <c r="AO23">
         <v>0.99807547980555666</v>
@@ -8647,14 +8650,14 @@
         <v>35.282870231460656</v>
       </c>
       <c r="AR23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS23" t="s">
+        <v>357</v>
+      </c>
+      <c r="AT23" t="s">
         <v>358</v>
       </c>
-      <c r="AT23" t="s">
-        <v>359</v>
-      </c>
       <c r="AU23" t="s">
         <v>10</v>
       </c>
@@ -8662,19 +8665,19 @@
         <v>20</v>
       </c>
       <c r="AW23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ23" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="BA23" t="s">
+        <v>421</v>
+      </c>
+      <c r="BB23" t="s">
         <v>422</v>
-      </c>
-      <c r="BB23" t="s">
-        <v>423</v>
       </c>
       <c r="BC23">
         <v>0.99241288386292881</v>
@@ -8685,14 +8688,14 @@
     </row>
     <row r="24" spans="2:56">
       <c r="B24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C24" t="s">
+        <v>194</v>
+      </c>
+      <c r="D24" t="s">
         <v>195</v>
       </c>
-      <c r="D24" t="s">
-        <v>196</v>
-      </c>
       <c r="E24" t="s">
         <v>10</v>
       </c>
@@ -8700,16 +8703,16 @@
         <v>20</v>
       </c>
       <c r="G24" t="s">
+        <v>168</v>
+      </c>
+      <c r="H24" t="s">
         <v>169</v>
       </c>
-      <c r="H24" t="s">
-        <v>170</v>
-      </c>
       <c r="J24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K24" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L24">
         <v>1.6370832793384471</v>
@@ -8718,14 +8721,14 @@
         <v>0.1729078211793279</v>
       </c>
       <c r="O24" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P24" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q24" t="s">
         <v>251</v>
       </c>
-      <c r="Q24" t="s">
-        <v>252</v>
-      </c>
       <c r="R24" t="s">
         <v>10</v>
       </c>
@@ -8733,22 +8736,22 @@
         <v>20</v>
       </c>
       <c r="T24" t="s">
+        <v>224</v>
+      </c>
+      <c r="U24" t="s">
         <v>225</v>
       </c>
-      <c r="U24" t="s">
-        <v>226</v>
-      </c>
       <c r="V24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="X24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Y24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Z24" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AA24">
         <v>0.9958319028842455</v>
@@ -8757,14 +8760,14 @@
         <v>76.415113788833068</v>
       </c>
       <c r="AD24" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AE24" t="s">
+        <v>300</v>
+      </c>
+      <c r="AF24" t="s">
         <v>301</v>
       </c>
-      <c r="AF24" t="s">
-        <v>302</v>
-      </c>
       <c r="AG24" t="s">
         <v>10</v>
       </c>
@@ -8772,19 +8775,19 @@
         <v>20</v>
       </c>
       <c r="AI24" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AJ24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AL24" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AM24" t="s">
+        <v>329</v>
+      </c>
+      <c r="AN24" t="s">
         <v>330</v>
-      </c>
-      <c r="AN24" t="s">
-        <v>331</v>
       </c>
       <c r="AO24">
         <v>0.99665105279570931</v>
@@ -8793,14 +8796,14 @@
         <v>61.397365411996212</v>
       </c>
       <c r="AR24" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS24" t="s">
+        <v>359</v>
+      </c>
+      <c r="AT24" t="s">
         <v>360</v>
       </c>
-      <c r="AT24" t="s">
-        <v>361</v>
-      </c>
       <c r="AU24" t="s">
         <v>10</v>
       </c>
@@ -8808,19 +8811,19 @@
         <v>20</v>
       </c>
       <c r="AW24" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ24" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BA24" t="s">
+        <v>423</v>
+      </c>
+      <c r="BB24" t="s">
         <v>424</v>
-      </c>
-      <c r="BB24" t="s">
-        <v>425</v>
       </c>
       <c r="BC24">
         <v>0.99503867375582744</v>
@@ -8831,14 +8834,14 @@
     </row>
     <row r="25" spans="2:56">
       <c r="B25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C25" t="s">
+        <v>196</v>
+      </c>
+      <c r="D25" t="s">
         <v>197</v>
       </c>
-      <c r="D25" t="s">
-        <v>198</v>
-      </c>
       <c r="E25" t="s">
         <v>10</v>
       </c>
@@ -8846,16 +8849,16 @@
         <v>20</v>
       </c>
       <c r="G25" t="s">
+        <v>168</v>
+      </c>
+      <c r="H25" t="s">
         <v>169</v>
       </c>
-      <c r="H25" t="s">
-        <v>170</v>
-      </c>
       <c r="J25" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K25" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L25">
         <v>0.73381363970591551</v>
@@ -8864,14 +8867,14 @@
         <v>0.16678541694650079</v>
       </c>
       <c r="O25" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P25" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q25" t="s">
         <v>253</v>
       </c>
-      <c r="Q25" t="s">
-        <v>254</v>
-      </c>
       <c r="R25" t="s">
         <v>10</v>
       </c>
@@ -8879,22 +8882,22 @@
         <v>20</v>
       </c>
       <c r="T25" t="s">
+        <v>224</v>
+      </c>
+      <c r="U25" t="s">
         <v>225</v>
       </c>
-      <c r="U25" t="s">
-        <v>226</v>
-      </c>
       <c r="V25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="X25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Y25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z25" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AA25">
         <v>0.9986195737404916</v>
@@ -8903,14 +8906,14 @@
         <v>25.307814757654675</v>
       </c>
       <c r="AD25" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AE25" t="s">
+        <v>302</v>
+      </c>
+      <c r="AF25" t="s">
         <v>303</v>
       </c>
-      <c r="AF25" t="s">
-        <v>304</v>
-      </c>
       <c r="AG25" t="s">
         <v>10</v>
       </c>
@@ -8918,19 +8921,19 @@
         <v>20</v>
       </c>
       <c r="AI25" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AJ25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AL25" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AM25" t="s">
+        <v>331</v>
+      </c>
+      <c r="AN25" t="s">
         <v>332</v>
-      </c>
-      <c r="AN25" t="s">
-        <v>333</v>
       </c>
       <c r="AO25">
         <v>0.99826030196534266</v>
@@ -8939,14 +8942,14 @@
         <v>31.894463968718917</v>
       </c>
       <c r="AR25" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS25" t="s">
+        <v>361</v>
+      </c>
+      <c r="AT25" t="s">
         <v>362</v>
       </c>
-      <c r="AT25" t="s">
-        <v>363</v>
-      </c>
       <c r="AU25" t="s">
         <v>10</v>
       </c>
@@ -8954,19 +8957,19 @@
         <v>20</v>
       </c>
       <c r="AW25" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ25" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="BA25" t="s">
+        <v>425</v>
+      </c>
+      <c r="BB25" t="s">
         <v>426</v>
-      </c>
-      <c r="BB25" t="s">
-        <v>427</v>
       </c>
       <c r="BC25">
         <v>0.99162758874212198</v>
@@ -8977,14 +8980,14 @@
     </row>
     <row r="26" spans="2:56">
       <c r="B26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C26" t="s">
+        <v>198</v>
+      </c>
+      <c r="D26" t="s">
         <v>199</v>
       </c>
-      <c r="D26" t="s">
-        <v>200</v>
-      </c>
       <c r="E26" t="s">
         <v>10</v>
       </c>
@@ -8992,16 +8995,16 @@
         <v>20</v>
       </c>
       <c r="G26" t="s">
+        <v>168</v>
+      </c>
+      <c r="H26" t="s">
         <v>169</v>
       </c>
-      <c r="H26" t="s">
-        <v>170</v>
-      </c>
       <c r="J26" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L26">
         <v>1.8144550028683772</v>
@@ -9010,14 +9013,14 @@
         <v>0.1577067378709853</v>
       </c>
       <c r="O26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P26" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q26" t="s">
         <v>255</v>
       </c>
-      <c r="Q26" t="s">
-        <v>256</v>
-      </c>
       <c r="R26" t="s">
         <v>10</v>
       </c>
@@ -9025,22 +9028,22 @@
         <v>20</v>
       </c>
       <c r="T26" t="s">
+        <v>224</v>
+      </c>
+      <c r="U26" t="s">
         <v>225</v>
       </c>
-      <c r="U26" t="s">
-        <v>226</v>
-      </c>
       <c r="V26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="X26" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Y26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Z26" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AA26">
         <v>0.99656426482871763</v>
@@ -9049,14 +9052,14 @@
         <v>62.988478140176163</v>
       </c>
       <c r="AR26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS26" t="s">
+        <v>363</v>
+      </c>
+      <c r="AT26" t="s">
         <v>364</v>
       </c>
-      <c r="AT26" t="s">
-        <v>365</v>
-      </c>
       <c r="AU26" t="s">
         <v>10</v>
       </c>
@@ -9064,19 +9067,19 @@
         <v>20</v>
       </c>
       <c r="AW26" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ26" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="BA26" t="s">
+        <v>427</v>
+      </c>
+      <c r="BB26" t="s">
         <v>428</v>
-      </c>
-      <c r="BB26" t="s">
-        <v>429</v>
       </c>
       <c r="BC26">
         <v>0.99508487560623826</v>
@@ -9087,14 +9090,14 @@
     </row>
     <row r="27" spans="2:56">
       <c r="AR27" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS27" t="s">
+        <v>365</v>
+      </c>
+      <c r="AT27" t="s">
         <v>366</v>
       </c>
-      <c r="AT27" t="s">
-        <v>367</v>
-      </c>
       <c r="AU27" t="s">
         <v>10</v>
       </c>
@@ -9102,19 +9105,19 @@
         <v>20</v>
       </c>
       <c r="AW27" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX27" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ27" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="BA27" t="s">
+        <v>429</v>
+      </c>
+      <c r="BB27" t="s">
         <v>430</v>
-      </c>
-      <c r="BB27" t="s">
-        <v>431</v>
       </c>
       <c r="BC27">
         <v>0.97496359905143026</v>
@@ -9125,14 +9128,14 @@
     </row>
     <row r="28" spans="2:56">
       <c r="AR28" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS28" t="s">
+        <v>367</v>
+      </c>
+      <c r="AT28" t="s">
         <v>368</v>
       </c>
-      <c r="AT28" t="s">
-        <v>369</v>
-      </c>
       <c r="AU28" t="s">
         <v>10</v>
       </c>
@@ -9140,19 +9143,19 @@
         <v>20</v>
       </c>
       <c r="AW28" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX28" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ28" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="BA28" t="s">
+        <v>431</v>
+      </c>
+      <c r="BB28" t="s">
         <v>432</v>
-      </c>
-      <c r="BB28" t="s">
-        <v>433</v>
       </c>
       <c r="BC28">
         <v>0.99514843803074871</v>
@@ -9163,14 +9166,14 @@
     </row>
     <row r="29" spans="2:56">
       <c r="AR29" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS29" t="s">
+        <v>369</v>
+      </c>
+      <c r="AT29" t="s">
         <v>370</v>
       </c>
-      <c r="AT29" t="s">
-        <v>371</v>
-      </c>
       <c r="AU29" t="s">
         <v>10</v>
       </c>
@@ -9178,19 +9181,19 @@
         <v>20</v>
       </c>
       <c r="AW29" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX29" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ29" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="BA29" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="BB29" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="BC29">
         <v>0.98039565814133589</v>
@@ -9201,14 +9204,14 @@
     </row>
     <row r="30" spans="2:56">
       <c r="AR30" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS30" t="s">
+        <v>371</v>
+      </c>
+      <c r="AT30" t="s">
         <v>372</v>
       </c>
-      <c r="AT30" t="s">
-        <v>373</v>
-      </c>
       <c r="AU30" t="s">
         <v>10</v>
       </c>
@@ -9216,19 +9219,19 @@
         <v>20</v>
       </c>
       <c r="AW30" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ30" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="BA30" t="s">
+        <v>434</v>
+      </c>
+      <c r="BB30" t="s">
         <v>435</v>
-      </c>
-      <c r="BB30" t="s">
-        <v>436</v>
       </c>
       <c r="BC30">
         <v>0.99199988291996133</v>
@@ -9239,14 +9242,14 @@
     </row>
     <row r="31" spans="2:56">
       <c r="AR31" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS31" t="s">
+        <v>373</v>
+      </c>
+      <c r="AT31" t="s">
         <v>374</v>
       </c>
-      <c r="AT31" t="s">
-        <v>375</v>
-      </c>
       <c r="AU31" t="s">
         <v>10</v>
       </c>
@@ -9254,19 +9257,19 @@
         <v>20</v>
       </c>
       <c r="AW31" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX31" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ31" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="BA31" t="s">
+        <v>436</v>
+      </c>
+      <c r="BB31" t="s">
         <v>437</v>
-      </c>
-      <c r="BB31" t="s">
-        <v>438</v>
       </c>
       <c r="BC31">
         <v>0.96374055461874508</v>
@@ -9277,14 +9280,14 @@
     </row>
     <row r="32" spans="2:56">
       <c r="AR32" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS32" t="s">
+        <v>375</v>
+      </c>
+      <c r="AT32" t="s">
         <v>376</v>
       </c>
-      <c r="AT32" t="s">
-        <v>377</v>
-      </c>
       <c r="AU32" t="s">
         <v>10</v>
       </c>
@@ -9292,19 +9295,19 @@
         <v>20</v>
       </c>
       <c r="AW32" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX32" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ32" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="BA32" t="s">
+        <v>438</v>
+      </c>
+      <c r="BB32" t="s">
         <v>439</v>
-      </c>
-      <c r="BB32" t="s">
-        <v>440</v>
       </c>
       <c r="BC32">
         <v>0.99048115912556611</v>
@@ -9315,14 +9318,14 @@
     </row>
     <row r="33" spans="44:56">
       <c r="AR33" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS33" t="s">
+        <v>377</v>
+      </c>
+      <c r="AT33" t="s">
         <v>378</v>
       </c>
-      <c r="AT33" t="s">
-        <v>379</v>
-      </c>
       <c r="AU33" t="s">
         <v>10</v>
       </c>
@@ -9330,19 +9333,19 @@
         <v>20</v>
       </c>
       <c r="AW33" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX33" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ33" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="BA33" t="s">
+        <v>440</v>
+      </c>
+      <c r="BB33" t="s">
         <v>441</v>
-      </c>
-      <c r="BB33" t="s">
-        <v>442</v>
       </c>
       <c r="BC33">
         <v>0.99441710380733805</v>
@@ -9353,14 +9356,14 @@
     </row>
     <row r="34" spans="44:56">
       <c r="AR34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS34" t="s">
+        <v>379</v>
+      </c>
+      <c r="AT34" t="s">
         <v>380</v>
       </c>
-      <c r="AT34" t="s">
-        <v>381</v>
-      </c>
       <c r="AU34" t="s">
         <v>10</v>
       </c>
@@ -9368,19 +9371,19 @@
         <v>20</v>
       </c>
       <c r="AW34" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX34" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ34" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="BA34" t="s">
+        <v>442</v>
+      </c>
+      <c r="BB34" t="s">
         <v>443</v>
-      </c>
-      <c r="BB34" t="s">
-        <v>444</v>
       </c>
       <c r="BC34">
         <v>0.9871879084242271</v>
@@ -9391,14 +9394,14 @@
     </row>
     <row r="35" spans="44:56">
       <c r="AR35" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS35" t="s">
+        <v>381</v>
+      </c>
+      <c r="AT35" t="s">
         <v>382</v>
       </c>
-      <c r="AT35" t="s">
-        <v>383</v>
-      </c>
       <c r="AU35" t="s">
         <v>10</v>
       </c>
@@ -9406,19 +9409,19 @@
         <v>20</v>
       </c>
       <c r="AW35" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX35" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ35" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="BA35" t="s">
+        <v>444</v>
+      </c>
+      <c r="BB35" t="s">
         <v>445</v>
-      </c>
-      <c r="BB35" t="s">
-        <v>446</v>
       </c>
       <c r="BC35">
         <v>0.99511226039729839</v>
@@ -9429,14 +9432,14 @@
     </row>
     <row r="36" spans="44:56">
       <c r="AR36" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS36" t="s">
+        <v>383</v>
+      </c>
+      <c r="AT36" t="s">
         <v>384</v>
       </c>
-      <c r="AT36" t="s">
-        <v>385</v>
-      </c>
       <c r="AU36" t="s">
         <v>10</v>
       </c>
@@ -9444,19 +9447,19 @@
         <v>20</v>
       </c>
       <c r="AW36" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX36" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="BA36" t="s">
+        <v>446</v>
+      </c>
+      <c r="BB36" t="s">
         <v>447</v>
-      </c>
-      <c r="BB36" t="s">
-        <v>448</v>
       </c>
       <c r="BC36">
         <v>0.99402092584318991</v>
@@ -9467,14 +9470,14 @@
     </row>
     <row r="37" spans="44:56">
       <c r="AR37" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS37" t="s">
+        <v>385</v>
+      </c>
+      <c r="AT37" t="s">
         <v>386</v>
       </c>
-      <c r="AT37" t="s">
-        <v>387</v>
-      </c>
       <c r="AU37" t="s">
         <v>10</v>
       </c>
@@ -9482,19 +9485,19 @@
         <v>20</v>
       </c>
       <c r="AW37" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX37" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ37" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="BA37" t="s">
+        <v>448</v>
+      </c>
+      <c r="BB37" t="s">
         <v>449</v>
-      </c>
-      <c r="BB37" t="s">
-        <v>450</v>
       </c>
       <c r="BC37">
         <v>0.99402264995370893</v>
@@ -9505,14 +9508,14 @@
     </row>
     <row r="38" spans="44:56">
       <c r="AR38" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS38" t="s">
+        <v>387</v>
+      </c>
+      <c r="AT38" t="s">
         <v>388</v>
       </c>
-      <c r="AT38" t="s">
-        <v>389</v>
-      </c>
       <c r="AU38" t="s">
         <v>10</v>
       </c>
@@ -9520,19 +9523,19 @@
         <v>20</v>
       </c>
       <c r="AW38" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX38" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ38" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="BA38" t="s">
+        <v>450</v>
+      </c>
+      <c r="BB38" t="s">
         <v>451</v>
-      </c>
-      <c r="BB38" t="s">
-        <v>452</v>
       </c>
       <c r="BC38">
         <v>0.99490522012066784</v>
@@ -9543,14 +9546,14 @@
     </row>
     <row r="39" spans="44:56">
       <c r="AR39" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS39" t="s">
+        <v>389</v>
+      </c>
+      <c r="AT39" t="s">
         <v>390</v>
       </c>
-      <c r="AT39" t="s">
-        <v>391</v>
-      </c>
       <c r="AU39" t="s">
         <v>10</v>
       </c>
@@ -9558,19 +9561,19 @@
         <v>20</v>
       </c>
       <c r="AW39" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX39" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ39" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="BA39" t="s">
+        <v>452</v>
+      </c>
+      <c r="BB39" t="s">
         <v>453</v>
-      </c>
-      <c r="BB39" t="s">
-        <v>454</v>
       </c>
       <c r="BC39">
         <v>0.99728827252195684</v>
@@ -9581,14 +9584,14 @@
     </row>
     <row r="40" spans="44:56">
       <c r="AR40" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS40" t="s">
+        <v>391</v>
+      </c>
+      <c r="AT40" t="s">
         <v>392</v>
       </c>
-      <c r="AT40" t="s">
-        <v>393</v>
-      </c>
       <c r="AU40" t="s">
         <v>10</v>
       </c>
@@ -9596,19 +9599,19 @@
         <v>20</v>
       </c>
       <c r="AW40" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX40" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ40" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="BA40" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="BB40" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="BC40">
         <v>0.95113733831453195</v>
@@ -9619,14 +9622,14 @@
     </row>
     <row r="41" spans="44:56">
       <c r="AR41" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS41" t="s">
+        <v>393</v>
+      </c>
+      <c r="AT41" t="s">
         <v>394</v>
       </c>
-      <c r="AT41" t="s">
-        <v>395</v>
-      </c>
       <c r="AU41" t="s">
         <v>10</v>
       </c>
@@ -9634,19 +9637,19 @@
         <v>20</v>
       </c>
       <c r="AW41" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX41" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ41" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="BA41" t="s">
+        <v>455</v>
+      </c>
+      <c r="BB41" t="s">
         <v>456</v>
-      </c>
-      <c r="BB41" t="s">
-        <v>457</v>
       </c>
       <c r="BC41">
         <v>0.9955021345306051</v>
@@ -9657,14 +9660,14 @@
     </row>
     <row r="42" spans="44:56">
       <c r="AR42" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS42" t="s">
+        <v>395</v>
+      </c>
+      <c r="AT42" t="s">
         <v>396</v>
       </c>
-      <c r="AT42" t="s">
-        <v>397</v>
-      </c>
       <c r="AU42" t="s">
         <v>10</v>
       </c>
@@ -9672,19 +9675,19 @@
         <v>20</v>
       </c>
       <c r="AW42" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX42" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ42" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="BA42" t="s">
+        <v>457</v>
+      </c>
+      <c r="BB42" t="s">
         <v>458</v>
-      </c>
-      <c r="BB42" t="s">
-        <v>459</v>
       </c>
       <c r="BC42">
         <v>0.99579892549254256</v>
@@ -9695,14 +9698,14 @@
     </row>
     <row r="43" spans="44:56">
       <c r="AR43" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AS43" t="s">
+        <v>397</v>
+      </c>
+      <c r="AT43" t="s">
         <v>398</v>
       </c>
-      <c r="AT43" t="s">
-        <v>399</v>
-      </c>
       <c r="AU43" t="s">
         <v>10</v>
       </c>
@@ -9710,19 +9713,19 @@
         <v>20</v>
       </c>
       <c r="AW43" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX43" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AZ43" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="BA43" t="s">
+        <v>459</v>
+      </c>
+      <c r="BB43" t="s">
         <v>460</v>
-      </c>
-      <c r="BB43" t="s">
-        <v>461</v>
       </c>
       <c r="BC43">
         <v>0.9877150845460122</v>
@@ -9743,96 +9746,96 @@
   <sheetData>
     <row r="9" spans="2:26">
       <c r="B9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="W9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="2:26">
       <c r="B10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C10" t="s">
         <v>159</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>160</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>161</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>162</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>163</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>164</v>
       </c>
-      <c r="H10" t="s">
-        <v>165</v>
-      </c>
       <c r="J10" t="s">
+        <v>159</v>
+      </c>
+      <c r="K10" t="s">
+        <v>201</v>
+      </c>
+      <c r="L10" t="s">
+        <v>202</v>
+      </c>
+      <c r="M10" t="s">
+        <v>203</v>
+      </c>
+      <c r="O10" t="s">
+        <v>158</v>
+      </c>
+      <c r="P10" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q10" t="s">
         <v>160</v>
       </c>
-      <c r="K10" t="s">
+      <c r="R10" t="s">
+        <v>161</v>
+      </c>
+      <c r="S10" t="s">
+        <v>162</v>
+      </c>
+      <c r="T10" t="s">
+        <v>163</v>
+      </c>
+      <c r="U10" t="s">
+        <v>164</v>
+      </c>
+      <c r="W10" t="s">
+        <v>159</v>
+      </c>
+      <c r="X10" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y10" t="s">
         <v>202</v>
       </c>
-      <c r="L10" t="s">
+      <c r="Z10" t="s">
         <v>203</v>
-      </c>
-      <c r="M10" t="s">
-        <v>204</v>
-      </c>
-      <c r="O10" t="s">
-        <v>159</v>
-      </c>
-      <c r="P10" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>161</v>
-      </c>
-      <c r="R10" t="s">
-        <v>162</v>
-      </c>
-      <c r="S10" t="s">
-        <v>163</v>
-      </c>
-      <c r="T10" t="s">
-        <v>164</v>
-      </c>
-      <c r="U10" t="s">
-        <v>165</v>
-      </c>
-      <c r="W10" t="s">
-        <v>160</v>
-      </c>
-      <c r="X10" t="s">
-        <v>202</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>203</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="11" spans="2:26">
       <c r="B11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C11" t="s">
+        <v>461</v>
+      </c>
+      <c r="D11" t="s">
         <v>462</v>
       </c>
-      <c r="D11" t="s">
-        <v>463</v>
-      </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
@@ -9840,16 +9843,16 @@
         <v>20</v>
       </c>
       <c r="G11" t="s">
+        <v>168</v>
+      </c>
+      <c r="H11" t="s">
         <v>169</v>
       </c>
-      <c r="H11" t="s">
-        <v>170</v>
-      </c>
       <c r="J11" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="K11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L11">
         <v>8.3728062197205944</v>
@@ -9858,14 +9861,14 @@
         <v>0.4071105959727585</v>
       </c>
       <c r="O11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P11" t="s">
+        <v>491</v>
+      </c>
+      <c r="Q11" t="s">
         <v>492</v>
       </c>
-      <c r="Q11" t="s">
-        <v>493</v>
-      </c>
       <c r="R11" t="s">
         <v>10</v>
       </c>
@@ -9873,16 +9876,16 @@
         <v>20</v>
       </c>
       <c r="T11" t="s">
+        <v>168</v>
+      </c>
+      <c r="U11" t="s">
         <v>169</v>
       </c>
-      <c r="U11" t="s">
-        <v>170</v>
-      </c>
       <c r="W11" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="X11" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="Y11">
         <v>2.177</v>
@@ -9893,14 +9896,14 @@
     </row>
     <row r="12" spans="2:26">
       <c r="B12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C12" t="s">
+        <v>463</v>
+      </c>
+      <c r="D12" t="s">
         <v>464</v>
       </c>
-      <c r="D12" t="s">
-        <v>465</v>
-      </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
@@ -9908,16 +9911,16 @@
         <v>20</v>
       </c>
       <c r="G12" t="s">
+        <v>168</v>
+      </c>
+      <c r="H12" t="s">
         <v>169</v>
       </c>
-      <c r="H12" t="s">
-        <v>170</v>
-      </c>
       <c r="J12" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K12" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L12">
         <v>42.531235680568031</v>
@@ -9926,14 +9929,14 @@
         <v>0.36457772816942419</v>
       </c>
       <c r="O12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P12" t="s">
+        <v>493</v>
+      </c>
+      <c r="Q12" t="s">
         <v>494</v>
       </c>
-      <c r="Q12" t="s">
-        <v>495</v>
-      </c>
       <c r="R12" t="s">
         <v>10</v>
       </c>
@@ -9941,16 +9944,16 @@
         <v>20</v>
       </c>
       <c r="T12" t="s">
+        <v>168</v>
+      </c>
+      <c r="U12" t="s">
         <v>169</v>
       </c>
-      <c r="U12" t="s">
-        <v>170</v>
-      </c>
       <c r="W12" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="X12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Y12">
         <v>47.905999999999999</v>
@@ -9961,14 +9964,14 @@
     </row>
     <row r="13" spans="2:26">
       <c r="B13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C13" t="s">
+        <v>465</v>
+      </c>
+      <c r="D13" t="s">
         <v>466</v>
       </c>
-      <c r="D13" t="s">
-        <v>467</v>
-      </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
@@ -9976,16 +9979,16 @@
         <v>20</v>
       </c>
       <c r="G13" t="s">
+        <v>168</v>
+      </c>
+      <c r="H13" t="s">
         <v>169</v>
       </c>
-      <c r="H13" t="s">
-        <v>170</v>
-      </c>
       <c r="J13" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L13">
         <v>30.271312154499352</v>
@@ -9994,14 +9997,14 @@
         <v>0.34977720239710119</v>
       </c>
       <c r="O13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P13" t="s">
+        <v>495</v>
+      </c>
+      <c r="Q13" t="s">
         <v>496</v>
       </c>
-      <c r="Q13" t="s">
-        <v>497</v>
-      </c>
       <c r="R13" t="s">
         <v>10</v>
       </c>
@@ -10009,16 +10012,16 @@
         <v>20</v>
       </c>
       <c r="T13" t="s">
+        <v>168</v>
+      </c>
+      <c r="U13" t="s">
         <v>169</v>
       </c>
-      <c r="U13" t="s">
-        <v>170</v>
-      </c>
       <c r="W13" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="X13" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Y13">
         <v>91.13</v>
@@ -10029,14 +10032,14 @@
     </row>
     <row r="14" spans="2:26">
       <c r="B14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C14" t="s">
+        <v>467</v>
+      </c>
+      <c r="D14" t="s">
         <v>468</v>
       </c>
-      <c r="D14" t="s">
-        <v>469</v>
-      </c>
       <c r="E14" t="s">
         <v>10</v>
       </c>
@@ -10044,16 +10047,16 @@
         <v>20</v>
       </c>
       <c r="G14" t="s">
+        <v>168</v>
+      </c>
+      <c r="H14" t="s">
         <v>169</v>
       </c>
-      <c r="H14" t="s">
-        <v>170</v>
-      </c>
       <c r="J14" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K14" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L14">
         <v>22.688073076145226</v>
@@ -10062,14 +10065,14 @@
         <v>0.2378222396486388</v>
       </c>
       <c r="O14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P14" t="s">
+        <v>497</v>
+      </c>
+      <c r="Q14" t="s">
         <v>498</v>
       </c>
-      <c r="Q14" t="s">
-        <v>499</v>
-      </c>
       <c r="R14" t="s">
         <v>10</v>
       </c>
@@ -10077,16 +10080,16 @@
         <v>20</v>
       </c>
       <c r="T14" t="s">
+        <v>168</v>
+      </c>
+      <c r="U14" t="s">
         <v>169</v>
       </c>
-      <c r="U14" t="s">
-        <v>170</v>
-      </c>
       <c r="W14" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="X14" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Y14">
         <v>30.484999999999999</v>
@@ -10097,14 +10100,14 @@
     </row>
     <row r="15" spans="2:26">
       <c r="B15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C15" t="s">
+        <v>469</v>
+      </c>
+      <c r="D15" t="s">
         <v>470</v>
       </c>
-      <c r="D15" t="s">
-        <v>471</v>
-      </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
@@ -10112,16 +10115,16 @@
         <v>20</v>
       </c>
       <c r="G15" t="s">
+        <v>168</v>
+      </c>
+      <c r="H15" t="s">
         <v>169</v>
       </c>
-      <c r="H15" t="s">
-        <v>170</v>
-      </c>
       <c r="J15" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K15" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L15">
         <v>29.120153762247021</v>
@@ -10130,14 +10133,14 @@
         <v>0.2926790130249729</v>
       </c>
       <c r="O15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P15" t="s">
+        <v>499</v>
+      </c>
+      <c r="Q15" t="s">
         <v>500</v>
       </c>
-      <c r="Q15" t="s">
-        <v>501</v>
-      </c>
       <c r="R15" t="s">
         <v>10</v>
       </c>
@@ -10145,16 +10148,16 @@
         <v>20</v>
       </c>
       <c r="T15" t="s">
+        <v>168</v>
+      </c>
+      <c r="U15" t="s">
         <v>169</v>
       </c>
-      <c r="U15" t="s">
-        <v>170</v>
-      </c>
       <c r="W15" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="X15" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Y15">
         <v>6.726</v>
@@ -10165,14 +10168,14 @@
     </row>
     <row r="16" spans="2:26">
       <c r="B16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C16" t="s">
+        <v>471</v>
+      </c>
+      <c r="D16" t="s">
         <v>472</v>
       </c>
-      <c r="D16" t="s">
-        <v>473</v>
-      </c>
       <c r="E16" t="s">
         <v>10</v>
       </c>
@@ -10180,16 +10183,16 @@
         <v>20</v>
       </c>
       <c r="G16" t="s">
+        <v>168</v>
+      </c>
+      <c r="H16" t="s">
         <v>169</v>
       </c>
-      <c r="H16" t="s">
-        <v>170</v>
-      </c>
       <c r="J16" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K16" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L16">
         <v>10.867385180190169</v>
@@ -10198,14 +10201,14 @@
         <v>0.1103684814428935</v>
       </c>
       <c r="O16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P16" t="s">
+        <v>501</v>
+      </c>
+      <c r="Q16" t="s">
         <v>502</v>
       </c>
-      <c r="Q16" t="s">
-        <v>503</v>
-      </c>
       <c r="R16" t="s">
         <v>10</v>
       </c>
@@ -10213,16 +10216,16 @@
         <v>20</v>
       </c>
       <c r="T16" t="s">
+        <v>168</v>
+      </c>
+      <c r="U16" t="s">
         <v>169</v>
       </c>
-      <c r="U16" t="s">
-        <v>170</v>
-      </c>
       <c r="W16" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="X16" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Y16">
         <v>33.183</v>
@@ -10233,14 +10236,14 @@
     </row>
     <row r="17" spans="2:26">
       <c r="B17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C17" t="s">
+        <v>473</v>
+      </c>
+      <c r="D17" t="s">
         <v>474</v>
       </c>
-      <c r="D17" t="s">
-        <v>475</v>
-      </c>
       <c r="E17" t="s">
         <v>10</v>
       </c>
@@ -10248,16 +10251,16 @@
         <v>20</v>
       </c>
       <c r="G17" t="s">
+        <v>168</v>
+      </c>
+      <c r="H17" t="s">
         <v>169</v>
       </c>
-      <c r="H17" t="s">
-        <v>170</v>
-      </c>
       <c r="J17" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K17" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L17">
         <v>32.115075062865692</v>
@@ -10266,14 +10269,14 @@
         <v>0.2243348627558987</v>
       </c>
       <c r="O17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P17" t="s">
+        <v>503</v>
+      </c>
+      <c r="Q17" t="s">
         <v>504</v>
       </c>
-      <c r="Q17" t="s">
-        <v>505</v>
-      </c>
       <c r="R17" t="s">
         <v>10</v>
       </c>
@@ -10281,16 +10284,16 @@
         <v>20</v>
       </c>
       <c r="T17" t="s">
+        <v>168</v>
+      </c>
+      <c r="U17" t="s">
         <v>169</v>
       </c>
-      <c r="U17" t="s">
-        <v>170</v>
-      </c>
       <c r="W17" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X17" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="Y17">
         <v>40.698999999999998</v>
@@ -10301,14 +10304,14 @@
     </row>
     <row r="18" spans="2:26">
       <c r="B18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C18" t="s">
+        <v>475</v>
+      </c>
+      <c r="D18" t="s">
         <v>476</v>
       </c>
-      <c r="D18" t="s">
-        <v>477</v>
-      </c>
       <c r="E18" t="s">
         <v>10</v>
       </c>
@@ -10316,16 +10319,16 @@
         <v>20</v>
       </c>
       <c r="G18" t="s">
+        <v>168</v>
+      </c>
+      <c r="H18" t="s">
         <v>169</v>
       </c>
-      <c r="H18" t="s">
-        <v>170</v>
-      </c>
       <c r="J18" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="K18" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L18">
         <v>9.0868240253443027</v>
@@ -10334,14 +10337,14 @@
         <v>0.17692716652199311</v>
       </c>
       <c r="O18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P18" t="s">
+        <v>505</v>
+      </c>
+      <c r="Q18" t="s">
         <v>506</v>
       </c>
-      <c r="Q18" t="s">
-        <v>507</v>
-      </c>
       <c r="R18" t="s">
         <v>10</v>
       </c>
@@ -10349,16 +10352,16 @@
         <v>20</v>
       </c>
       <c r="T18" t="s">
+        <v>168</v>
+      </c>
+      <c r="U18" t="s">
         <v>169</v>
       </c>
-      <c r="U18" t="s">
-        <v>170</v>
-      </c>
       <c r="W18" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="X18" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Y18">
         <v>43.79</v>
@@ -10369,14 +10372,14 @@
     </row>
     <row r="19" spans="2:26">
       <c r="B19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C19" t="s">
+        <v>477</v>
+      </c>
+      <c r="D19" t="s">
         <v>478</v>
       </c>
-      <c r="D19" t="s">
-        <v>479</v>
-      </c>
       <c r="E19" t="s">
         <v>10</v>
       </c>
@@ -10384,16 +10387,16 @@
         <v>20</v>
       </c>
       <c r="G19" t="s">
+        <v>168</v>
+      </c>
+      <c r="H19" t="s">
         <v>169</v>
       </c>
-      <c r="H19" t="s">
-        <v>170</v>
-      </c>
       <c r="J19" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K19" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L19">
         <v>18.016423245563796</v>
@@ -10402,14 +10405,14 @@
         <v>0.37709145338738631</v>
       </c>
       <c r="O19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P19" t="s">
+        <v>507</v>
+      </c>
+      <c r="Q19" t="s">
         <v>508</v>
       </c>
-      <c r="Q19" t="s">
-        <v>509</v>
-      </c>
       <c r="R19" t="s">
         <v>10</v>
       </c>
@@ -10417,16 +10420,16 @@
         <v>20</v>
       </c>
       <c r="T19" t="s">
+        <v>168</v>
+      </c>
+      <c r="U19" t="s">
         <v>169</v>
       </c>
-      <c r="U19" t="s">
-        <v>170</v>
-      </c>
       <c r="W19" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="X19" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Y19">
         <v>3.617</v>
@@ -10437,14 +10440,14 @@
     </row>
     <row r="20" spans="2:26">
       <c r="B20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C20" t="s">
+        <v>479</v>
+      </c>
+      <c r="D20" t="s">
         <v>480</v>
       </c>
-      <c r="D20" t="s">
-        <v>481</v>
-      </c>
       <c r="E20" t="s">
         <v>10</v>
       </c>
@@ -10452,16 +10455,16 @@
         <v>20</v>
       </c>
       <c r="G20" t="s">
+        <v>168</v>
+      </c>
+      <c r="H20" t="s">
         <v>169</v>
       </c>
-      <c r="H20" t="s">
-        <v>170</v>
-      </c>
       <c r="J20" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K20" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L20">
         <v>0.75250112047637663</v>
@@ -10470,14 +10473,14 @@
         <v>0.20583489876164651</v>
       </c>
       <c r="O20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P20" t="s">
+        <v>509</v>
+      </c>
+      <c r="Q20" t="s">
         <v>510</v>
       </c>
-      <c r="Q20" t="s">
-        <v>511</v>
-      </c>
       <c r="R20" t="s">
         <v>10</v>
       </c>
@@ -10485,16 +10488,16 @@
         <v>20</v>
       </c>
       <c r="T20" t="s">
+        <v>168</v>
+      </c>
+      <c r="U20" t="s">
         <v>169</v>
       </c>
-      <c r="U20" t="s">
-        <v>170</v>
-      </c>
       <c r="W20" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="X20" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Y20">
         <v>45.468000000000004</v>
@@ -10505,14 +10508,14 @@
     </row>
     <row r="21" spans="2:26">
       <c r="B21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C21" t="s">
+        <v>481</v>
+      </c>
+      <c r="D21" t="s">
         <v>482</v>
       </c>
-      <c r="D21" t="s">
-        <v>483</v>
-      </c>
       <c r="E21" t="s">
         <v>10</v>
       </c>
@@ -10520,16 +10523,16 @@
         <v>20</v>
       </c>
       <c r="G21" t="s">
+        <v>168</v>
+      </c>
+      <c r="H21" t="s">
         <v>169</v>
       </c>
-      <c r="H21" t="s">
-        <v>170</v>
-      </c>
       <c r="J21" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K21" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L21">
         <v>18.381813037942475</v>
@@ -10538,14 +10541,14 @@
         <v>0.21707807750595889</v>
       </c>
       <c r="O21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P21" t="s">
+        <v>511</v>
+      </c>
+      <c r="Q21" t="s">
         <v>512</v>
       </c>
-      <c r="Q21" t="s">
-        <v>513</v>
-      </c>
       <c r="R21" t="s">
         <v>10</v>
       </c>
@@ -10553,16 +10556,16 @@
         <v>20</v>
       </c>
       <c r="T21" t="s">
+        <v>168</v>
+      </c>
+      <c r="U21" t="s">
         <v>169</v>
       </c>
-      <c r="U21" t="s">
-        <v>170</v>
-      </c>
       <c r="W21" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="X21" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="Y21">
         <v>33.305</v>
@@ -10573,14 +10576,14 @@
     </row>
     <row r="22" spans="2:26">
       <c r="B22" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C22" t="s">
+        <v>483</v>
+      </c>
+      <c r="D22" t="s">
         <v>484</v>
       </c>
-      <c r="D22" t="s">
-        <v>485</v>
-      </c>
       <c r="E22" t="s">
         <v>10</v>
       </c>
@@ -10588,16 +10591,16 @@
         <v>20</v>
       </c>
       <c r="G22" t="s">
+        <v>168</v>
+      </c>
+      <c r="H22" t="s">
         <v>169</v>
       </c>
-      <c r="H22" t="s">
-        <v>170</v>
-      </c>
       <c r="J22" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="K22" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L22">
         <v>4.5221914845937041</v>
@@ -10606,14 +10609,14 @@
         <v>0.11806257993100711</v>
       </c>
       <c r="O22" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P22" t="s">
+        <v>513</v>
+      </c>
+      <c r="Q22" t="s">
         <v>514</v>
       </c>
-      <c r="Q22" t="s">
-        <v>515</v>
-      </c>
       <c r="R22" t="s">
         <v>10</v>
       </c>
@@ -10621,16 +10624,16 @@
         <v>20</v>
       </c>
       <c r="T22" t="s">
+        <v>168</v>
+      </c>
+      <c r="U22" t="s">
         <v>169</v>
       </c>
-      <c r="U22" t="s">
-        <v>170</v>
-      </c>
       <c r="W22" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="X22" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Y22">
         <v>32.006</v>
@@ -10641,14 +10644,14 @@
     </row>
     <row r="23" spans="2:26">
       <c r="B23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C23" t="s">
+        <v>485</v>
+      </c>
+      <c r="D23" t="s">
         <v>486</v>
       </c>
-      <c r="D23" t="s">
-        <v>487</v>
-      </c>
       <c r="E23" t="s">
         <v>10</v>
       </c>
@@ -10656,16 +10659,16 @@
         <v>20</v>
       </c>
       <c r="G23" t="s">
+        <v>168</v>
+      </c>
+      <c r="H23" t="s">
         <v>169</v>
       </c>
-      <c r="H23" t="s">
-        <v>170</v>
-      </c>
       <c r="J23" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K23" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L23">
         <v>8.2953562793919264</v>
@@ -10674,14 +10677,14 @@
         <v>0.1425131297827614</v>
       </c>
       <c r="O23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P23" t="s">
+        <v>515</v>
+      </c>
+      <c r="Q23" t="s">
         <v>516</v>
       </c>
-      <c r="Q23" t="s">
-        <v>517</v>
-      </c>
       <c r="R23" t="s">
         <v>10</v>
       </c>
@@ -10689,16 +10692,16 @@
         <v>20</v>
       </c>
       <c r="T23" t="s">
+        <v>168</v>
+      </c>
+      <c r="U23" t="s">
         <v>169</v>
       </c>
-      <c r="U23" t="s">
-        <v>170</v>
-      </c>
       <c r="W23" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="X23" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Y23">
         <v>92.117999999999995</v>
@@ -10709,14 +10712,14 @@
     </row>
     <row r="24" spans="2:26">
       <c r="B24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C24" t="s">
+        <v>487</v>
+      </c>
+      <c r="D24" t="s">
         <v>488</v>
       </c>
-      <c r="D24" t="s">
-        <v>489</v>
-      </c>
       <c r="E24" t="s">
         <v>10</v>
       </c>
@@ -10724,16 +10727,16 @@
         <v>20</v>
       </c>
       <c r="G24" t="s">
+        <v>168</v>
+      </c>
+      <c r="H24" t="s">
         <v>169</v>
       </c>
-      <c r="H24" t="s">
-        <v>170</v>
-      </c>
       <c r="J24" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="K24" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L24">
         <v>1.2792726734837132</v>
@@ -10742,14 +10745,14 @@
         <v>0.120834301617764</v>
       </c>
       <c r="O24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P24" t="s">
+        <v>517</v>
+      </c>
+      <c r="Q24" t="s">
         <v>518</v>
       </c>
-      <c r="Q24" t="s">
-        <v>519</v>
-      </c>
       <c r="R24" t="s">
         <v>10</v>
       </c>
@@ -10757,16 +10760,16 @@
         <v>20</v>
       </c>
       <c r="T24" t="s">
+        <v>168</v>
+      </c>
+      <c r="U24" t="s">
         <v>169</v>
       </c>
-      <c r="U24" t="s">
-        <v>170</v>
-      </c>
       <c r="W24" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="X24" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Y24">
         <v>55.912999999999997</v>
@@ -10777,14 +10780,14 @@
     </row>
     <row r="25" spans="2:26">
       <c r="B25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C25" t="s">
+        <v>489</v>
+      </c>
+      <c r="D25" t="s">
         <v>490</v>
       </c>
-      <c r="D25" t="s">
-        <v>491</v>
-      </c>
       <c r="E25" t="s">
         <v>10</v>
       </c>
@@ -10792,16 +10795,16 @@
         <v>20</v>
       </c>
       <c r="G25" t="s">
+        <v>168</v>
+      </c>
+      <c r="H25" t="s">
         <v>169</v>
       </c>
-      <c r="H25" t="s">
-        <v>170</v>
-      </c>
       <c r="J25" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="K25" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L25">
         <v>1.6182682752282065</v>
@@ -10810,14 +10813,14 @@
         <v>0.1260421379882968</v>
       </c>
       <c r="O25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P25" t="s">
+        <v>519</v>
+      </c>
+      <c r="Q25" t="s">
         <v>520</v>
       </c>
-      <c r="Q25" t="s">
-        <v>521</v>
-      </c>
       <c r="R25" t="s">
         <v>10</v>
       </c>
@@ -10825,16 +10828,16 @@
         <v>20</v>
       </c>
       <c r="T25" t="s">
+        <v>168</v>
+      </c>
+      <c r="U25" t="s">
         <v>169</v>
       </c>
-      <c r="U25" t="s">
-        <v>170</v>
-      </c>
       <c r="W25" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="X25" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="Y25">
         <v>164.86799999999999</v>
@@ -10845,14 +10848,14 @@
     </row>
     <row r="26" spans="2:26">
       <c r="O26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P26" t="s">
+        <v>521</v>
+      </c>
+      <c r="Q26" t="s">
         <v>522</v>
       </c>
-      <c r="Q26" t="s">
-        <v>523</v>
-      </c>
       <c r="R26" t="s">
         <v>10</v>
       </c>
@@ -10860,16 +10863,16 @@
         <v>20</v>
       </c>
       <c r="T26" t="s">
+        <v>168</v>
+      </c>
+      <c r="U26" t="s">
         <v>169</v>
       </c>
-      <c r="U26" t="s">
-        <v>170</v>
-      </c>
       <c r="W26" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X26" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Y26">
         <v>177.54</v>
@@ -10880,14 +10883,14 @@
     </row>
     <row r="27" spans="2:26">
       <c r="O27" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P27" t="s">
+        <v>523</v>
+      </c>
+      <c r="Q27" t="s">
         <v>524</v>
       </c>
-      <c r="Q27" t="s">
-        <v>525</v>
-      </c>
       <c r="R27" t="s">
         <v>10</v>
       </c>
@@ -10895,16 +10898,16 @@
         <v>20</v>
       </c>
       <c r="T27" t="s">
+        <v>168</v>
+      </c>
+      <c r="U27" t="s">
         <v>169</v>
       </c>
-      <c r="U27" t="s">
-        <v>170</v>
-      </c>
       <c r="W27" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="X27" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="Y27">
         <v>234.209</v>
@@ -10915,14 +10918,14 @@
     </row>
     <row r="28" spans="2:26">
       <c r="O28" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P28" t="s">
+        <v>525</v>
+      </c>
+      <c r="Q28" t="s">
         <v>526</v>
       </c>
-      <c r="Q28" t="s">
-        <v>527</v>
-      </c>
       <c r="R28" t="s">
         <v>10</v>
       </c>
@@ -10930,16 +10933,16 @@
         <v>20</v>
       </c>
       <c r="T28" t="s">
+        <v>168</v>
+      </c>
+      <c r="U28" t="s">
         <v>169</v>
       </c>
-      <c r="U28" t="s">
-        <v>170</v>
-      </c>
       <c r="W28" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="X28" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Y28">
         <v>244.34299999999999</v>
@@ -10950,14 +10953,14 @@
     </row>
     <row r="29" spans="2:26">
       <c r="O29" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P29" t="s">
+        <v>527</v>
+      </c>
+      <c r="Q29" t="s">
         <v>528</v>
       </c>
-      <c r="Q29" t="s">
-        <v>529</v>
-      </c>
       <c r="R29" t="s">
         <v>10</v>
       </c>
@@ -10965,16 +10968,16 @@
         <v>20</v>
       </c>
       <c r="T29" t="s">
+        <v>168</v>
+      </c>
+      <c r="U29" t="s">
         <v>169</v>
       </c>
-      <c r="U29" t="s">
-        <v>170</v>
-      </c>
       <c r="W29" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="X29" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Y29">
         <v>96.406999999999996</v>
@@ -10985,14 +10988,14 @@
     </row>
     <row r="30" spans="2:26">
       <c r="O30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P30" t="s">
+        <v>529</v>
+      </c>
+      <c r="Q30" t="s">
         <v>530</v>
       </c>
-      <c r="Q30" t="s">
-        <v>531</v>
-      </c>
       <c r="R30" t="s">
         <v>10</v>
       </c>
@@ -11000,16 +11003,16 @@
         <v>20</v>
       </c>
       <c r="T30" t="s">
+        <v>168</v>
+      </c>
+      <c r="U30" t="s">
         <v>169</v>
       </c>
-      <c r="U30" t="s">
-        <v>170</v>
-      </c>
       <c r="W30" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="X30" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Y30">
         <v>60.06</v>
@@ -11020,14 +11023,14 @@
     </row>
     <row r="31" spans="2:26">
       <c r="O31" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P31" t="s">
+        <v>531</v>
+      </c>
+      <c r="Q31" t="s">
         <v>532</v>
       </c>
-      <c r="Q31" t="s">
-        <v>533</v>
-      </c>
       <c r="R31" t="s">
         <v>10</v>
       </c>
@@ -11035,16 +11038,16 @@
         <v>20</v>
       </c>
       <c r="T31" t="s">
+        <v>168</v>
+      </c>
+      <c r="U31" t="s">
         <v>169</v>
       </c>
-      <c r="U31" t="s">
-        <v>170</v>
-      </c>
       <c r="W31" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="X31" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="Y31">
         <v>142.483</v>
@@ -11055,14 +11058,14 @@
     </row>
     <row r="32" spans="2:26">
       <c r="O32" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P32" t="s">
+        <v>533</v>
+      </c>
+      <c r="Q32" t="s">
         <v>534</v>
       </c>
-      <c r="Q32" t="s">
-        <v>535</v>
-      </c>
       <c r="R32" t="s">
         <v>10</v>
       </c>
@@ -11070,16 +11073,16 @@
         <v>20</v>
       </c>
       <c r="T32" t="s">
+        <v>168</v>
+      </c>
+      <c r="U32" t="s">
         <v>169</v>
       </c>
-      <c r="U32" t="s">
-        <v>170</v>
-      </c>
       <c r="W32" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="X32" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Y32">
         <v>72.956000000000003</v>
@@ -11090,14 +11093,14 @@
     </row>
     <row r="33" spans="15:26">
       <c r="O33" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P33" t="s">
+        <v>535</v>
+      </c>
+      <c r="Q33" t="s">
         <v>536</v>
       </c>
-      <c r="Q33" t="s">
-        <v>537</v>
-      </c>
       <c r="R33" t="s">
         <v>10</v>
       </c>
@@ -11105,16 +11108,16 @@
         <v>20</v>
       </c>
       <c r="T33" t="s">
+        <v>168</v>
+      </c>
+      <c r="U33" t="s">
         <v>169</v>
       </c>
-      <c r="U33" t="s">
-        <v>170</v>
-      </c>
       <c r="W33" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="X33" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Y33">
         <v>19.841000000000001</v>
@@ -11125,14 +11128,14 @@
     </row>
     <row r="34" spans="15:26">
       <c r="O34" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P34" t="s">
+        <v>537</v>
+      </c>
+      <c r="Q34" t="s">
         <v>538</v>
       </c>
-      <c r="Q34" t="s">
-        <v>539</v>
-      </c>
       <c r="R34" t="s">
         <v>10</v>
       </c>
@@ -11140,16 +11143,16 @@
         <v>20</v>
       </c>
       <c r="T34" t="s">
+        <v>168</v>
+      </c>
+      <c r="U34" t="s">
         <v>169</v>
       </c>
-      <c r="U34" t="s">
-        <v>170</v>
-      </c>
       <c r="W34" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="X34" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Y34">
         <v>138.42500000000001</v>
@@ -11160,14 +11163,14 @@
     </row>
     <row r="35" spans="15:26">
       <c r="O35" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P35" t="s">
+        <v>539</v>
+      </c>
+      <c r="Q35" t="s">
         <v>540</v>
       </c>
-      <c r="Q35" t="s">
-        <v>541</v>
-      </c>
       <c r="R35" t="s">
         <v>10</v>
       </c>
@@ -11175,16 +11178,16 @@
         <v>20</v>
       </c>
       <c r="T35" t="s">
+        <v>168</v>
+      </c>
+      <c r="U35" t="s">
         <v>169</v>
       </c>
-      <c r="U35" t="s">
-        <v>170</v>
-      </c>
       <c r="W35" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="X35" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Y35">
         <v>69.513999999999996</v>
@@ -11195,14 +11198,14 @@
     </row>
     <row r="36" spans="15:26">
       <c r="O36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P36" t="s">
+        <v>541</v>
+      </c>
+      <c r="Q36" t="s">
         <v>542</v>
       </c>
-      <c r="Q36" t="s">
-        <v>543</v>
-      </c>
       <c r="R36" t="s">
         <v>10</v>
       </c>
@@ -11210,16 +11213,16 @@
         <v>20</v>
       </c>
       <c r="T36" t="s">
+        <v>168</v>
+      </c>
+      <c r="U36" t="s">
         <v>169</v>
       </c>
-      <c r="U36" t="s">
-        <v>170</v>
-      </c>
       <c r="W36" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="X36" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Y36">
         <v>60.743000000000002</v>
@@ -11230,14 +11233,14 @@
     </row>
     <row r="37" spans="15:26">
       <c r="O37" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P37" t="s">
+        <v>543</v>
+      </c>
+      <c r="Q37" t="s">
         <v>544</v>
       </c>
-      <c r="Q37" t="s">
-        <v>545</v>
-      </c>
       <c r="R37" t="s">
         <v>10</v>
       </c>
@@ -11245,16 +11248,16 @@
         <v>20</v>
       </c>
       <c r="T37" t="s">
+        <v>168</v>
+      </c>
+      <c r="U37" t="s">
         <v>169</v>
       </c>
-      <c r="U37" t="s">
-        <v>170</v>
-      </c>
       <c r="W37" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="X37" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y37">
         <v>6.194</v>
@@ -11265,14 +11268,14 @@
     </row>
     <row r="38" spans="15:26">
       <c r="O38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P38" t="s">
+        <v>545</v>
+      </c>
+      <c r="Q38" t="s">
         <v>546</v>
       </c>
-      <c r="Q38" t="s">
-        <v>547</v>
-      </c>
       <c r="R38" t="s">
         <v>10</v>
       </c>
@@ -11280,16 +11283,16 @@
         <v>20</v>
       </c>
       <c r="T38" t="s">
+        <v>168</v>
+      </c>
+      <c r="U38" t="s">
         <v>169</v>
       </c>
-      <c r="U38" t="s">
-        <v>170</v>
-      </c>
       <c r="W38" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="X38" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="Y38">
         <v>44.996000000000002</v>
@@ -11300,14 +11303,14 @@
     </row>
     <row r="39" spans="15:26">
       <c r="O39" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P39" t="s">
+        <v>547</v>
+      </c>
+      <c r="Q39" t="s">
         <v>548</v>
       </c>
-      <c r="Q39" t="s">
-        <v>549</v>
-      </c>
       <c r="R39" t="s">
         <v>10</v>
       </c>
@@ -11315,16 +11318,16 @@
         <v>20</v>
       </c>
       <c r="T39" t="s">
+        <v>168</v>
+      </c>
+      <c r="U39" t="s">
         <v>169</v>
       </c>
-      <c r="U39" t="s">
-        <v>170</v>
-      </c>
       <c r="W39" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X39" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Y39">
         <v>45.517000000000003</v>
@@ -11335,14 +11338,14 @@
     </row>
     <row r="40" spans="15:26">
       <c r="O40" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P40" t="s">
+        <v>549</v>
+      </c>
+      <c r="Q40" t="s">
         <v>550</v>
       </c>
-      <c r="Q40" t="s">
-        <v>551</v>
-      </c>
       <c r="R40" t="s">
         <v>10</v>
       </c>
@@ -11350,16 +11353,16 @@
         <v>20</v>
       </c>
       <c r="T40" t="s">
+        <v>168</v>
+      </c>
+      <c r="U40" t="s">
         <v>169</v>
       </c>
-      <c r="U40" t="s">
-        <v>170</v>
-      </c>
       <c r="W40" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="X40" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Y40">
         <v>76.210999999999999</v>
@@ -11370,14 +11373,14 @@
     </row>
     <row r="41" spans="15:26">
       <c r="O41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P41" t="s">
+        <v>551</v>
+      </c>
+      <c r="Q41" t="s">
         <v>552</v>
       </c>
-      <c r="Q41" t="s">
-        <v>553</v>
-      </c>
       <c r="R41" t="s">
         <v>10</v>
       </c>
@@ -11385,16 +11388,16 @@
         <v>20</v>
       </c>
       <c r="T41" t="s">
+        <v>168</v>
+      </c>
+      <c r="U41" t="s">
         <v>169</v>
       </c>
-      <c r="U41" t="s">
-        <v>170</v>
-      </c>
       <c r="W41" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="X41" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Y41">
         <v>20.327999999999999</v>
@@ -11405,14 +11408,14 @@
     </row>
     <row r="42" spans="15:26">
       <c r="O42" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P42" t="s">
+        <v>553</v>
+      </c>
+      <c r="Q42" t="s">
         <v>554</v>
       </c>
-      <c r="Q42" t="s">
-        <v>555</v>
-      </c>
       <c r="R42" t="s">
         <v>10</v>
       </c>
@@ -11420,16 +11423,16 @@
         <v>20</v>
       </c>
       <c r="T42" t="s">
+        <v>168</v>
+      </c>
+      <c r="U42" t="s">
         <v>169</v>
       </c>
-      <c r="U42" t="s">
-        <v>170</v>
-      </c>
       <c r="W42" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="X42" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Y42">
         <v>65.320999999999998</v>
@@ -11440,14 +11443,14 @@
     </row>
     <row r="43" spans="15:26">
       <c r="O43" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P43" t="s">
+        <v>555</v>
+      </c>
+      <c r="Q43" t="s">
         <v>556</v>
       </c>
-      <c r="Q43" t="s">
-        <v>557</v>
-      </c>
       <c r="R43" t="s">
         <v>10</v>
       </c>
@@ -11455,16 +11458,16 @@
         <v>20</v>
       </c>
       <c r="T43" t="s">
+        <v>168</v>
+      </c>
+      <c r="U43" t="s">
         <v>169</v>
       </c>
-      <c r="U43" t="s">
-        <v>170</v>
-      </c>
       <c r="W43" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="X43" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="Y43">
         <v>32.902000000000001</v>
@@ -11480,26 +11483,26 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B6ACE87-10DB-4D24-9E2C-7F47D0E68560}">
-  <dimension ref="B9:P73"/>
+  <dimension ref="B9:P75"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:16">
       <c r="B9" t="s">
-        <v>201</v>
+        <v>588</v>
       </c>
       <c r="J9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="2:16">
       <c r="B10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E10">
         <v>2023</v>
@@ -11514,30 +11517,30 @@
         <v>53</v>
       </c>
       <c r="J10" t="s">
+        <v>158</v>
+      </c>
+      <c r="K10" t="s">
         <v>159</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>160</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>161</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>162</v>
       </c>
-      <c r="N10" t="s">
+      <c r="O10" t="s">
         <v>163</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>164</v>
-      </c>
-      <c r="P10" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="11" spans="2:16">
       <c r="B11" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C11" t="s">
         <v>30</v>
@@ -11555,13 +11558,13 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="H11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K11" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="M11" t="s">
         <v>10</v>
@@ -11570,15 +11573,15 @@
         <v>20</v>
       </c>
       <c r="O11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P11" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C12" t="s">
         <v>30</v>
@@ -11596,13 +11599,13 @@
         <v>0.5</v>
       </c>
       <c r="H12" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="J12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K12" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M12" t="s">
         <v>10</v>
@@ -11611,15 +11614,15 @@
         <v>20</v>
       </c>
       <c r="O12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P12" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C13" t="s">
         <v>30</v>
@@ -11637,13 +11640,13 @@
         <v>5150</v>
       </c>
       <c r="H13" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="J13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K13" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M13" t="s">
         <v>10</v>
@@ -11652,15 +11655,15 @@
         <v>20</v>
       </c>
       <c r="O13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P13" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="B14" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C14" t="s">
         <v>30</v>
@@ -11678,13 +11681,13 @@
         <v>180</v>
       </c>
       <c r="H14" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="J14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K14" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="M14" t="s">
         <v>10</v>
@@ -11693,15 +11696,15 @@
         <v>20</v>
       </c>
       <c r="O14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P14" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="B15" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C15" t="s">
         <v>30</v>
@@ -11719,13 +11722,13 @@
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="J15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K15" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="M15" t="s">
         <v>10</v>
@@ -11734,15 +11737,15 @@
         <v>20</v>
       </c>
       <c r="O15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P15" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="16" spans="2:16">
       <c r="B16" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C16" t="s">
         <v>30</v>
@@ -11760,13 +11763,13 @@
         <v>0.35000000000000003</v>
       </c>
       <c r="H16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K16" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="M16" t="s">
         <v>10</v>
@@ -11775,15 +11778,15 @@
         <v>20</v>
       </c>
       <c r="O16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P16" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="17" spans="2:16">
       <c r="B17" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C17" t="s">
         <v>30</v>
@@ -11801,13 +11804,13 @@
         <v>0.5</v>
       </c>
       <c r="H17" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="J17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K17" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="M17" t="s">
         <v>10</v>
@@ -11816,15 +11819,15 @@
         <v>20</v>
       </c>
       <c r="O17" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P17" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="18" spans="2:16">
       <c r="B18" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C18" t="s">
         <v>30</v>
@@ -11842,13 +11845,13 @@
         <v>2400</v>
       </c>
       <c r="H18" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="J18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K18" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="M18" t="s">
         <v>10</v>
@@ -11857,15 +11860,15 @@
         <v>20</v>
       </c>
       <c r="O18" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P18" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C19" t="s">
         <v>30</v>
@@ -11883,13 +11886,13 @@
         <v>85</v>
       </c>
       <c r="H19" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="J19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K19" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="M19" t="s">
         <v>10</v>
@@ -11898,15 +11901,15 @@
         <v>20</v>
       </c>
       <c r="O19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P19" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C20" t="s">
         <v>30</v>
@@ -11924,13 +11927,13 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="J20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K20" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="M20" t="s">
         <v>10</v>
@@ -11939,15 +11942,15 @@
         <v>20</v>
       </c>
       <c r="O20" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P20" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C21" t="s">
         <v>32</v>
@@ -11965,13 +11968,13 @@
         <v>0.61</v>
       </c>
       <c r="H21" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K21" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="M21" t="s">
         <v>10</v>
@@ -11980,15 +11983,15 @@
         <v>20</v>
       </c>
       <c r="O21" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P21" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="22" spans="2:16">
       <c r="B22" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C22" t="s">
         <v>32</v>
@@ -12006,13 +12009,13 @@
         <v>1000</v>
       </c>
       <c r="H22" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="J22" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K22" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="M22" t="s">
         <v>10</v>
@@ -12021,15 +12024,15 @@
         <v>20</v>
       </c>
       <c r="O22" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P22" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C23" t="s">
         <v>32</v>
@@ -12047,13 +12050,13 @@
         <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="J23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K23" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="M23" t="s">
         <v>10</v>
@@ -12062,15 +12065,15 @@
         <v>20</v>
       </c>
       <c r="O23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P23" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="24" spans="2:16">
       <c r="B24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C24" t="s">
         <v>32</v>
@@ -12088,13 +12091,13 @@
         <v>0.54</v>
       </c>
       <c r="H24" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K24" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="M24" t="s">
         <v>10</v>
@@ -12103,15 +12106,15 @@
         <v>20</v>
       </c>
       <c r="O24" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P24" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="25" spans="2:16">
       <c r="B25" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C25" t="s">
         <v>32</v>
@@ -12129,13 +12132,13 @@
         <v>2350</v>
       </c>
       <c r="H25" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="J25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K25" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="M25" t="s">
         <v>10</v>
@@ -12144,15 +12147,15 @@
         <v>20</v>
       </c>
       <c r="O25" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P25" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="26" spans="2:16">
       <c r="B26" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C26" t="s">
         <v>32</v>
@@ -12170,30 +12173,12 @@
         <v>60</v>
       </c>
       <c r="H26" t="s">
-        <v>561</v>
-      </c>
-      <c r="J26" t="s">
-        <v>166</v>
-      </c>
-      <c r="K26" t="s">
-        <v>577</v>
-      </c>
-      <c r="M26" t="s">
-        <v>10</v>
-      </c>
-      <c r="N26" t="s">
-        <v>20</v>
-      </c>
-      <c r="O26" t="s">
-        <v>226</v>
-      </c>
-      <c r="P26" t="s">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C27" t="s">
         <v>31</v>
@@ -12211,30 +12196,30 @@
         <v>0.4</v>
       </c>
       <c r="H27" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J27" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K27" t="s">
+        <v>576</v>
+      </c>
+      <c r="M27" t="s">
+        <v>10</v>
+      </c>
+      <c r="N27" t="s">
+        <v>20</v>
+      </c>
+      <c r="O27" t="s">
+        <v>225</v>
+      </c>
+      <c r="P27" t="s">
         <v>579</v>
-      </c>
-      <c r="M27" t="s">
-        <v>10</v>
-      </c>
-      <c r="N27" t="s">
-        <v>20</v>
-      </c>
-      <c r="O27" t="s">
-        <v>226</v>
-      </c>
-      <c r="P27" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C28" t="s">
         <v>31</v>
@@ -12252,12 +12237,30 @@
         <v>4300</v>
       </c>
       <c r="H28" t="s">
-        <v>560</v>
+        <v>559</v>
+      </c>
+      <c r="J28" t="s">
+        <v>165</v>
+      </c>
+      <c r="K28" t="s">
+        <v>578</v>
+      </c>
+      <c r="M28" t="s">
+        <v>10</v>
+      </c>
+      <c r="N28" t="s">
+        <v>20</v>
+      </c>
+      <c r="O28" t="s">
+        <v>225</v>
+      </c>
+      <c r="P28" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C29" t="s">
         <v>31</v>
@@ -12275,12 +12278,12 @@
         <v>130</v>
       </c>
       <c r="H29" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -12298,12 +12301,12 @@
         <v>0.42</v>
       </c>
       <c r="H30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="2:16">
       <c r="B31" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C31" t="s">
         <v>32</v>
@@ -12321,12 +12324,12 @@
         <v>500</v>
       </c>
       <c r="H31" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="32" spans="2:16">
       <c r="B32" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C32" t="s">
         <v>32</v>
@@ -12344,12 +12347,12 @@
         <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C33" t="s">
         <v>27</v>
@@ -12367,12 +12370,12 @@
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" spans="2:8">
       <c r="B34" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C34" t="s">
         <v>27</v>
@@ -12390,12 +12393,12 @@
         <v>0.4</v>
       </c>
       <c r="H34" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="B35" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C35" t="s">
         <v>27</v>
@@ -12413,12 +12416,12 @@
         <v>2700</v>
       </c>
       <c r="H35" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C36" t="s">
         <v>27</v>
@@ -12436,12 +12439,12 @@
         <v>65</v>
       </c>
       <c r="H36" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C37" t="s">
         <v>27</v>
@@ -12459,12 +12462,12 @@
         <v>4</v>
       </c>
       <c r="H37" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C38" t="s">
         <v>32</v>
@@ -12482,12 +12485,12 @@
         <v>0.5</v>
       </c>
       <c r="H38" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C39" t="s">
         <v>32</v>
@@ -12505,12 +12508,12 @@
         <v>2400</v>
       </c>
       <c r="H39" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C40" t="s">
         <v>32</v>
@@ -12528,12 +12531,12 @@
         <v>85</v>
       </c>
       <c r="H40" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C41" t="s">
         <v>31</v>
@@ -12551,12 +12554,12 @@
         <v>0.43</v>
       </c>
       <c r="H41" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" spans="2:8">
       <c r="B42" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C42" t="s">
         <v>31</v>
@@ -12574,12 +12577,12 @@
         <v>5100</v>
       </c>
       <c r="H42" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C43" t="s">
         <v>31</v>
@@ -12597,12 +12600,12 @@
         <v>180</v>
       </c>
       <c r="H43" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C44" t="s">
         <v>35</v>
@@ -12620,12 +12623,12 @@
         <v>0.33</v>
       </c>
       <c r="H44" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45" spans="2:8">
       <c r="B45" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C45" t="s">
         <v>35</v>
@@ -12643,12 +12646,12 @@
         <v>4500</v>
       </c>
       <c r="H45" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C46" t="s">
         <v>35</v>
@@ -12666,12 +12669,12 @@
         <v>175</v>
       </c>
       <c r="H46" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="B47" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C47" t="s">
         <v>31</v>
@@ -12689,12 +12692,12 @@
         <v>0.4</v>
       </c>
       <c r="H47" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="2:8">
       <c r="B48" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C48" t="s">
         <v>31</v>
@@ -12712,12 +12715,12 @@
         <v>5150</v>
       </c>
       <c r="H48" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C49" t="s">
         <v>31</v>
@@ -12735,12 +12738,12 @@
         <v>155</v>
       </c>
       <c r="H49" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="50" spans="2:8">
       <c r="B50" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C50" t="s">
         <v>26</v>
@@ -12758,12 +12761,12 @@
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="51" spans="2:8">
       <c r="B51" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C51" t="s">
         <v>26</v>
@@ -12781,12 +12784,12 @@
         <v>0.23</v>
       </c>
       <c r="H51" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C52" t="s">
         <v>26</v>
@@ -12804,12 +12807,12 @@
         <v>480</v>
       </c>
       <c r="H52" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C53" t="s">
         <v>26</v>
@@ -12827,12 +12830,12 @@
         <v>16</v>
       </c>
       <c r="H53" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="54" spans="2:8">
       <c r="B54" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C54" t="s">
         <v>26</v>
@@ -12850,12 +12853,12 @@
         <v>1.5</v>
       </c>
       <c r="H54" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C55" t="s">
         <v>31</v>
@@ -12873,12 +12876,12 @@
         <v>0.39</v>
       </c>
       <c r="H55" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="56" spans="2:8">
       <c r="B56" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C56" t="s">
         <v>31</v>
@@ -12896,12 +12899,12 @@
         <v>1800</v>
       </c>
       <c r="H56" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="B57" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C57" t="s">
         <v>31</v>
@@ -12919,12 +12922,12 @@
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="B58" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C58" t="s">
         <v>31</v>
@@ -12942,12 +12945,12 @@
         <v>0.43</v>
       </c>
       <c r="H58" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="59" spans="2:8">
       <c r="B59" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C59" t="s">
         <v>31</v>
@@ -12965,12 +12968,12 @@
         <v>2100</v>
       </c>
       <c r="H59" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="60" spans="2:8">
       <c r="B60" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C60" t="s">
         <v>31</v>
@@ -12988,12 +12991,12 @@
         <v>65</v>
       </c>
       <c r="H60" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="B61" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C61" t="s">
         <v>31</v>
@@ -13011,12 +13014,12 @@
         <v>0.48</v>
       </c>
       <c r="H61" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="62" spans="2:8">
       <c r="B62" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C62" t="s">
         <v>31</v>
@@ -13034,12 +13037,12 @@
         <v>2300</v>
       </c>
       <c r="H62" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="B63" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C63" t="s">
         <v>31</v>
@@ -13057,237 +13060,237 @@
         <v>70</v>
       </c>
       <c r="H63" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8">
-      <c r="B64" t="s">
-        <v>577</v>
-      </c>
-      <c r="C64" t="s">
-        <v>578</v>
-      </c>
-      <c r="D64" t="s">
-        <v>19</v>
-      </c>
-      <c r="E64">
-        <v>1</v>
-      </c>
-      <c r="F64">
-        <v>1</v>
-      </c>
-      <c r="G64">
-        <v>1</v>
-      </c>
-      <c r="H64" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="65" spans="2:8">
-      <c r="B65" t="s">
-        <v>577</v>
-      </c>
-      <c r="C65" t="s">
-        <v>578</v>
-      </c>
-      <c r="D65" t="s">
-        <v>19</v>
-      </c>
-      <c r="E65">
-        <v>0.41000000000000003</v>
-      </c>
-      <c r="F65">
-        <v>0.46</v>
-      </c>
-      <c r="G65">
-        <v>0.49</v>
-      </c>
-      <c r="H65" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="66" spans="2:8">
       <c r="B66" t="s">
+        <v>576</v>
+      </c>
+      <c r="C66" t="s">
         <v>577</v>
-      </c>
-      <c r="C66" t="s">
-        <v>578</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
       </c>
       <c r="E66">
-        <v>4060</v>
+        <v>1</v>
       </c>
       <c r="F66">
-        <v>2760</v>
+        <v>1</v>
       </c>
       <c r="G66">
-        <v>1980</v>
+        <v>1</v>
       </c>
       <c r="H66" t="s">
-        <v>560</v>
+        <v>142</v>
       </c>
     </row>
     <row r="67" spans="2:8">
       <c r="B67" t="s">
+        <v>576</v>
+      </c>
+      <c r="C67" t="s">
         <v>577</v>
-      </c>
-      <c r="C67" t="s">
-        <v>578</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
       </c>
       <c r="E67">
-        <v>120</v>
+        <v>0.41000000000000003</v>
       </c>
       <c r="F67">
-        <v>95</v>
+        <v>0.46</v>
       </c>
       <c r="G67">
-        <v>70</v>
+        <v>0.49</v>
       </c>
       <c r="H67" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="68" spans="2:8">
       <c r="B68" t="s">
+        <v>576</v>
+      </c>
+      <c r="C68" t="s">
         <v>577</v>
-      </c>
-      <c r="C68" t="s">
-        <v>578</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
       </c>
       <c r="E68">
-        <v>3</v>
+        <v>4060</v>
       </c>
       <c r="F68">
-        <v>3</v>
+        <v>2760</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>1980</v>
       </c>
       <c r="H68" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="69" spans="2:8">
       <c r="B69" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C69" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="F69">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="H69" t="s">
-        <v>143</v>
+        <v>560</v>
       </c>
     </row>
     <row r="70" spans="2:8">
       <c r="B70" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C70" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D70" t="s">
         <v>19</v>
       </c>
       <c r="E70">
-        <v>0.42</v>
+        <v>3</v>
       </c>
       <c r="F70">
-        <v>0.43</v>
+        <v>3</v>
       </c>
       <c r="G70">
-        <v>0.44</v>
+        <v>3</v>
       </c>
       <c r="H70" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C71" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D71" t="s">
         <v>19</v>
       </c>
       <c r="E71">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="F71">
-        <v>1430</v>
+        <v>1</v>
       </c>
       <c r="G71">
-        <v>1370</v>
+        <v>1</v>
       </c>
       <c r="H71" t="s">
-        <v>560</v>
+        <v>142</v>
       </c>
     </row>
     <row r="72" spans="2:8">
       <c r="B72" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C72" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D72" t="s">
         <v>19</v>
       </c>
       <c r="E72">
-        <v>38</v>
+        <v>0.42</v>
       </c>
       <c r="F72">
-        <v>36</v>
+        <v>0.43</v>
       </c>
       <c r="G72">
-        <v>36</v>
+        <v>0.44</v>
       </c>
       <c r="H72" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="73" spans="2:8">
       <c r="B73" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C73" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D73" t="s">
         <v>19</v>
       </c>
       <c r="E73">
+        <v>1500</v>
+      </c>
+      <c r="F73">
+        <v>1430</v>
+      </c>
+      <c r="G73">
+        <v>1370</v>
+      </c>
+      <c r="H73" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8">
+      <c r="B74" t="s">
+        <v>578</v>
+      </c>
+      <c r="C74" t="s">
+        <v>577</v>
+      </c>
+      <c r="D74" t="s">
+        <v>19</v>
+      </c>
+      <c r="E74">
+        <v>38</v>
+      </c>
+      <c r="F74">
+        <v>36</v>
+      </c>
+      <c r="G74">
+        <v>36</v>
+      </c>
+      <c r="H74" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="75" spans="2:8">
+      <c r="B75" t="s">
+        <v>578</v>
+      </c>
+      <c r="C75" t="s">
+        <v>577</v>
+      </c>
+      <c r="D75" t="s">
+        <v>19</v>
+      </c>
+      <c r="E75">
         <v>1.5</v>
       </c>
-      <c r="F73">
+      <c r="F75">
         <v>1.5</v>
       </c>
-      <c r="G73">
+      <c r="G75">
         <v>1.5</v>
       </c>
-      <c r="H73" t="s">
-        <v>562</v>
+      <c r="H75" t="s">
+        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B51EFDC-50DF-4216-AB1A-12C32B1053F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C457755C-0EB5-477D-B422-23BB7DAB2DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2001" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1958" uniqueCount="571">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -121,9 +121,6 @@
     <t>TWh</t>
   </si>
   <si>
-    <t>elc_buildings,elc_industry,elc_transport</t>
-  </si>
-  <si>
     <t>~FI_Comm</t>
   </si>
   <si>
@@ -157,16 +154,10 @@
     <t>gas</t>
   </si>
   <si>
-    <t>geothermal</t>
-  </si>
-  <si>
     <t>hydrogen</t>
   </si>
   <si>
     <t>nuclear</t>
-  </si>
-  <si>
-    <t>oil</t>
   </si>
   <si>
     <t>Csets</t>
@@ -406,15 +397,6 @@
     <t>STG</t>
   </si>
   <si>
-    <t>Trd_electricity import</t>
-  </si>
-  <si>
-    <t>Trd_electricity export</t>
-  </si>
-  <si>
-    <t>$/GJ</t>
-  </si>
-  <si>
     <t>invcost</t>
   </si>
   <si>
@@ -425,12 +407,6 @@
   </si>
   <si>
     <t>life</t>
-  </si>
-  <si>
-    <t>Demand sectors</t>
-  </si>
-  <si>
-    <t>generic fuel supply</t>
   </si>
   <si>
     <t>XXX</t>
@@ -558,24 +534,12 @@
     <t>efficiency</t>
   </si>
   <si>
-    <t>Hydrogen demand</t>
-  </si>
-  <si>
-    <t>hydrogen_allsect</t>
-  </si>
-  <si>
     <t>windon</t>
   </si>
   <si>
     <t>windoff</t>
   </si>
   <si>
-    <t>hydro and geothermal</t>
-  </si>
-  <si>
-    <t>renewable</t>
-  </si>
-  <si>
     <t>nuclear_fuel</t>
   </si>
   <si>
@@ -1869,25 +1833,7 @@
     <t>yes</t>
   </si>
   <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>\I: e_demand</t>
-  </si>
-  <si>
-    <t>\I: h_demand</t>
-  </si>
-  <si>
-    <t>\I: gas</t>
-  </si>
-  <si>
     <t>TRAELC</t>
-  </si>
-  <si>
-    <t>\I: bioenergy</t>
-  </si>
-  <si>
-    <t>\I: fossil_supply</t>
   </si>
   <si>
     <t>~FI_T: FX~USD21</t>
@@ -1908,7 +1854,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2052,13 +1998,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2391,7 +2330,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="155">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
@@ -2783,8 +2722,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="17"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3198,7 +3135,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{034C1C47-C7B1-48B4-9602-2B825216B37E}">
-  <dimension ref="B2:V21"/>
+  <dimension ref="B2:V17"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="10.1328125" bestFit="1" customWidth="1"/>
@@ -3222,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -3264,7 +3201,7 @@
         <v>5</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P3" s="1">
         <v>2022</v>
@@ -3273,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="S3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="2:22">
@@ -3348,14 +3285,14 @@
       <c r="Q5" s="1"/>
     </row>
     <row r="6" spans="2:22">
-      <c r="B6" t="s">
-        <v>580</v>
-      </c>
-      <c r="C6" s="147" t="s">
-        <v>581</v>
+      <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>20</v>
@@ -3368,36 +3305,32 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="str">
         <f>C6</f>
-        <v>\I: e_demand</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" s="1">
-        <v>1</v>
-      </c>
-      <c r="N6" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O6" s="1"/>
+        <v>nuclear_fuel</v>
+      </c>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1">
+        <f>V6*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
       <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="V6" t="s">
-        <v>97</v>
+      <c r="V6">
+        <v>0.1</v>
       </c>
     </row>
     <row r="7" spans="2:22">
-      <c r="B7" t="s">
-        <v>580</v>
-      </c>
-      <c r="C7" s="147" t="s">
-        <v>582</v>
+      <c r="B7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>20</v>
@@ -3410,408 +3343,142 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="str">
         <f>C7</f>
-        <v>\I: h_demand</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" t="s">
-        <v>144</v>
-      </c>
-      <c r="M7" s="1">
-        <v>1</v>
-      </c>
-      <c r="N7" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O7" s="1"/>
+        <v>solar_potential</v>
+      </c>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1">
+        <f>V7*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
       <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
+      <c r="V7">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="8" spans="2:22">
-      <c r="B8" t="s">
-        <v>580</v>
+      <c r="B8" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" s="1"/>
+        <v>140</v>
+      </c>
+      <c r="D8" t="s">
+        <v>143</v>
+      </c>
       <c r="E8" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F8" t="s">
         <v>10</v>
       </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
+      <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="str">
-        <f>C10</f>
-        <v>\I: fossil_supply</v>
+        <f>C8</f>
+        <v>winon_potential</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1" t="s">
-        <v>31</v>
+        <v>135</v>
       </c>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1">
-        <f t="shared" ref="O8:O12" si="0">V8*3.6</f>
-        <v>7.2</v>
+        <f>V8*3.6</f>
+        <v>0.36000000000000004</v>
       </c>
       <c r="P8" s="1"/>
-      <c r="V8" s="1">
-        <v>2</v>
+      <c r="V8">
+        <v>0.1</v>
       </c>
     </row>
     <row r="9" spans="2:22">
-      <c r="B9" t="s">
-        <v>580</v>
+      <c r="B9" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
-      </c>
-      <c r="D9" s="1"/>
+        <v>141</v>
+      </c>
+      <c r="D9" t="s">
+        <v>144</v>
+      </c>
       <c r="E9" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F9" t="s">
         <v>10</v>
       </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
+      <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
+      <c r="J9" s="1" t="str">
+        <f>C9</f>
+        <v>winoff_potential</v>
+      </c>
       <c r="K9" s="1"/>
-      <c r="L9" s="148" t="s">
-        <v>583</v>
+      <c r="L9" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <f t="shared" ref="O9" si="0">V9*3.6</f>
+        <v>0.36000000000000004</v>
       </c>
       <c r="P9" s="1"/>
-      <c r="V9" s="1">
-        <v>5</v>
+      <c r="V9">
+        <v>0.1</v>
       </c>
     </row>
     <row r="10" spans="2:22">
-      <c r="B10" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1">
-        <f>V10*3.6</f>
-        <v>36</v>
-      </c>
-      <c r="P10" s="1"/>
-      <c r="V10">
-        <v>10</v>
-      </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="B11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="1" t="str">
-        <f>C11</f>
-        <v>renewable</v>
-      </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1">
-        <f t="shared" si="0"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="P11" s="1"/>
-      <c r="V11">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="12" spans="2:22">
-      <c r="B12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1">
-        <f t="shared" si="0"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="P12" s="1"/>
-      <c r="V12">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-      <c r="L13" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1">
-        <f>V13*3.6</f>
-        <v>25.2</v>
-      </c>
-      <c r="P13" s="1"/>
-      <c r="V13" s="1">
-        <v>7</v>
-      </c>
     </row>
     <row r="14" spans="2:22">
-      <c r="B14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" t="s">
-        <v>152</v>
-      </c>
-      <c r="D14" t="s">
-        <v>155</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="1" t="str">
-        <f>C12</f>
-        <v>nuclear_fuel</v>
-      </c>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1">
-        <f>V14*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="P14" s="1"/>
-      <c r="V14">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" t="s">
-        <v>153</v>
-      </c>
-      <c r="D15" t="s">
-        <v>156</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="1" t="str">
-        <f>C13</f>
-        <v>solar_potential</v>
-      </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1">
-        <f>V15*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="P15" s="1"/>
-      <c r="V15">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="1" t="str">
-        <f>C14</f>
-        <v>winon_potential</v>
-      </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1">
-        <f>V16*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="P16" s="1"/>
-      <c r="V16">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="17" spans="2:22">
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
+    </row>
+    <row r="17" spans="8:9">
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="1" t="str">
-        <f>C15</f>
-        <v>winoff_potential</v>
-      </c>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1">
-        <f t="shared" ref="O17" si="1">V17*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="P17" s="1"/>
-      <c r="V17">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="20" spans="2:22">
-      <c r="J20" t="str">
-        <f>C8</f>
-        <v>Trd_electricity import</v>
-      </c>
-      <c r="L20" t="s">
-        <v>19</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>3</v>
-      </c>
-      <c r="R20">
-        <v>1000</v>
-      </c>
-      <c r="S20">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="2:22">
-      <c r="J21" t="str">
-        <f>C9</f>
-        <v>Trd_electricity export</v>
-      </c>
-      <c r="K21" t="s">
-        <v>19</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>3</v>
-      </c>
-      <c r="R21">
-        <v>1000</v>
-      </c>
-      <c r="S21">
-        <v>50</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3847,7 +3514,7 @@
   <sheetData>
     <row r="2" spans="2:23">
       <c r="B2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -3859,42 +3526,42 @@
     </row>
     <row r="3" spans="2:23">
       <c r="B3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="4" spans="2:23">
       <c r="B4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="5" t="s">
@@ -3905,13 +3572,13 @@
     </row>
     <row r="5" spans="2:23">
       <c r="C5" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="5" t="s">
@@ -3933,7 +3600,7 @@
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
       <c r="M8" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
@@ -3956,10 +3623,10 @@
         <v>7</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>11</v>
@@ -3969,16 +3636,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N9" s="6">
         <f>J35</f>
@@ -4012,24 +3679,24 @@
         <v>3</v>
       </c>
       <c r="V9" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="W9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="2:23">
       <c r="B10" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>10</v>
@@ -4039,13 +3706,13 @@
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>19</v>
@@ -4075,13 +3742,13 @@
     <row r="11" spans="2:23">
       <c r="B11" s="5"/>
       <c r="C11" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>10</v>
@@ -4091,13 +3758,13 @@
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J11" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="J11" s="6" t="s">
-        <v>64</v>
-      </c>
       <c r="K11" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>19</v>
@@ -4129,13 +3796,13 @@
       <c r="G12" s="5"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="J12" s="6" t="s">
-        <v>64</v>
-      </c>
       <c r="K12" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L12" s="6"/>
       <c r="M12" s="7" t="s">
@@ -4162,10 +3829,10 @@
       <c r="G13" s="5"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
@@ -4203,10 +3870,10 @@
     </row>
     <row r="14" spans="2:23">
       <c r="I14" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N14" s="4">
         <f>J44</f>
@@ -4239,10 +3906,10 @@
     </row>
     <row r="15" spans="2:23">
       <c r="I15" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J15" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M15" t="s">
         <v>18</v>
@@ -4259,10 +3926,10 @@
     </row>
     <row r="16" spans="2:23">
       <c r="I16" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J16" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="N16" s="9">
         <v>31.536000000000001</v>
@@ -4276,10 +3943,10 @@
     </row>
     <row r="17" spans="9:23">
       <c r="I17" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N17" s="4">
         <v>0.85</v>
@@ -4293,13 +3960,13 @@
     </row>
     <row r="18" spans="9:23">
       <c r="I18" t="s">
+        <v>56</v>
+      </c>
+      <c r="J18" t="s">
         <v>59</v>
       </c>
-      <c r="J18" t="s">
-        <v>62</v>
-      </c>
       <c r="K18" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>19</v>
@@ -4328,13 +3995,13 @@
     </row>
     <row r="19" spans="9:23">
       <c r="I19" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J19" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="K19" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="L19" t="s">
         <v>19</v>
@@ -4359,13 +4026,13 @@
     </row>
     <row r="20" spans="9:23">
       <c r="I20" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J20" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="K20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M20" t="s">
         <v>14</v>
@@ -4382,10 +4049,10 @@
     </row>
     <row r="21" spans="9:23">
       <c r="I21" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J21" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N21" s="4">
         <f>J49</f>
@@ -4418,10 +4085,10 @@
     </row>
     <row r="22" spans="9:23">
       <c r="I22" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J22" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N22" s="4">
         <f>J53</f>
@@ -4454,10 +4121,10 @@
     </row>
     <row r="23" spans="9:23">
       <c r="I23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J23" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M23" t="s">
         <v>18</v>
@@ -4474,10 +4141,10 @@
     </row>
     <row r="24" spans="9:23">
       <c r="I24" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J24" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="N24" s="9">
         <v>31.536000000000001</v>
@@ -4491,10 +4158,10 @@
     </row>
     <row r="25" spans="9:23">
       <c r="I25" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J25" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N25" s="4">
         <v>0.85</v>
@@ -4508,7 +4175,7 @@
     </row>
     <row r="31" spans="9:23" ht="15.75">
       <c r="I31" s="10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="J31" s="11"/>
       <c r="K31" s="11"/>
@@ -4520,7 +4187,7 @@
     </row>
     <row r="32" spans="9:23" ht="15.75">
       <c r="I32" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J32" s="11"/>
       <c r="K32" s="11"/>
@@ -4542,7 +4209,7 @@
     </row>
     <row r="34" spans="9:16" ht="15.75">
       <c r="I34" s="13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J34" s="14"/>
       <c r="K34" s="14"/>
@@ -4578,7 +4245,7 @@
     </row>
     <row r="36" spans="9:16" ht="15.75">
       <c r="I36" s="15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J36" s="14"/>
       <c r="K36" s="14"/>
@@ -4590,7 +4257,7 @@
     </row>
     <row r="37" spans="9:16" ht="15.75">
       <c r="I37" s="13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J37" s="14"/>
       <c r="K37" s="14"/>
@@ -4602,7 +4269,7 @@
     </row>
     <row r="38" spans="9:16" ht="15.75">
       <c r="I38" s="14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J38" s="16">
         <v>1363</v>
@@ -4628,7 +4295,7 @@
     </row>
     <row r="39" spans="9:16" ht="15.75">
       <c r="I39" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="J39" s="16">
         <v>1363</v>
@@ -4654,7 +4321,7 @@
     </row>
     <row r="40" spans="9:16" ht="15.75">
       <c r="I40" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J40" s="16">
         <v>1363</v>
@@ -4680,7 +4347,7 @@
     </row>
     <row r="41" spans="9:16" ht="15.75">
       <c r="I41" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J41" s="17"/>
       <c r="K41" s="17"/>
@@ -4692,7 +4359,7 @@
     </row>
     <row r="42" spans="9:16" ht="15.75">
       <c r="I42" s="14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J42" s="18">
         <v>34</v>
@@ -4718,7 +4385,7 @@
     </row>
     <row r="43" spans="9:16" ht="15.75">
       <c r="I43" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="J43" s="18">
         <v>34</v>
@@ -4744,7 +4411,7 @@
     </row>
     <row r="44" spans="9:16" ht="15.75">
       <c r="I44" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J44" s="18">
         <v>34</v>
@@ -4770,7 +4437,7 @@
     </row>
     <row r="45" spans="9:16" ht="15.75">
       <c r="I45" s="15" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J45" s="17"/>
       <c r="K45" s="17"/>
@@ -4782,7 +4449,7 @@
     </row>
     <row r="46" spans="9:16" ht="15.75">
       <c r="I46" s="13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J46" s="17"/>
       <c r="K46" s="17"/>
@@ -4794,7 +4461,7 @@
     </row>
     <row r="47" spans="9:16" ht="15.75">
       <c r="I47" s="14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J47" s="16">
         <v>2470</v>
@@ -4820,7 +4487,7 @@
     </row>
     <row r="48" spans="9:16" ht="15.75">
       <c r="I48" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="J48" s="16">
         <v>2470</v>
@@ -4846,7 +4513,7 @@
     </row>
     <row r="49" spans="9:16" ht="15.75">
       <c r="I49" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J49" s="16">
         <v>2470</v>
@@ -4872,7 +4539,7 @@
     </row>
     <row r="50" spans="9:16" ht="15.75">
       <c r="I50" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J50" s="17"/>
       <c r="K50" s="17"/>
@@ -4884,7 +4551,7 @@
     </row>
     <row r="51" spans="9:16" ht="15.75">
       <c r="I51" s="14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J51" s="18">
         <v>62</v>
@@ -4910,7 +4577,7 @@
     </row>
     <row r="52" spans="9:16" ht="15.75">
       <c r="I52" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="J52" s="18">
         <v>62</v>
@@ -4936,7 +4603,7 @@
     </row>
     <row r="53" spans="9:16" ht="15.75">
       <c r="I53" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J53" s="18">
         <v>62</v>
@@ -4972,7 +4639,7 @@
     </row>
     <row r="55" spans="9:16" ht="15.75">
       <c r="I55" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J55" s="11">
         <v>0.85</v>
@@ -4986,7 +4653,7 @@
     </row>
     <row r="56" spans="9:16" ht="15.75">
       <c r="I56" s="11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J56" s="11"/>
       <c r="K56" s="11"/>
@@ -4998,7 +4665,7 @@
     </row>
     <row r="57" spans="9:16" ht="15.75">
       <c r="I57" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J57" s="11"/>
       <c r="K57" s="11"/>
@@ -5091,7 +4758,7 @@
       <c r="F3" s="23"/>
       <c r="G3" s="23"/>
       <c r="H3" s="23" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="I3" s="23"/>
       <c r="J3" s="23"/>
@@ -5124,16 +4791,16 @@
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I4">
         <v>2030</v>
@@ -5142,22 +4809,22 @@
         <v>0</v>
       </c>
       <c r="K4" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="L4" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="M4" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="N4" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="O4" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="P4" s="23" t="s">
         <v>86</v>
-      </c>
-      <c r="L4" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="M4" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="N4" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="O4" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="P4" s="23" t="s">
-        <v>89</v>
       </c>
       <c r="Q4" s="23"/>
       <c r="R4" s="23" t="s">
@@ -5170,30 +4837,30 @@
         <v>7</v>
       </c>
       <c r="U4" s="23" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="V4" s="23" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="W4" s="23" t="s">
         <v>11</v>
       </c>
       <c r="X4" s="23" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="Y4" s="23" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="2:25">
       <c r="B5" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>584</v>
+        <v>568</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K5" s="23">
         <v>0.90249999999999997</v>
@@ -5216,14 +4883,14 @@
       </c>
       <c r="Q5" s="23"/>
       <c r="R5" s="23" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="S5" s="23" t="str">
         <f>B5</f>
         <v>ev_battery</v>
       </c>
       <c r="T5" s="23" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="U5" s="23" t="s">
         <v>20</v>
@@ -5240,7 +4907,7 @@
     <row r="6" spans="2:25">
       <c r="B6" s="23"/>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="K6" s="23"/>
       <c r="L6" s="24">
@@ -5263,10 +4930,10 @@
     <row r="7" spans="2:25">
       <c r="B7" s="23"/>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="23"/>
@@ -5296,7 +4963,7 @@
         <v>AuxStoIN</v>
       </c>
       <c r="H8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -5354,28 +5021,28 @@
   <sheetData>
     <row r="1" spans="1:18" ht="33.75" customHeight="1">
       <c r="A1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C1" s="149" t="s">
-        <v>105</v>
-      </c>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="150" t="s">
-        <v>106</v>
-      </c>
-      <c r="G1" s="149"/>
-      <c r="H1" s="151"/>
-      <c r="I1" s="149" t="s">
-        <v>107</v>
-      </c>
-      <c r="J1" s="149"/>
-      <c r="K1" s="149"/>
-      <c r="L1" s="149"/>
-      <c r="M1" s="149"/>
-      <c r="N1" s="149"/>
-      <c r="O1" s="152" t="s">
-        <v>108</v>
+        <v>96</v>
+      </c>
+      <c r="C1" s="147" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="147"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="147" t="s">
+        <v>99</v>
+      </c>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="150" t="s">
+        <v>100</v>
       </c>
       <c r="P1" s="27"/>
       <c r="Q1" s="27"/>
@@ -5383,44 +5050,44 @@
     </row>
     <row r="2" spans="1:18">
       <c r="C2" s="28" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I2" s="28" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="K2" s="28" t="str">
         <f>I2</f>
         <v>input~GASNGA</v>
       </c>
       <c r="L2" s="28" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="M2" s="28" t="str">
         <f>K2</f>
         <v>input~GASNGA</v>
       </c>
       <c r="N2" s="28" t="s">
-        <v>142</v>
-      </c>
-      <c r="O2" s="153"/>
+        <v>134</v>
+      </c>
+      <c r="O2" s="151"/>
       <c r="P2" s="27"/>
       <c r="Q2" s="27"/>
       <c r="R2" s="27"/>
@@ -5465,7 +5132,7 @@
       <c r="N3" s="28">
         <v>2050</v>
       </c>
-      <c r="O3" s="153"/>
+      <c r="O3" s="151"/>
       <c r="P3" s="27"/>
       <c r="Q3" s="27"/>
       <c r="R3" s="27"/>
@@ -5478,7 +5145,7 @@
         <v>2030</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="F4" s="30">
         <v>2015</v>
@@ -5487,27 +5154,27 @@
         <v>2030</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="I4" s="29" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="J4" s="29" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="K4" s="32" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="L4" s="33" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="M4" s="29" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="O4" s="154"/>
+        <v>109</v>
+      </c>
+      <c r="O4" s="152"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="27"/>
       <c r="R4" s="27"/>
@@ -5550,7 +5217,7 @@
         <v>9.4E-2</v>
       </c>
       <c r="O5" s="41" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="P5" s="42"/>
       <c r="Q5" s="42"/>
@@ -5594,7 +5261,7 @@
         <v>1.0940000000000001</v>
       </c>
       <c r="O6" s="50" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="P6" s="51"/>
       <c r="Q6" s="51"/>
@@ -5638,7 +5305,7 @@
         <v>9.4E-2</v>
       </c>
       <c r="O7" s="41" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="P7" s="42"/>
       <c r="Q7" s="42"/>
@@ -5682,7 +5349,7 @@
         <v>1.17</v>
       </c>
       <c r="O8" s="50" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="P8" s="51"/>
       <c r="Q8" s="51"/>
@@ -5726,7 +5393,7 @@
         <v>1.19</v>
       </c>
       <c r="O9" s="41" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="P9" s="42"/>
       <c r="Q9" s="42"/>
@@ -5770,7 +5437,7 @@
         <v>1.18</v>
       </c>
       <c r="O10" s="50" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="P10" s="51"/>
       <c r="Q10" s="51"/>
@@ -5814,7 +5481,7 @@
         <v>1.2</v>
       </c>
       <c r="O11" s="41" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="P11" s="42"/>
       <c r="Q11" s="42"/>
@@ -5858,7 +5525,7 @@
         <v>0.70799999999999996</v>
       </c>
       <c r="O12" s="50" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="P12" s="51"/>
       <c r="Q12" s="51"/>
@@ -5902,7 +5569,7 @@
         <v>0.72</v>
       </c>
       <c r="O13" s="41" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="P13" s="42"/>
       <c r="Q13" s="42"/>
@@ -5946,7 +5613,7 @@
         <v>0.01</v>
       </c>
       <c r="O14" s="62" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="P14" s="63"/>
       <c r="Q14" s="63"/>
@@ -5990,7 +5657,7 @@
         <v>0.06</v>
       </c>
       <c r="O15" s="72" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="P15" s="73"/>
       <c r="Q15" s="73"/>
@@ -6034,7 +5701,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="O16" s="82" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="P16" s="83"/>
       <c r="Q16" s="83"/>
@@ -6078,7 +5745,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="72" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="P17" s="73"/>
       <c r="Q17" s="73"/>
@@ -6122,7 +5789,7 @@
         <v>3.056E-2</v>
       </c>
       <c r="O18" s="92" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="P18" s="93"/>
       <c r="Q18" s="93"/>
@@ -6166,7 +5833,7 @@
         <v>0.02</v>
       </c>
       <c r="O19" s="103" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="P19" s="104"/>
       <c r="Q19" s="104"/>
@@ -6210,7 +5877,7 @@
         <v>1.5694083453910281</v>
       </c>
       <c r="O20" s="113" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="P20" s="93"/>
       <c r="Q20" s="93"/>
@@ -6254,7 +5921,7 @@
         <v>0.3</v>
       </c>
       <c r="O21" s="122" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="P21" s="123"/>
       <c r="Q21" s="123"/>
@@ -6298,7 +5965,7 @@
         <v>0.3</v>
       </c>
       <c r="O22" s="132" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="P22" s="133"/>
       <c r="Q22" s="133"/>
@@ -6342,7 +6009,7 @@
         <v>0.20588235294117646</v>
       </c>
       <c r="O23" s="142" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="P23" s="123"/>
       <c r="Q23" s="123"/>
@@ -6350,7 +6017,7 @@
     </row>
     <row r="26" spans="1:26" ht="17.25" thickBot="1">
       <c r="C26" s="143" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="T26" s="143" t="s">
         <v>0</v>
@@ -6392,7 +6059,7 @@
         <v>input~GASNGA~2015</v>
       </c>
       <c r="J27" s="144" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="K27" s="144" t="str">
         <f t="shared" si="1"/>
@@ -6414,10 +6081,10 @@
         <v>1</v>
       </c>
       <c r="P27" s="144" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="Q27" s="144" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="T27" s="144" t="s">
         <v>6</v>
@@ -6429,21 +6096,21 @@
         <v>7</v>
       </c>
       <c r="W27" s="144" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="X27" s="144" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="Y27" s="144" t="s">
         <v>11</v>
       </c>
       <c r="Z27" s="144" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:26">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B28" t="s">
         <v>15</v>
@@ -6487,7 +6154,7 @@
         <v>0.85470085470085477</v>
       </c>
       <c r="O28" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="P28">
         <v>25</v>
@@ -6517,12 +6184,12 @@
         <v>14</v>
       </c>
       <c r="Z28" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:26">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
         <v>15</v>
@@ -6566,7 +6233,7 @@
         <v>0.84745762711864414</v>
       </c>
       <c r="O29" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="P29">
         <v>25</v>
@@ -6596,7 +6263,7 @@
         <v>14</v>
       </c>
       <c r="Z29" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -6618,185 +6285,185 @@
   <sheetData>
     <row r="9" spans="2:56">
       <c r="B9" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="J9" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="O9" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="X9" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="AD9" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="AL9" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="AR9" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="AZ9" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="2:56">
       <c r="B10" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="C10" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="D10" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="E10" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="F10" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="G10" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="H10" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="J10" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="K10" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="L10" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="M10" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="O10" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="P10" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="Q10" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="R10" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="S10" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="T10" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="U10" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="V10" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="X10" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="Y10" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="Z10" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="AA10" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="AB10" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="AD10" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="AE10" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="AF10" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="AG10" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="AH10" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="AI10" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="AJ10" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="AL10" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="AM10" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="AN10" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="AO10" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="AP10" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="AR10" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="AS10" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="AT10" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="AU10" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="AV10" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="AW10" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="AX10" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="AZ10" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="BA10" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="BB10" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="BC10" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="BD10" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" spans="2:56">
       <c r="B11" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C11" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D11" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -6805,16 +6472,16 @@
         <v>20</v>
       </c>
       <c r="G11" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H11" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J11" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="K11" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="L11">
         <v>14.703515544593534</v>
@@ -6823,13 +6490,13 @@
         <v>0.18394567124097769</v>
       </c>
       <c r="O11" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="P11" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="Q11" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="R11" t="s">
         <v>10</v>
@@ -6838,22 +6505,22 @@
         <v>20</v>
       </c>
       <c r="T11" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="U11" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="V11" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="X11" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="Y11" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="Z11" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="AA11">
         <v>0.99781284363204548</v>
@@ -6862,13 +6529,13 @@
         <v>40.097866745833329</v>
       </c>
       <c r="AD11" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AE11" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="AF11" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="AG11" t="s">
         <v>10</v>
@@ -6877,19 +6544,19 @@
         <v>20</v>
       </c>
       <c r="AI11" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AJ11" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AL11" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="AM11" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="AN11" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="AO11">
         <v>0.99692224665834439</v>
@@ -6898,13 +6565,13 @@
         <v>56.425477930352955</v>
       </c>
       <c r="AR11" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS11" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="AT11" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="AU11" t="s">
         <v>10</v>
@@ -6913,19 +6580,19 @@
         <v>20</v>
       </c>
       <c r="AW11" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX11" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ11" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="BA11" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="BB11" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="BC11">
         <v>0.9878288138539939</v>
@@ -6936,13 +6603,13 @@
     </row>
     <row r="12" spans="2:56">
       <c r="B12" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C12" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="D12" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -6951,16 +6618,16 @@
         <v>20</v>
       </c>
       <c r="G12" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H12" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J12" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="K12" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="L12">
         <v>7.0247960503319238</v>
@@ -6969,13 +6636,13 @@
         <v>0.1895344528514209</v>
       </c>
       <c r="O12" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="P12" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="Q12" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="R12" t="s">
         <v>10</v>
@@ -6984,22 +6651,22 @@
         <v>20</v>
       </c>
       <c r="T12" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="U12" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="V12" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="X12" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="Y12" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="Z12" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="AA12">
         <v>0.99164479201276912</v>
@@ -7008,13 +6675,13 @@
         <v>153.17881309923388</v>
       </c>
       <c r="AD12" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AE12" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="AF12" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="AG12" t="s">
         <v>10</v>
@@ -7023,19 +6690,19 @@
         <v>20</v>
       </c>
       <c r="AI12" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AJ12" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AL12" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="AM12" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="AN12" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="AO12">
         <v>0.99590345602074126</v>
@@ -7044,13 +6711,13 @@
         <v>75.103306286410302</v>
       </c>
       <c r="AR12" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS12" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="AT12" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="AU12" t="s">
         <v>10</v>
@@ -7059,19 +6726,19 @@
         <v>20</v>
       </c>
       <c r="AW12" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX12" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ12" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="BA12" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="BB12" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="BC12">
         <v>0.98395883577792953</v>
@@ -7082,13 +6749,13 @@
     </row>
     <row r="13" spans="2:56">
       <c r="B13" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C13" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="D13" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -7097,16 +6764,16 @@
         <v>20</v>
       </c>
       <c r="G13" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H13" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J13" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="K13" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="L13">
         <v>12.174517979652411</v>
@@ -7115,13 +6782,13 @@
         <v>0.18533082336913481</v>
       </c>
       <c r="O13" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="P13" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="Q13" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="R13" t="s">
         <v>10</v>
@@ -7130,22 +6797,22 @@
         <v>20</v>
       </c>
       <c r="T13" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="U13" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="V13" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="X13" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="Y13" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="Z13" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="AA13">
         <v>0.99568371668484024</v>
@@ -7154,13 +6821,13 @@
         <v>79.131860777928608</v>
       </c>
       <c r="AD13" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AE13" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="AF13" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="AG13" t="s">
         <v>10</v>
@@ -7169,19 +6836,19 @@
         <v>20</v>
       </c>
       <c r="AI13" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AJ13" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AL13" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="AM13" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="AN13" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="AO13">
         <v>0.9975157188831717</v>
@@ -7190,13 +6857,13 @@
         <v>45.545153808519316</v>
       </c>
       <c r="AR13" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS13" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="AT13" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="AU13" t="s">
         <v>10</v>
@@ -7205,19 +6872,19 @@
         <v>20</v>
       </c>
       <c r="AW13" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX13" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ13" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="BA13" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="BB13" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="BC13">
         <v>0.94957327345368925</v>
@@ -7228,13 +6895,13 @@
     </row>
     <row r="14" spans="2:56">
       <c r="B14" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C14" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="D14" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -7243,16 +6910,16 @@
         <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H14" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J14" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="K14" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="L14">
         <v>8.646134759765264</v>
@@ -7261,13 +6928,13 @@
         <v>0.18564315469610329</v>
       </c>
       <c r="O14" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="P14" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="Q14" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="R14" t="s">
         <v>10</v>
@@ -7276,22 +6943,22 @@
         <v>20</v>
       </c>
       <c r="T14" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="U14" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="V14" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="X14" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="Y14" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="Z14" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="AA14">
         <v>0.99673728461460676</v>
@@ -7300,13 +6967,13 @@
         <v>59.816448732209111</v>
       </c>
       <c r="AD14" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AE14" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="AF14" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="AG14" t="s">
         <v>10</v>
@@ -7315,19 +6982,19 @@
         <v>20</v>
       </c>
       <c r="AI14" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AJ14" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AL14" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="AM14" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="AN14" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="AO14">
         <v>0.99725701149052537</v>
@@ -7336,13 +7003,13 @@
         <v>50.288122673700855</v>
       </c>
       <c r="AR14" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS14" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="AT14" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="AU14" t="s">
         <v>10</v>
@@ -7351,19 +7018,19 @@
         <v>20</v>
       </c>
       <c r="AW14" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX14" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ14" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="BA14" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="BB14" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="BC14">
         <v>0.98560960960201449</v>
@@ -7374,14 +7041,14 @@
     </row>
     <row r="15" spans="2:56">
       <c r="B15" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" t="s">
+        <v>164</v>
+      </c>
+      <c r="D15" t="s">
         <v>165</v>
       </c>
-      <c r="C15" t="s">
-        <v>176</v>
-      </c>
-      <c r="D15" t="s">
-        <v>177</v>
-      </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
@@ -7389,16 +7056,16 @@
         <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H15" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J15" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="K15" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="L15">
         <v>10.978710703279315</v>
@@ -7407,14 +7074,14 @@
         <v>0.1751830539964257</v>
       </c>
       <c r="O15" t="s">
+        <v>209</v>
+      </c>
+      <c r="P15" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q15" t="s">
         <v>221</v>
       </c>
-      <c r="P15" t="s">
-        <v>232</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>233</v>
-      </c>
       <c r="R15" t="s">
         <v>10</v>
       </c>
@@ -7422,22 +7089,22 @@
         <v>20</v>
       </c>
       <c r="T15" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="U15" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="V15" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="X15" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="Y15" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="Z15" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="AA15">
         <v>0.99709164861435029</v>
@@ -7446,13 +7113,13 @@
         <v>53.319775403577559</v>
       </c>
       <c r="AD15" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AE15" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="AF15" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="AG15" t="s">
         <v>10</v>
@@ -7461,19 +7128,19 @@
         <v>20</v>
       </c>
       <c r="AI15" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AJ15" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AL15" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="AM15" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="AN15" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="AO15">
         <v>0.99595483459575906</v>
@@ -7482,13 +7149,13 @@
         <v>74.161365744417125</v>
       </c>
       <c r="AR15" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS15" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="AT15" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="AU15" t="s">
         <v>10</v>
@@ -7497,19 +7164,19 @@
         <v>20</v>
       </c>
       <c r="AW15" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX15" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ15" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="BA15" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="BB15" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="BC15">
         <v>0.99053075643264799</v>
@@ -7520,13 +7187,13 @@
     </row>
     <row r="16" spans="2:56">
       <c r="B16" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C16" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="D16" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -7535,16 +7202,16 @@
         <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H16" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J16" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="K16" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="L16">
         <v>13.930117028134356</v>
@@ -7553,13 +7220,13 @@
         <v>0.18239756272718469</v>
       </c>
       <c r="O16" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="P16" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="Q16" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="R16" t="s">
         <v>10</v>
@@ -7568,22 +7235,22 @@
         <v>20</v>
       </c>
       <c r="T16" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="U16" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="V16" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="X16" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="Y16" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="Z16" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="AA16">
         <v>0.99552574319771747</v>
@@ -7592,13 +7259,13 @@
         <v>82.028041375179441</v>
       </c>
       <c r="AD16" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AE16" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="AF16" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="AG16" t="s">
         <v>10</v>
@@ -7607,19 +7274,19 @@
         <v>20</v>
       </c>
       <c r="AI16" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AJ16" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AL16" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="AM16" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="AN16" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="AO16">
         <v>0.99761292756299069</v>
@@ -7628,13 +7295,13 @@
         <v>43.762994678503716</v>
       </c>
       <c r="AR16" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS16" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="AT16" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="AU16" t="s">
         <v>10</v>
@@ -7643,19 +7310,19 @@
         <v>20</v>
       </c>
       <c r="AW16" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX16" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ16" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="BA16" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="BB16" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="BC16">
         <v>0.98974923036021278</v>
@@ -7666,13 +7333,13 @@
     </row>
     <row r="17" spans="2:56">
       <c r="B17" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C17" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="D17" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -7681,16 +7348,16 @@
         <v>20</v>
       </c>
       <c r="G17" t="s">
+        <v>156</v>
+      </c>
+      <c r="H17" t="s">
+        <v>157</v>
+      </c>
+      <c r="J17" t="s">
         <v>168</v>
       </c>
-      <c r="H17" t="s">
-        <v>169</v>
-      </c>
-      <c r="J17" t="s">
-        <v>180</v>
-      </c>
       <c r="K17" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="L17">
         <v>7.7139766429685555</v>
@@ -7699,13 +7366,13 @@
         <v>0.16714441187363149</v>
       </c>
       <c r="O17" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="P17" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="Q17" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="R17" t="s">
         <v>10</v>
@@ -7714,22 +7381,22 @@
         <v>20</v>
       </c>
       <c r="T17" t="s">
+        <v>212</v>
+      </c>
+      <c r="U17" t="s">
+        <v>213</v>
+      </c>
+      <c r="V17" t="s">
+        <v>157</v>
+      </c>
+      <c r="X17" t="s">
         <v>224</v>
       </c>
-      <c r="U17" t="s">
-        <v>225</v>
-      </c>
-      <c r="V17" t="s">
-        <v>169</v>
-      </c>
-      <c r="X17" t="s">
-        <v>236</v>
-      </c>
       <c r="Y17" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="Z17" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="AA17">
         <v>0.99856414548474748</v>
@@ -7738,13 +7405,13 @@
         <v>26.323999446296273</v>
       </c>
       <c r="AD17" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AE17" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="AF17" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="AG17" t="s">
         <v>10</v>
@@ -7753,19 +7420,19 @@
         <v>20</v>
       </c>
       <c r="AI17" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AJ17" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AL17" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="AM17" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="AN17" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="AO17">
         <v>0.99446613913875159</v>
@@ -7774,13 +7441,13 @@
         <v>101.45411578955439</v>
       </c>
       <c r="AR17" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS17" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="AT17" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="AU17" t="s">
         <v>10</v>
@@ -7789,19 +7456,19 @@
         <v>20</v>
       </c>
       <c r="AW17" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX17" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ17" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="BA17" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="BB17" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="BC17">
         <v>0.99439449087123744</v>
@@ -7812,13 +7479,13 @@
     </row>
     <row r="18" spans="2:56">
       <c r="B18" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C18" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="D18" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -7827,16 +7494,16 @@
         <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H18" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J18" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="K18" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="L18">
         <v>13.532966068581743</v>
@@ -7845,13 +7512,13 @@
         <v>0.15443081133819789</v>
       </c>
       <c r="O18" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="P18" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="Q18" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="R18" t="s">
         <v>10</v>
@@ -7860,22 +7527,22 @@
         <v>20</v>
       </c>
       <c r="T18" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="U18" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="V18" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="X18" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="Y18" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="Z18" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="AA18">
         <v>0.99837169372341228</v>
@@ -7884,13 +7551,13 @@
         <v>29.852281737441412</v>
       </c>
       <c r="AD18" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AE18" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="AF18" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="AG18" t="s">
         <v>10</v>
@@ -7899,19 +7566,19 @@
         <v>20</v>
       </c>
       <c r="AI18" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AJ18" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AL18" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="AM18" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="AN18" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="AO18">
         <v>0.99821201020674788</v>
@@ -7920,13 +7587,13 @@
         <v>32.77981287628851</v>
       </c>
       <c r="AR18" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS18" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="AT18" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="AU18" t="s">
         <v>10</v>
@@ -7935,19 +7602,19 @@
         <v>20</v>
       </c>
       <c r="AW18" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX18" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ18" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="BA18" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="BB18" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="BC18">
         <v>0.9960370911532308</v>
@@ -7958,13 +7625,13 @@
     </row>
     <row r="19" spans="2:56">
       <c r="B19" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C19" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="D19" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -7973,16 +7640,16 @@
         <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H19" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J19" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="K19" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="L19">
         <v>0.30791874242419603</v>
@@ -7991,13 +7658,13 @@
         <v>0.15242372922965119</v>
       </c>
       <c r="O19" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="P19" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="Q19" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="R19" t="s">
         <v>10</v>
@@ -8006,22 +7673,22 @@
         <v>20</v>
       </c>
       <c r="T19" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="U19" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="V19" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="X19" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="Y19" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="Z19" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="AA19">
         <v>0.99541580702824473</v>
@@ -8030,13 +7697,13 @@
         <v>84.0435378155141</v>
       </c>
       <c r="AD19" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AE19" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="AF19" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="AG19" t="s">
         <v>10</v>
@@ -8045,19 +7712,19 @@
         <v>20</v>
       </c>
       <c r="AI19" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AJ19" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AL19" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="AM19" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="AN19" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="AO19">
         <v>0.99562511313409086</v>
@@ -8066,13 +7733,13 @@
         <v>80.206259208334231</v>
       </c>
       <c r="AR19" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS19" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="AT19" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="AU19" t="s">
         <v>10</v>
@@ -8081,19 +7748,19 @@
         <v>20</v>
       </c>
       <c r="AW19" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX19" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ19" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="BA19" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="BB19" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="BC19">
         <v>0.98596601099553871</v>
@@ -8104,13 +7771,13 @@
     </row>
     <row r="20" spans="2:56">
       <c r="B20" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C20" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="D20" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -8119,16 +7786,16 @@
         <v>20</v>
       </c>
       <c r="G20" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H20" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J20" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="K20" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="L20">
         <v>3.0931829905152187E-2</v>
@@ -8137,13 +7804,13 @@
         <v>0.13596321535260519</v>
       </c>
       <c r="O20" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="P20" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="Q20" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="R20" t="s">
         <v>10</v>
@@ -8152,22 +7819,22 @@
         <v>20</v>
       </c>
       <c r="T20" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="U20" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="V20" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="X20" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="Y20" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="Z20" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="AA20">
         <v>0.9981722170039925</v>
@@ -8176,13 +7843,13 @@
         <v>33.509354926805031</v>
       </c>
       <c r="AD20" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AE20" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="AF20" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="AG20" t="s">
         <v>10</v>
@@ -8191,19 +7858,19 @@
         <v>20</v>
       </c>
       <c r="AI20" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AJ20" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AL20" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="AM20" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="AN20" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="AO20">
         <v>0.99857516825685033</v>
@@ -8212,13 +7879,13 @@
         <v>26.121915291078167</v>
       </c>
       <c r="AR20" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS20" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="AT20" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="AU20" t="s">
         <v>10</v>
@@ -8227,19 +7894,19 @@
         <v>20</v>
       </c>
       <c r="AW20" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX20" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ20" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="BA20" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="BB20" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="BC20">
         <v>0.96328479701100822</v>
@@ -8250,13 +7917,13 @@
     </row>
     <row r="21" spans="2:56">
       <c r="B21" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C21" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="D21" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -8265,16 +7932,16 @@
         <v>20</v>
       </c>
       <c r="G21" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H21" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J21" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="K21" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="L21">
         <v>7.2737697525181089</v>
@@ -8283,13 +7950,13 @@
         <v>0.1484590937756623</v>
       </c>
       <c r="O21" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="P21" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="Q21" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="R21" t="s">
         <v>10</v>
@@ -8298,22 +7965,22 @@
         <v>20</v>
       </c>
       <c r="T21" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="U21" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="V21" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="X21" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="Y21" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="Z21" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="AA21">
         <v>0.99757939258365447</v>
@@ -8322,13 +7989,13 @@
         <v>44.377802633000776</v>
       </c>
       <c r="AD21" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AE21" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="AF21" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="AG21" t="s">
         <v>10</v>
@@ -8337,19 +8004,19 @@
         <v>20</v>
       </c>
       <c r="AI21" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AJ21" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AL21" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="AM21" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="AN21" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="AO21">
         <v>0.99624198670989172</v>
@@ -8358,13 +8025,13 @@
         <v>68.896910318651507</v>
       </c>
       <c r="AR21" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS21" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="AT21" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="AU21" t="s">
         <v>10</v>
@@ -8373,19 +8040,19 @@
         <v>20</v>
       </c>
       <c r="AW21" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX21" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ21" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="BA21" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="BB21" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="BC21">
         <v>0.98248517632197996</v>
@@ -8396,13 +8063,13 @@
     </row>
     <row r="22" spans="2:56">
       <c r="B22" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C22" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D22" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -8411,16 +8078,16 @@
         <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H22" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J22" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="K22" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="L22">
         <v>7.307015755869652</v>
@@ -8429,13 +8096,13 @@
         <v>0.17768231485175401</v>
       </c>
       <c r="O22" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="P22" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="Q22" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="R22" t="s">
         <v>10</v>
@@ -8444,22 +8111,22 @@
         <v>20</v>
       </c>
       <c r="T22" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="U22" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="V22" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="X22" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="Y22" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="Z22" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="AA22">
         <v>0.9982917156958806</v>
@@ -8468,13 +8135,13 @@
         <v>31.318545575522229</v>
       </c>
       <c r="AD22" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AE22" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="AF22" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="AG22" t="s">
         <v>10</v>
@@ -8483,19 +8150,19 @@
         <v>20</v>
       </c>
       <c r="AI22" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AJ22" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AL22" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="AM22" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="AN22" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="AO22">
         <v>0.99239099026325794</v>
@@ -8504,13 +8171,13 @@
         <v>139.49851184027145</v>
       </c>
       <c r="AR22" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS22" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="AT22" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="AU22" t="s">
         <v>10</v>
@@ -8519,19 +8186,19 @@
         <v>20</v>
       </c>
       <c r="AW22" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX22" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ22" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="BA22" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="BB22" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="BC22">
         <v>0.992142345264865</v>
@@ -8542,13 +8209,13 @@
     </row>
     <row r="23" spans="2:56">
       <c r="B23" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C23" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="D23" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -8557,16 +8224,16 @@
         <v>20</v>
       </c>
       <c r="G23" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H23" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J23" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="K23" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="L23">
         <v>13.939949671576917</v>
@@ -8575,13 +8242,13 @@
         <v>0.1699372145053003</v>
       </c>
       <c r="O23" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="P23" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="Q23" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="R23" t="s">
         <v>10</v>
@@ -8590,22 +8257,22 @@
         <v>20</v>
       </c>
       <c r="T23" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="U23" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="V23" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="X23" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="Y23" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="Z23" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="AA23">
         <v>0.99649838493007836</v>
@@ -8614,13 +8281,13 @@
         <v>64.196276281897482</v>
       </c>
       <c r="AD23" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AE23" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="AF23" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="AG23" t="s">
         <v>10</v>
@@ -8629,19 +8296,19 @@
         <v>20</v>
       </c>
       <c r="AI23" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AJ23" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AL23" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="AM23" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="AN23" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="AO23">
         <v>0.99807547980555666</v>
@@ -8650,13 +8317,13 @@
         <v>35.282870231460656</v>
       </c>
       <c r="AR23" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS23" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="AT23" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="AU23" t="s">
         <v>10</v>
@@ -8665,19 +8332,19 @@
         <v>20</v>
       </c>
       <c r="AW23" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX23" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ23" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="BA23" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="BB23" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="BC23">
         <v>0.99241288386292881</v>
@@ -8688,13 +8355,13 @@
     </row>
     <row r="24" spans="2:56">
       <c r="B24" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C24" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="D24" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -8703,16 +8370,16 @@
         <v>20</v>
       </c>
       <c r="G24" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H24" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J24" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="K24" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="L24">
         <v>1.6370832793384471</v>
@@ -8721,13 +8388,13 @@
         <v>0.1729078211793279</v>
       </c>
       <c r="O24" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="P24" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="Q24" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="R24" t="s">
         <v>10</v>
@@ -8736,22 +8403,22 @@
         <v>20</v>
       </c>
       <c r="T24" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="U24" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="V24" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="X24" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="Y24" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="Z24" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="AA24">
         <v>0.9958319028842455</v>
@@ -8760,13 +8427,13 @@
         <v>76.415113788833068</v>
       </c>
       <c r="AD24" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AE24" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="AF24" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="AG24" t="s">
         <v>10</v>
@@ -8775,19 +8442,19 @@
         <v>20</v>
       </c>
       <c r="AI24" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AJ24" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AL24" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="AM24" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="AN24" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="AO24">
         <v>0.99665105279570931</v>
@@ -8796,13 +8463,13 @@
         <v>61.397365411996212</v>
       </c>
       <c r="AR24" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS24" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="AT24" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="AU24" t="s">
         <v>10</v>
@@ -8811,19 +8478,19 @@
         <v>20</v>
       </c>
       <c r="AW24" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX24" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ24" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="BA24" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="BB24" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="BC24">
         <v>0.99503867375582744</v>
@@ -8834,13 +8501,13 @@
     </row>
     <row r="25" spans="2:56">
       <c r="B25" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C25" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="D25" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -8849,16 +8516,16 @@
         <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H25" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J25" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="K25" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="L25">
         <v>0.73381363970591551</v>
@@ -8867,13 +8534,13 @@
         <v>0.16678541694650079</v>
       </c>
       <c r="O25" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="P25" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="Q25" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="R25" t="s">
         <v>10</v>
@@ -8882,22 +8549,22 @@
         <v>20</v>
       </c>
       <c r="T25" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="U25" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="V25" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="X25" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="Y25" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="Z25" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="AA25">
         <v>0.9986195737404916</v>
@@ -8906,13 +8573,13 @@
         <v>25.307814757654675</v>
       </c>
       <c r="AD25" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AE25" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="AF25" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="AG25" t="s">
         <v>10</v>
@@ -8921,19 +8588,19 @@
         <v>20</v>
       </c>
       <c r="AI25" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AJ25" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AL25" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="AM25" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="AN25" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="AO25">
         <v>0.99826030196534266</v>
@@ -8942,13 +8609,13 @@
         <v>31.894463968718917</v>
       </c>
       <c r="AR25" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS25" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="AT25" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="AU25" t="s">
         <v>10</v>
@@ -8957,19 +8624,19 @@
         <v>20</v>
       </c>
       <c r="AW25" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX25" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ25" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="BA25" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="BB25" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="BC25">
         <v>0.99162758874212198</v>
@@ -8980,13 +8647,13 @@
     </row>
     <row r="26" spans="2:56">
       <c r="B26" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C26" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="D26" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -8995,16 +8662,16 @@
         <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H26" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J26" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="K26" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="L26">
         <v>1.8144550028683772</v>
@@ -9013,13 +8680,13 @@
         <v>0.1577067378709853</v>
       </c>
       <c r="O26" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="P26" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="Q26" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="R26" t="s">
         <v>10</v>
@@ -9028,22 +8695,22 @@
         <v>20</v>
       </c>
       <c r="T26" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="U26" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="V26" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="X26" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="Y26" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="Z26" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="AA26">
         <v>0.99656426482871763</v>
@@ -9052,13 +8719,13 @@
         <v>62.988478140176163</v>
       </c>
       <c r="AR26" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS26" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="AT26" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="AU26" t="s">
         <v>10</v>
@@ -9067,19 +8734,19 @@
         <v>20</v>
       </c>
       <c r="AW26" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX26" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ26" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="BA26" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="BB26" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="BC26">
         <v>0.99508487560623826</v>
@@ -9090,13 +8757,13 @@
     </row>
     <row r="27" spans="2:56">
       <c r="AR27" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS27" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="AT27" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="AU27" t="s">
         <v>10</v>
@@ -9105,19 +8772,19 @@
         <v>20</v>
       </c>
       <c r="AW27" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX27" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ27" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="BA27" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="BB27" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="BC27">
         <v>0.97496359905143026</v>
@@ -9128,13 +8795,13 @@
     </row>
     <row r="28" spans="2:56">
       <c r="AR28" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS28" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="AT28" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="AU28" t="s">
         <v>10</v>
@@ -9143,19 +8810,19 @@
         <v>20</v>
       </c>
       <c r="AW28" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX28" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ28" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="BA28" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="BB28" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="BC28">
         <v>0.99514843803074871</v>
@@ -9166,13 +8833,13 @@
     </row>
     <row r="29" spans="2:56">
       <c r="AR29" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS29" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="AT29" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="AU29" t="s">
         <v>10</v>
@@ -9181,19 +8848,19 @@
         <v>20</v>
       </c>
       <c r="AW29" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX29" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ29" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="BA29" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="BB29" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="BC29">
         <v>0.98039565814133589</v>
@@ -9204,13 +8871,13 @@
     </row>
     <row r="30" spans="2:56">
       <c r="AR30" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS30" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="AT30" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="AU30" t="s">
         <v>10</v>
@@ -9219,19 +8886,19 @@
         <v>20</v>
       </c>
       <c r="AW30" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX30" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ30" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="BA30" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="BB30" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="BC30">
         <v>0.99199988291996133</v>
@@ -9242,13 +8909,13 @@
     </row>
     <row r="31" spans="2:56">
       <c r="AR31" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS31" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="AT31" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="AU31" t="s">
         <v>10</v>
@@ -9257,19 +8924,19 @@
         <v>20</v>
       </c>
       <c r="AW31" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX31" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ31" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="BA31" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="BB31" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="BC31">
         <v>0.96374055461874508</v>
@@ -9280,13 +8947,13 @@
     </row>
     <row r="32" spans="2:56">
       <c r="AR32" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS32" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="AT32" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="AU32" t="s">
         <v>10</v>
@@ -9295,19 +8962,19 @@
         <v>20</v>
       </c>
       <c r="AW32" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX32" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ32" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="BA32" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="BB32" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="BC32">
         <v>0.99048115912556611</v>
@@ -9318,13 +8985,13 @@
     </row>
     <row r="33" spans="44:56">
       <c r="AR33" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS33" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="AT33" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="AU33" t="s">
         <v>10</v>
@@ -9333,19 +9000,19 @@
         <v>20</v>
       </c>
       <c r="AW33" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX33" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ33" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="BA33" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="BB33" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="BC33">
         <v>0.99441710380733805</v>
@@ -9356,13 +9023,13 @@
     </row>
     <row r="34" spans="44:56">
       <c r="AR34" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS34" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="AT34" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="AU34" t="s">
         <v>10</v>
@@ -9371,19 +9038,19 @@
         <v>20</v>
       </c>
       <c r="AW34" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX34" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ34" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="BA34" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="BB34" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="BC34">
         <v>0.9871879084242271</v>
@@ -9394,13 +9061,13 @@
     </row>
     <row r="35" spans="44:56">
       <c r="AR35" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS35" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="AT35" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="AU35" t="s">
         <v>10</v>
@@ -9409,19 +9076,19 @@
         <v>20</v>
       </c>
       <c r="AW35" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX35" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ35" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="BA35" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="BB35" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="BC35">
         <v>0.99511226039729839</v>
@@ -9432,13 +9099,13 @@
     </row>
     <row r="36" spans="44:56">
       <c r="AR36" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS36" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="AT36" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="AU36" t="s">
         <v>10</v>
@@ -9447,19 +9114,19 @@
         <v>20</v>
       </c>
       <c r="AW36" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX36" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ36" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="BA36" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="BB36" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="BC36">
         <v>0.99402092584318991</v>
@@ -9470,13 +9137,13 @@
     </row>
     <row r="37" spans="44:56">
       <c r="AR37" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS37" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="AT37" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="AU37" t="s">
         <v>10</v>
@@ -9485,19 +9152,19 @@
         <v>20</v>
       </c>
       <c r="AW37" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX37" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ37" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="BA37" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="BB37" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="BC37">
         <v>0.99402264995370893</v>
@@ -9508,13 +9175,13 @@
     </row>
     <row r="38" spans="44:56">
       <c r="AR38" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS38" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="AT38" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="AU38" t="s">
         <v>10</v>
@@ -9523,19 +9190,19 @@
         <v>20</v>
       </c>
       <c r="AW38" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX38" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ38" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="BA38" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="BB38" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="BC38">
         <v>0.99490522012066784</v>
@@ -9546,13 +9213,13 @@
     </row>
     <row r="39" spans="44:56">
       <c r="AR39" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS39" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="AT39" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="AU39" t="s">
         <v>10</v>
@@ -9561,19 +9228,19 @@
         <v>20</v>
       </c>
       <c r="AW39" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX39" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ39" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="BA39" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="BB39" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="BC39">
         <v>0.99728827252195684</v>
@@ -9584,13 +9251,13 @@
     </row>
     <row r="40" spans="44:56">
       <c r="AR40" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS40" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="AT40" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="AU40" t="s">
         <v>10</v>
@@ -9599,19 +9266,19 @@
         <v>20</v>
       </c>
       <c r="AW40" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX40" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ40" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="BA40" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="BB40" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="BC40">
         <v>0.95113733831453195</v>
@@ -9622,13 +9289,13 @@
     </row>
     <row r="41" spans="44:56">
       <c r="AR41" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS41" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="AT41" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="AU41" t="s">
         <v>10</v>
@@ -9637,19 +9304,19 @@
         <v>20</v>
       </c>
       <c r="AW41" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX41" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ41" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="BA41" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="BB41" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="BC41">
         <v>0.9955021345306051</v>
@@ -9660,13 +9327,13 @@
     </row>
     <row r="42" spans="44:56">
       <c r="AR42" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS42" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="AT42" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="AU42" t="s">
         <v>10</v>
@@ -9675,19 +9342,19 @@
         <v>20</v>
       </c>
       <c r="AW42" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX42" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ42" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="BA42" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="BB42" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="BC42">
         <v>0.99579892549254256</v>
@@ -9698,13 +9365,13 @@
     </row>
     <row r="43" spans="44:56">
       <c r="AR43" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AS43" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="AT43" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="AU43" t="s">
         <v>10</v>
@@ -9713,19 +9380,19 @@
         <v>20</v>
       </c>
       <c r="AW43" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AX43" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AZ43" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="BA43" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="BB43" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="BC43">
         <v>0.9877150845460122</v>
@@ -9746,95 +9413,95 @@
   <sheetData>
     <row r="9" spans="2:26">
       <c r="B9" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="J9" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="O9" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="W9" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="2:26">
       <c r="B10" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="C10" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="D10" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="E10" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="F10" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="G10" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="H10" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="J10" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="K10" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="L10" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="M10" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="O10" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="P10" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="Q10" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="R10" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="S10" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="T10" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="U10" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="W10" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="X10" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="Y10" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="Z10" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="2:26">
       <c r="B11" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C11" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="D11" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -9843,16 +9510,16 @@
         <v>20</v>
       </c>
       <c r="G11" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H11" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J11" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="K11" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="L11">
         <v>8.3728062197205944</v>
@@ -9861,13 +9528,13 @@
         <v>0.4071105959727585</v>
       </c>
       <c r="O11" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P11" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="Q11" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="R11" t="s">
         <v>10</v>
@@ -9876,16 +9543,16 @@
         <v>20</v>
       </c>
       <c r="T11" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U11" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W11" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="X11" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="Y11">
         <v>2.177</v>
@@ -9896,13 +9563,13 @@
     </row>
     <row r="12" spans="2:26">
       <c r="B12" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C12" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="D12" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -9911,16 +9578,16 @@
         <v>20</v>
       </c>
       <c r="G12" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H12" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J12" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="K12" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="L12">
         <v>42.531235680568031</v>
@@ -9929,13 +9596,13 @@
         <v>0.36457772816942419</v>
       </c>
       <c r="O12" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P12" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="Q12" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="R12" t="s">
         <v>10</v>
@@ -9944,16 +9611,16 @@
         <v>20</v>
       </c>
       <c r="T12" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U12" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W12" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="X12" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="Y12">
         <v>47.905999999999999</v>
@@ -9964,13 +9631,13 @@
     </row>
     <row r="13" spans="2:26">
       <c r="B13" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C13" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="D13" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -9979,16 +9646,16 @@
         <v>20</v>
       </c>
       <c r="G13" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H13" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J13" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="K13" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="L13">
         <v>30.271312154499352</v>
@@ -9997,13 +9664,13 @@
         <v>0.34977720239710119</v>
       </c>
       <c r="O13" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P13" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="Q13" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="R13" t="s">
         <v>10</v>
@@ -10012,16 +9679,16 @@
         <v>20</v>
       </c>
       <c r="T13" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U13" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W13" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="X13" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="Y13">
         <v>91.13</v>
@@ -10032,13 +9699,13 @@
     </row>
     <row r="14" spans="2:26">
       <c r="B14" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C14" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="D14" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -10047,16 +9714,16 @@
         <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H14" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J14" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="K14" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="L14">
         <v>22.688073076145226</v>
@@ -10065,13 +9732,13 @@
         <v>0.2378222396486388</v>
       </c>
       <c r="O14" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P14" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="Q14" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="R14" t="s">
         <v>10</v>
@@ -10080,16 +9747,16 @@
         <v>20</v>
       </c>
       <c r="T14" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U14" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W14" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="X14" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="Y14">
         <v>30.484999999999999</v>
@@ -10100,13 +9767,13 @@
     </row>
     <row r="15" spans="2:26">
       <c r="B15" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C15" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="D15" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -10115,16 +9782,16 @@
         <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H15" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J15" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="K15" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="L15">
         <v>29.120153762247021</v>
@@ -10133,13 +9800,13 @@
         <v>0.2926790130249729</v>
       </c>
       <c r="O15" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P15" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="Q15" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="R15" t="s">
         <v>10</v>
@@ -10148,16 +9815,16 @@
         <v>20</v>
       </c>
       <c r="T15" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U15" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W15" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="X15" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="Y15">
         <v>6.726</v>
@@ -10168,13 +9835,13 @@
     </row>
     <row r="16" spans="2:26">
       <c r="B16" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C16" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="D16" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -10183,16 +9850,16 @@
         <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H16" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J16" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="K16" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="L16">
         <v>10.867385180190169</v>
@@ -10201,13 +9868,13 @@
         <v>0.1103684814428935</v>
       </c>
       <c r="O16" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P16" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="Q16" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="R16" t="s">
         <v>10</v>
@@ -10216,16 +9883,16 @@
         <v>20</v>
       </c>
       <c r="T16" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U16" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W16" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="X16" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="Y16">
         <v>33.183</v>
@@ -10236,13 +9903,13 @@
     </row>
     <row r="17" spans="2:26">
       <c r="B17" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C17" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="D17" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -10251,16 +9918,16 @@
         <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H17" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J17" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="K17" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="L17">
         <v>32.115075062865692</v>
@@ -10269,13 +9936,13 @@
         <v>0.2243348627558987</v>
       </c>
       <c r="O17" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P17" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="Q17" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="R17" t="s">
         <v>10</v>
@@ -10284,16 +9951,16 @@
         <v>20</v>
       </c>
       <c r="T17" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U17" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W17" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="X17" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="Y17">
         <v>40.698999999999998</v>
@@ -10304,13 +9971,13 @@
     </row>
     <row r="18" spans="2:26">
       <c r="B18" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C18" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="D18" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -10319,16 +9986,16 @@
         <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H18" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J18" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="K18" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="L18">
         <v>9.0868240253443027</v>
@@ -10337,13 +10004,13 @@
         <v>0.17692716652199311</v>
       </c>
       <c r="O18" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P18" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="Q18" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="R18" t="s">
         <v>10</v>
@@ -10352,16 +10019,16 @@
         <v>20</v>
       </c>
       <c r="T18" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U18" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W18" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="X18" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="Y18">
         <v>43.79</v>
@@ -10372,13 +10039,13 @@
     </row>
     <row r="19" spans="2:26">
       <c r="B19" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C19" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="D19" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -10387,16 +10054,16 @@
         <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H19" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J19" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="K19" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="L19">
         <v>18.016423245563796</v>
@@ -10405,13 +10072,13 @@
         <v>0.37709145338738631</v>
       </c>
       <c r="O19" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P19" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="Q19" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="R19" t="s">
         <v>10</v>
@@ -10420,16 +10087,16 @@
         <v>20</v>
       </c>
       <c r="T19" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U19" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W19" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="X19" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="Y19">
         <v>3.617</v>
@@ -10440,13 +10107,13 @@
     </row>
     <row r="20" spans="2:26">
       <c r="B20" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C20" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="D20" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -10455,16 +10122,16 @@
         <v>20</v>
       </c>
       <c r="G20" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H20" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J20" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="K20" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="L20">
         <v>0.75250112047637663</v>
@@ -10473,13 +10140,13 @@
         <v>0.20583489876164651</v>
       </c>
       <c r="O20" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P20" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="Q20" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="R20" t="s">
         <v>10</v>
@@ -10488,16 +10155,16 @@
         <v>20</v>
       </c>
       <c r="T20" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U20" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W20" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="X20" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="Y20">
         <v>45.468000000000004</v>
@@ -10508,13 +10175,13 @@
     </row>
     <row r="21" spans="2:26">
       <c r="B21" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C21" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="D21" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -10523,16 +10190,16 @@
         <v>20</v>
       </c>
       <c r="G21" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H21" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J21" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="K21" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="L21">
         <v>18.381813037942475</v>
@@ -10541,13 +10208,13 @@
         <v>0.21707807750595889</v>
       </c>
       <c r="O21" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P21" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="Q21" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="R21" t="s">
         <v>10</v>
@@ -10556,16 +10223,16 @@
         <v>20</v>
       </c>
       <c r="T21" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U21" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W21" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="X21" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="Y21">
         <v>33.305</v>
@@ -10576,13 +10243,13 @@
     </row>
     <row r="22" spans="2:26">
       <c r="B22" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C22" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="D22" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -10591,16 +10258,16 @@
         <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H22" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J22" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="K22" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="L22">
         <v>4.5221914845937041</v>
@@ -10609,13 +10276,13 @@
         <v>0.11806257993100711</v>
       </c>
       <c r="O22" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P22" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="Q22" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="R22" t="s">
         <v>10</v>
@@ -10624,16 +10291,16 @@
         <v>20</v>
       </c>
       <c r="T22" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U22" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W22" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="X22" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="Y22">
         <v>32.006</v>
@@ -10644,13 +10311,13 @@
     </row>
     <row r="23" spans="2:26">
       <c r="B23" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C23" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="D23" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -10659,16 +10326,16 @@
         <v>20</v>
       </c>
       <c r="G23" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H23" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J23" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="K23" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="L23">
         <v>8.2953562793919264</v>
@@ -10677,13 +10344,13 @@
         <v>0.1425131297827614</v>
       </c>
       <c r="O23" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P23" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="Q23" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="R23" t="s">
         <v>10</v>
@@ -10692,16 +10359,16 @@
         <v>20</v>
       </c>
       <c r="T23" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U23" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W23" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="X23" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="Y23">
         <v>92.117999999999995</v>
@@ -10712,13 +10379,13 @@
     </row>
     <row r="24" spans="2:26">
       <c r="B24" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C24" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="D24" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -10727,16 +10394,16 @@
         <v>20</v>
       </c>
       <c r="G24" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H24" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J24" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="K24" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="L24">
         <v>1.2792726734837132</v>
@@ -10745,13 +10412,13 @@
         <v>0.120834301617764</v>
       </c>
       <c r="O24" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P24" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="Q24" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="R24" t="s">
         <v>10</v>
@@ -10760,16 +10427,16 @@
         <v>20</v>
       </c>
       <c r="T24" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U24" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W24" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="X24" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="Y24">
         <v>55.912999999999997</v>
@@ -10780,13 +10447,13 @@
     </row>
     <row r="25" spans="2:26">
       <c r="B25" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C25" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="D25" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -10795,16 +10462,16 @@
         <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H25" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="J25" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="K25" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="L25">
         <v>1.6182682752282065</v>
@@ -10813,13 +10480,13 @@
         <v>0.1260421379882968</v>
       </c>
       <c r="O25" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P25" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="Q25" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="R25" t="s">
         <v>10</v>
@@ -10828,16 +10495,16 @@
         <v>20</v>
       </c>
       <c r="T25" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U25" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W25" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="X25" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="Y25">
         <v>164.86799999999999</v>
@@ -10848,13 +10515,13 @@
     </row>
     <row r="26" spans="2:26">
       <c r="O26" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P26" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="Q26" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="R26" t="s">
         <v>10</v>
@@ -10863,16 +10530,16 @@
         <v>20</v>
       </c>
       <c r="T26" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U26" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W26" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="X26" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="Y26">
         <v>177.54</v>
@@ -10883,13 +10550,13 @@
     </row>
     <row r="27" spans="2:26">
       <c r="O27" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P27" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="Q27" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="R27" t="s">
         <v>10</v>
@@ -10898,16 +10565,16 @@
         <v>20</v>
       </c>
       <c r="T27" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U27" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W27" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="X27" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="Y27">
         <v>234.209</v>
@@ -10918,13 +10585,13 @@
     </row>
     <row r="28" spans="2:26">
       <c r="O28" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P28" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="Q28" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="R28" t="s">
         <v>10</v>
@@ -10933,16 +10600,16 @@
         <v>20</v>
       </c>
       <c r="T28" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U28" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W28" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="X28" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="Y28">
         <v>244.34299999999999</v>
@@ -10953,13 +10620,13 @@
     </row>
     <row r="29" spans="2:26">
       <c r="O29" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P29" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="Q29" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="R29" t="s">
         <v>10</v>
@@ -10968,16 +10635,16 @@
         <v>20</v>
       </c>
       <c r="T29" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U29" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W29" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="X29" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="Y29">
         <v>96.406999999999996</v>
@@ -10988,13 +10655,13 @@
     </row>
     <row r="30" spans="2:26">
       <c r="O30" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P30" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="Q30" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="R30" t="s">
         <v>10</v>
@@ -11003,16 +10670,16 @@
         <v>20</v>
       </c>
       <c r="T30" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U30" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W30" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="X30" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="Y30">
         <v>60.06</v>
@@ -11023,13 +10690,13 @@
     </row>
     <row r="31" spans="2:26">
       <c r="O31" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P31" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="Q31" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="R31" t="s">
         <v>10</v>
@@ -11038,16 +10705,16 @@
         <v>20</v>
       </c>
       <c r="T31" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U31" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W31" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="X31" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="Y31">
         <v>142.483</v>
@@ -11058,13 +10725,13 @@
     </row>
     <row r="32" spans="2:26">
       <c r="O32" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P32" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="Q32" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="R32" t="s">
         <v>10</v>
@@ -11073,16 +10740,16 @@
         <v>20</v>
       </c>
       <c r="T32" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U32" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W32" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="X32" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="Y32">
         <v>72.956000000000003</v>
@@ -11093,13 +10760,13 @@
     </row>
     <row r="33" spans="15:26">
       <c r="O33" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P33" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="Q33" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="R33" t="s">
         <v>10</v>
@@ -11108,16 +10775,16 @@
         <v>20</v>
       </c>
       <c r="T33" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U33" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W33" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="X33" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="Y33">
         <v>19.841000000000001</v>
@@ -11128,13 +10795,13 @@
     </row>
     <row r="34" spans="15:26">
       <c r="O34" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P34" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="Q34" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="R34" t="s">
         <v>10</v>
@@ -11143,16 +10810,16 @@
         <v>20</v>
       </c>
       <c r="T34" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U34" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W34" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="X34" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="Y34">
         <v>138.42500000000001</v>
@@ -11163,13 +10830,13 @@
     </row>
     <row r="35" spans="15:26">
       <c r="O35" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P35" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="Q35" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="R35" t="s">
         <v>10</v>
@@ -11178,16 +10845,16 @@
         <v>20</v>
       </c>
       <c r="T35" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U35" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W35" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="X35" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="Y35">
         <v>69.513999999999996</v>
@@ -11198,13 +10865,13 @@
     </row>
     <row r="36" spans="15:26">
       <c r="O36" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P36" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="Q36" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="R36" t="s">
         <v>10</v>
@@ -11213,16 +10880,16 @@
         <v>20</v>
       </c>
       <c r="T36" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U36" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W36" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="X36" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="Y36">
         <v>60.743000000000002</v>
@@ -11233,13 +10900,13 @@
     </row>
     <row r="37" spans="15:26">
       <c r="O37" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P37" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="Q37" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="R37" t="s">
         <v>10</v>
@@ -11248,16 +10915,16 @@
         <v>20</v>
       </c>
       <c r="T37" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U37" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W37" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="X37" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="Y37">
         <v>6.194</v>
@@ -11268,13 +10935,13 @@
     </row>
     <row r="38" spans="15:26">
       <c r="O38" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P38" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="Q38" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="R38" t="s">
         <v>10</v>
@@ -11283,16 +10950,16 @@
         <v>20</v>
       </c>
       <c r="T38" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U38" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W38" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="X38" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="Y38">
         <v>44.996000000000002</v>
@@ -11303,13 +10970,13 @@
     </row>
     <row r="39" spans="15:26">
       <c r="O39" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P39" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="Q39" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="R39" t="s">
         <v>10</v>
@@ -11318,16 +10985,16 @@
         <v>20</v>
       </c>
       <c r="T39" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U39" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W39" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="X39" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="Y39">
         <v>45.517000000000003</v>
@@ -11338,13 +11005,13 @@
     </row>
     <row r="40" spans="15:26">
       <c r="O40" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P40" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="Q40" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="R40" t="s">
         <v>10</v>
@@ -11353,16 +11020,16 @@
         <v>20</v>
       </c>
       <c r="T40" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U40" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W40" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="X40" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="Y40">
         <v>76.210999999999999</v>
@@ -11373,13 +11040,13 @@
     </row>
     <row r="41" spans="15:26">
       <c r="O41" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P41" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="Q41" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="R41" t="s">
         <v>10</v>
@@ -11388,16 +11055,16 @@
         <v>20</v>
       </c>
       <c r="T41" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U41" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W41" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="X41" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="Y41">
         <v>20.327999999999999</v>
@@ -11408,13 +11075,13 @@
     </row>
     <row r="42" spans="15:26">
       <c r="O42" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P42" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="Q42" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="R42" t="s">
         <v>10</v>
@@ -11423,16 +11090,16 @@
         <v>20</v>
       </c>
       <c r="T42" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U42" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W42" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="X42" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="Y42">
         <v>65.320999999999998</v>
@@ -11443,13 +11110,13 @@
     </row>
     <row r="43" spans="15:26">
       <c r="O43" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P43" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="Q43" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="R43" t="s">
         <v>10</v>
@@ -11458,16 +11125,16 @@
         <v>20</v>
       </c>
       <c r="T43" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="U43" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="W43" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="X43" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="Y43">
         <v>32.902000000000001</v>
@@ -11488,21 +11155,21 @@
   <sheetData>
     <row r="9" spans="2:16">
       <c r="B9" t="s">
-        <v>588</v>
+        <v>570</v>
       </c>
       <c r="J9" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="2:16">
       <c r="B10" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="C10" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D10" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="E10">
         <v>2023</v>
@@ -11514,36 +11181,36 @@
         <v>2050</v>
       </c>
       <c r="H10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J10" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="K10" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="L10" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="M10" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="N10" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="O10" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="P10" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="2:16">
       <c r="B11" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
         <v>19</v>
@@ -11558,13 +11225,13 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="H11" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="J11" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="K11" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="M11" t="s">
         <v>10</v>
@@ -11573,18 +11240,18 @@
         <v>20</v>
       </c>
       <c r="O11" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="P11" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
         <v>19</v>
@@ -11599,13 +11266,13 @@
         <v>0.5</v>
       </c>
       <c r="H12" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="J12" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="K12" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="M12" t="s">
         <v>10</v>
@@ -11614,18 +11281,18 @@
         <v>20</v>
       </c>
       <c r="O12" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="P12" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
         <v>19</v>
@@ -11640,13 +11307,13 @@
         <v>5150</v>
       </c>
       <c r="H13" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="J13" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="K13" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="M13" t="s">
         <v>10</v>
@@ -11655,18 +11322,18 @@
         <v>20</v>
       </c>
       <c r="O13" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="P13" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="B14" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
         <v>19</v>
@@ -11681,13 +11348,13 @@
         <v>180</v>
       </c>
       <c r="H14" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="J14" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="K14" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="M14" t="s">
         <v>10</v>
@@ -11696,18 +11363,18 @@
         <v>20</v>
       </c>
       <c r="O14" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="P14" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="B15" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
         <v>19</v>
@@ -11722,13 +11389,13 @@
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="J15" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="K15" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="M15" t="s">
         <v>10</v>
@@ -11737,18 +11404,18 @@
         <v>20</v>
       </c>
       <c r="O15" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="P15" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
     </row>
     <row r="16" spans="2:16">
       <c r="B16" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
         <v>19</v>
@@ -11763,13 +11430,13 @@
         <v>0.35000000000000003</v>
       </c>
       <c r="H16" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="J16" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="K16" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="M16" t="s">
         <v>10</v>
@@ -11778,18 +11445,18 @@
         <v>20</v>
       </c>
       <c r="O16" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="P16" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
     </row>
     <row r="17" spans="2:16">
       <c r="B17" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s">
         <v>19</v>
@@ -11804,33 +11471,33 @@
         <v>0.5</v>
       </c>
       <c r="H17" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="J17" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="K17" t="s">
+        <v>555</v>
+      </c>
+      <c r="M17" t="s">
+        <v>10</v>
+      </c>
+      <c r="N17" t="s">
+        <v>20</v>
+      </c>
+      <c r="O17" t="s">
+        <v>213</v>
+      </c>
+      <c r="P17" t="s">
         <v>567</v>
-      </c>
-      <c r="M17" t="s">
-        <v>10</v>
-      </c>
-      <c r="N17" t="s">
-        <v>20</v>
-      </c>
-      <c r="O17" t="s">
-        <v>225</v>
-      </c>
-      <c r="P17" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="18" spans="2:16">
       <c r="B18" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="s">
         <v>19</v>
@@ -11845,13 +11512,13 @@
         <v>2400</v>
       </c>
       <c r="H18" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="J18" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="K18" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="M18" t="s">
         <v>10</v>
@@ -11860,18 +11527,18 @@
         <v>20</v>
       </c>
       <c r="O18" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="P18" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19" t="s">
         <v>19</v>
@@ -11886,13 +11553,13 @@
         <v>85</v>
       </c>
       <c r="H19" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="J19" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="K19" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="M19" t="s">
         <v>10</v>
@@ -11901,18 +11568,18 @@
         <v>20</v>
       </c>
       <c r="O19" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="P19" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D20" t="s">
         <v>19</v>
@@ -11927,13 +11594,13 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="J20" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="K20" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="M20" t="s">
         <v>10</v>
@@ -11942,18 +11609,18 @@
         <v>20</v>
       </c>
       <c r="O20" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="P20" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s">
         <v>19</v>
@@ -11968,13 +11635,13 @@
         <v>0.61</v>
       </c>
       <c r="H21" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="J21" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="K21" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="M21" t="s">
         <v>10</v>
@@ -11983,18 +11650,18 @@
         <v>20</v>
       </c>
       <c r="O21" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="P21" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
     </row>
     <row r="22" spans="2:16">
       <c r="B22" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D22" t="s">
         <v>19</v>
@@ -12009,13 +11676,13 @@
         <v>1000</v>
       </c>
       <c r="H22" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="J22" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="K22" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="M22" t="s">
         <v>10</v>
@@ -12024,18 +11691,18 @@
         <v>20</v>
       </c>
       <c r="O22" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="P22" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D23" t="s">
         <v>19</v>
@@ -12050,13 +11717,13 @@
         <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="J23" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="K23" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="M23" t="s">
         <v>10</v>
@@ -12065,18 +11732,18 @@
         <v>20</v>
       </c>
       <c r="O23" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="P23" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
     </row>
     <row r="24" spans="2:16">
       <c r="B24" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
         <v>19</v>
@@ -12091,13 +11758,13 @@
         <v>0.54</v>
       </c>
       <c r="H24" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="J24" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="K24" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="M24" t="s">
         <v>10</v>
@@ -12106,18 +11773,18 @@
         <v>20</v>
       </c>
       <c r="O24" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="P24" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
     </row>
     <row r="25" spans="2:16">
       <c r="B25" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D25" t="s">
         <v>19</v>
@@ -12132,13 +11799,13 @@
         <v>2350</v>
       </c>
       <c r="H25" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="J25" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="K25" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="M25" t="s">
         <v>10</v>
@@ -12147,18 +11814,18 @@
         <v>20</v>
       </c>
       <c r="O25" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="P25" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
     </row>
     <row r="26" spans="2:16">
       <c r="B26" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D26" t="s">
         <v>19</v>
@@ -12173,15 +11840,15 @@
         <v>60</v>
       </c>
       <c r="H26" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D27" t="s">
         <v>19</v>
@@ -12196,13 +11863,13 @@
         <v>0.4</v>
       </c>
       <c r="H27" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="J27" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="K27" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="M27" t="s">
         <v>10</v>
@@ -12211,18 +11878,18 @@
         <v>20</v>
       </c>
       <c r="O27" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="P27" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D28" t="s">
         <v>19</v>
@@ -12237,13 +11904,13 @@
         <v>4300</v>
       </c>
       <c r="H28" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="J28" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="K28" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="M28" t="s">
         <v>10</v>
@@ -12252,18 +11919,18 @@
         <v>20</v>
       </c>
       <c r="O28" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="P28" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D29" t="s">
         <v>19</v>
@@ -12278,15 +11945,15 @@
         <v>130</v>
       </c>
       <c r="H29" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="C30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D30" t="s">
         <v>19</v>
@@ -12301,15 +11968,15 @@
         <v>0.42</v>
       </c>
       <c r="H30" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="2:16">
       <c r="B31" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="C31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D31" t="s">
         <v>19</v>
@@ -12324,15 +11991,15 @@
         <v>500</v>
       </c>
       <c r="H31" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
     </row>
     <row r="32" spans="2:16">
       <c r="B32" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="C32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s">
         <v>19</v>
@@ -12347,15 +12014,15 @@
         <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D33" t="s">
         <v>19</v>
@@ -12370,15 +12037,15 @@
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="2:8">
       <c r="B34" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D34" t="s">
         <v>19</v>
@@ -12393,15 +12060,15 @@
         <v>0.4</v>
       </c>
       <c r="H34" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="B35" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D35" t="s">
         <v>19</v>
@@ -12416,15 +12083,15 @@
         <v>2700</v>
       </c>
       <c r="H35" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="C36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D36" t="s">
         <v>19</v>
@@ -12439,15 +12106,15 @@
         <v>65</v>
       </c>
       <c r="H36" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="C37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D37" t="s">
         <v>19</v>
@@ -12462,15 +12129,15 @@
         <v>4</v>
       </c>
       <c r="H37" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="C38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D38" t="s">
         <v>19</v>
@@ -12485,15 +12152,15 @@
         <v>0.5</v>
       </c>
       <c r="H38" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="C39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D39" t="s">
         <v>19</v>
@@ -12508,15 +12175,15 @@
         <v>2400</v>
       </c>
       <c r="H39" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="C40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D40" t="s">
         <v>19</v>
@@ -12531,15 +12198,15 @@
         <v>85</v>
       </c>
       <c r="H40" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="C41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D41" t="s">
         <v>19</v>
@@ -12554,15 +12221,15 @@
         <v>0.43</v>
       </c>
       <c r="H41" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="2:8">
       <c r="B42" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="C42" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D42" t="s">
         <v>19</v>
@@ -12577,15 +12244,15 @@
         <v>5100</v>
       </c>
       <c r="H42" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="C43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D43" t="s">
         <v>19</v>
@@ -12600,15 +12267,15 @@
         <v>180</v>
       </c>
       <c r="H43" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="C44" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D44" t="s">
         <v>19</v>
@@ -12623,15 +12290,15 @@
         <v>0.33</v>
       </c>
       <c r="H44" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45" spans="2:8">
       <c r="B45" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="C45" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D45" t="s">
         <v>19</v>
@@ -12646,15 +12313,15 @@
         <v>4500</v>
       </c>
       <c r="H45" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="C46" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D46" t="s">
         <v>19</v>
@@ -12669,15 +12336,15 @@
         <v>175</v>
       </c>
       <c r="H46" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="B47" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="C47" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D47" t="s">
         <v>19</v>
@@ -12692,15 +12359,15 @@
         <v>0.4</v>
       </c>
       <c r="H47" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="48" spans="2:8">
       <c r="B48" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="C48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D48" t="s">
         <v>19</v>
@@ -12715,15 +12382,15 @@
         <v>5150</v>
       </c>
       <c r="H48" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="C49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D49" t="s">
         <v>19</v>
@@ -12738,15 +12405,15 @@
         <v>155</v>
       </c>
       <c r="H49" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
     </row>
     <row r="50" spans="2:8">
       <c r="B50" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="C50" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D50" t="s">
         <v>19</v>
@@ -12761,15 +12428,15 @@
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="51" spans="2:8">
       <c r="B51" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="C51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D51" t="s">
         <v>19</v>
@@ -12784,15 +12451,15 @@
         <v>0.23</v>
       </c>
       <c r="H51" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="C52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D52" t="s">
         <v>19</v>
@@ -12807,15 +12474,15 @@
         <v>480</v>
       </c>
       <c r="H52" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="C53" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D53" t="s">
         <v>19</v>
@@ -12830,15 +12497,15 @@
         <v>16</v>
       </c>
       <c r="H53" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
     </row>
     <row r="54" spans="2:8">
       <c r="B54" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="C54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D54" t="s">
         <v>19</v>
@@ -12853,15 +12520,15 @@
         <v>1.5</v>
       </c>
       <c r="H54" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="C55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D55" t="s">
         <v>19</v>
@@ -12876,15 +12543,15 @@
         <v>0.39</v>
       </c>
       <c r="H55" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56" spans="2:8">
       <c r="B56" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="C56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D56" t="s">
         <v>19</v>
@@ -12899,15 +12566,15 @@
         <v>1800</v>
       </c>
       <c r="H56" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="B57" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="C57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D57" t="s">
         <v>19</v>
@@ -12922,15 +12589,15 @@
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="B58" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="C58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D58" t="s">
         <v>19</v>
@@ -12945,15 +12612,15 @@
         <v>0.43</v>
       </c>
       <c r="H58" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="2:8">
       <c r="B59" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="C59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D59" t="s">
         <v>19</v>
@@ -12968,15 +12635,15 @@
         <v>2100</v>
       </c>
       <c r="H59" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
     </row>
     <row r="60" spans="2:8">
       <c r="B60" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="C60" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D60" t="s">
         <v>19</v>
@@ -12991,15 +12658,15 @@
         <v>65</v>
       </c>
       <c r="H60" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="B61" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="C61" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D61" t="s">
         <v>19</v>
@@ -13014,15 +12681,15 @@
         <v>0.48</v>
       </c>
       <c r="H61" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" spans="2:8">
       <c r="B62" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="C62" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D62" t="s">
         <v>19</v>
@@ -13037,15 +12704,15 @@
         <v>2300</v>
       </c>
       <c r="H62" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="B63" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="C63" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D63" t="s">
         <v>19</v>
@@ -13060,15 +12727,15 @@
         <v>70</v>
       </c>
       <c r="H63" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
     </row>
     <row r="66" spans="2:8">
       <c r="B66" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="C66" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
@@ -13083,15 +12750,15 @@
         <v>1</v>
       </c>
       <c r="H66" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="67" spans="2:8">
       <c r="B67" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="C67" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
@@ -13106,15 +12773,15 @@
         <v>0.49</v>
       </c>
       <c r="H67" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
     </row>
     <row r="68" spans="2:8">
       <c r="B68" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="C68" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
@@ -13129,15 +12796,15 @@
         <v>1980</v>
       </c>
       <c r="H68" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
     </row>
     <row r="69" spans="2:8">
       <c r="B69" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="C69" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
@@ -13152,15 +12819,15 @@
         <v>70</v>
       </c>
       <c r="H69" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
     </row>
     <row r="70" spans="2:8">
       <c r="B70" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="C70" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="D70" t="s">
         <v>19</v>
@@ -13175,15 +12842,15 @@
         <v>3</v>
       </c>
       <c r="H70" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="C71" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="D71" t="s">
         <v>19</v>
@@ -13198,15 +12865,15 @@
         <v>1</v>
       </c>
       <c r="H71" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="72" spans="2:8">
       <c r="B72" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="C72" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="D72" t="s">
         <v>19</v>
@@ -13221,15 +12888,15 @@
         <v>0.44</v>
       </c>
       <c r="H72" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
     </row>
     <row r="73" spans="2:8">
       <c r="B73" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="C73" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="D73" t="s">
         <v>19</v>
@@ -13244,15 +12911,15 @@
         <v>1370</v>
       </c>
       <c r="H73" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
     </row>
     <row r="74" spans="2:8">
       <c r="B74" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="C74" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="D74" t="s">
         <v>19</v>
@@ -13267,15 +12934,15 @@
         <v>36</v>
       </c>
       <c r="H74" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
     </row>
     <row r="75" spans="2:8">
       <c r="B75" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="C75" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="D75" t="s">
         <v>19</v>
@@ -13290,7 +12957,7 @@
         <v>1.5</v>
       </c>
       <c r="H75" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
     </row>
   </sheetData>
